--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C056F41-D6D9-4CA5-82C2-3CDFE1A3B964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E9E61A4-74B9-4B31-B43C-90CCC9F8128C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1AD9C8EF-0A24-44F4-88D7-7B3BBBFBD485}"/>
+    <workbookView xWindow="7200" yWindow="30" windowWidth="21600" windowHeight="11385" xr2:uid="{A4B675B1-F77A-4BEE-9EF9-5ECEC5AAEFBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4984,7 +4984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA06D5F8-F8BA-4DE0-87C4-C81D57BB73BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B70F4FB-D88C-4329-A0F7-5D0EE33304B4}">
   <dimension ref="A1:N839"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5272,7 +5272,7 @@
         <v>297</v>
       </c>
       <c r="L7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -5644,7 +5644,7 @@
         <v>1700</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>3505</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>12000</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101">
         <v>0</v>
@@ -9636,7 +9636,7 @@
         <v>18000</v>
       </c>
       <c r="L110">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M110">
         <v>0</v>
@@ -10668,7 +10668,7 @@
         <v>8550</v>
       </c>
       <c r="K134">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L134">
         <v>2</v>
@@ -11843,7 +11843,7 @@
         <v>1230</v>
       </c>
       <c r="L162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M162">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>2000</v>
       </c>
       <c r="L193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193">
         <v>0</v>
@@ -14401,7 +14401,7 @@
         <v>1365</v>
       </c>
       <c r="L223">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M223">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>1929</v>
       </c>
       <c r="L227">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M227">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>5418</v>
       </c>
       <c r="L231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231">
         <v>0</v>
@@ -16093,7 +16093,7 @@
         <v>0</v>
       </c>
       <c r="L262">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M262">
         <v>0</v>
@@ -17763,7 +17763,7 @@
         <v>3225.8</v>
       </c>
       <c r="L302">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M302">
         <v>0</v>
@@ -18015,7 +18015,7 @@
         <v>3000</v>
       </c>
       <c r="L308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M308">
         <v>0</v>
@@ -19040,7 +19040,7 @@
         <v>1250</v>
       </c>
       <c r="L333">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M333">
         <v>0</v>
@@ -22544,7 +22544,7 @@
         <v>20000</v>
       </c>
       <c r="L417">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M417">
         <v>0</v>
@@ -22676,7 +22676,7 @@
         <v>20000</v>
       </c>
       <c r="L420">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M420">
         <v>0</v>
@@ -22764,7 +22764,7 @@
         <v>20000</v>
       </c>
       <c r="L422">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M422">
         <v>0</v>
@@ -22808,7 +22808,7 @@
         <v>26000</v>
       </c>
       <c r="L423">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M423">
         <v>0</v>
@@ -22852,7 +22852,7 @@
         <v>20000</v>
       </c>
       <c r="L424">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M424">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>22000</v>
       </c>
       <c r="L426">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M426">
         <v>0</v>
@@ -23186,7 +23186,7 @@
         <v>22400</v>
       </c>
       <c r="L432">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M432">
         <v>0</v>
@@ -23356,7 +23356,7 @@
         <v>23000</v>
       </c>
       <c r="L436">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -23485,7 +23485,7 @@
         <v>20000</v>
       </c>
       <c r="L439">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M439">
         <v>0</v>
@@ -23573,7 +23573,7 @@
         <v>22000</v>
       </c>
       <c r="L441">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M441">
         <v>0</v>
@@ -23599,25 +23599,25 @@
         <v>820</v>
       </c>
       <c r="F442">
-        <v>13050</v>
+        <v>14490</v>
       </c>
       <c r="G442">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H442">
         <v>21</v>
       </c>
       <c r="I442">
-        <v>13050</v>
+        <v>14490</v>
       </c>
       <c r="J442">
-        <v>22567.4</v>
+        <v>14490</v>
       </c>
       <c r="K442">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="L442">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -23643,25 +23643,25 @@
         <v>197</v>
       </c>
       <c r="F443">
-        <v>12750</v>
+        <v>11710</v>
       </c>
       <c r="G443">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="H443">
         <v>21</v>
       </c>
       <c r="I443">
-        <v>12750</v>
+        <v>11710</v>
       </c>
       <c r="J443">
-        <v>24106.400000000001</v>
+        <v>11710</v>
       </c>
       <c r="K443">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="L443">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -23690,7 +23690,7 @@
         <v>15860</v>
       </c>
       <c r="G444">
-        <v>48000</v>
+        <v>58000</v>
       </c>
       <c r="H444">
         <v>21</v>
@@ -23746,7 +23746,7 @@
         <v>24000</v>
       </c>
       <c r="L445">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M445">
         <v>0</v>
@@ -23790,7 +23790,7 @@
         <v>21000</v>
       </c>
       <c r="L446">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M446">
         <v>0</v>
@@ -23916,7 +23916,7 @@
         <v>30000</v>
       </c>
       <c r="L449">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M449">
         <v>0</v>
@@ -23957,7 +23957,7 @@
         <v>25000</v>
       </c>
       <c r="L450">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M450">
         <v>0</v>
@@ -24358,25 +24358,25 @@
         <v>28</v>
       </c>
       <c r="F460">
-        <v>11381</v>
+        <v>13175</v>
       </c>
       <c r="G460">
-        <v>40000</v>
+        <v>46304.9</v>
       </c>
       <c r="H460">
         <v>21</v>
       </c>
       <c r="I460">
-        <v>11381</v>
+        <v>13175</v>
       </c>
       <c r="J460">
-        <v>11381</v>
+        <v>13175</v>
       </c>
       <c r="K460">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="L460">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M460">
         <v>0</v>
@@ -25059,7 +25059,7 @@
         <v>20000</v>
       </c>
       <c r="L476">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M476">
         <v>0</v>
@@ -25100,7 +25100,7 @@
         <v>20000</v>
       </c>
       <c r="L477">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M477">
         <v>0</v>
@@ -25141,7 +25141,7 @@
         <v>20000</v>
       </c>
       <c r="L478">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M478">
         <v>0</v>
@@ -25229,7 +25229,7 @@
         <v>18000</v>
       </c>
       <c r="L480">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M480">
         <v>0</v>
@@ -25317,7 +25317,7 @@
         <v>21000</v>
       </c>
       <c r="L482">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M482">
         <v>0</v>
@@ -25402,7 +25402,7 @@
         <v>20000</v>
       </c>
       <c r="L484">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M484">
         <v>0</v>
@@ -25575,7 +25575,7 @@
         <v>22000</v>
       </c>
       <c r="L488">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>23000</v>
       </c>
       <c r="L490">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M490">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>24000</v>
       </c>
       <c r="L491">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M491">
         <v>0</v>
@@ -25821,7 +25821,7 @@
         <v>173</v>
       </c>
       <c r="F494">
-        <v>8897</v>
+        <v>10000</v>
       </c>
       <c r="G494">
         <v>40000</v>
@@ -25830,16 +25830,16 @@
         <v>21</v>
       </c>
       <c r="I494">
-        <v>8897</v>
+        <v>10000</v>
       </c>
       <c r="J494">
-        <v>18164.099999999999</v>
+        <v>10000</v>
       </c>
       <c r="K494">
         <v>20000</v>
       </c>
       <c r="L494">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M494">
         <v>0</v>
@@ -25868,7 +25868,7 @@
         <v>12408</v>
       </c>
       <c r="G495">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H495">
         <v>21</v>
@@ -25956,7 +25956,7 @@
         <v>11374</v>
       </c>
       <c r="G497">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H497">
         <v>21</v>
@@ -26015,7 +26015,7 @@
         <v>20000</v>
       </c>
       <c r="L498">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M498">
         <v>0</v>
@@ -26100,7 +26100,7 @@
         <v>20000</v>
       </c>
       <c r="L500">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M500">
         <v>0</v>
@@ -26226,7 +26226,7 @@
         <v>24000</v>
       </c>
       <c r="L503">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M503">
         <v>0</v>
@@ -26255,7 +26255,7 @@
         <v>17400</v>
       </c>
       <c r="G504">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="H504">
         <v>21</v>
@@ -26270,7 +26270,7 @@
         <v>29000</v>
       </c>
       <c r="L504">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M504">
         <v>0</v>
@@ -26299,7 +26299,7 @@
         <v>19860</v>
       </c>
       <c r="G505">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="H505">
         <v>21</v>
@@ -26704,7 +26704,7 @@
         <v>22000</v>
       </c>
       <c r="L514">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M514">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>21500</v>
       </c>
       <c r="L517">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M517">
         <v>0</v>
@@ -27006,7 +27006,7 @@
         <v>30000</v>
       </c>
       <c r="L521">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M521">
         <v>0</v>
@@ -27079,7 +27079,7 @@
         <v>17574</v>
       </c>
       <c r="G523">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="H523">
         <v>21</v>
@@ -27094,7 +27094,7 @@
         <v>30000</v>
       </c>
       <c r="L523">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M523">
         <v>0</v>
@@ -27182,7 +27182,7 @@
         <v>55000</v>
       </c>
       <c r="L525">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M525">
         <v>0</v>
@@ -27712,7 +27712,7 @@
         <v>931</v>
       </c>
       <c r="F538">
-        <v>8496</v>
+        <v>8183</v>
       </c>
       <c r="G538">
         <v>40000</v>
@@ -27721,16 +27721,16 @@
         <v>21</v>
       </c>
       <c r="I538">
-        <v>8496</v>
+        <v>8183</v>
       </c>
       <c r="J538">
-        <v>17221.400000000001</v>
+        <v>16586.900000000001</v>
       </c>
       <c r="K538">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="L538">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M538">
         <v>0</v>
@@ -27994,7 +27994,7 @@
         <v>23000</v>
       </c>
       <c r="L544">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M544">
         <v>0</v>
@@ -28020,25 +28020,25 @@
         <v>1021</v>
       </c>
       <c r="F545">
-        <v>15700</v>
+        <v>16500</v>
       </c>
       <c r="G545">
-        <v>52000</v>
+        <v>55000</v>
       </c>
       <c r="H545">
         <v>21</v>
       </c>
       <c r="I545">
-        <v>15700</v>
+        <v>16500</v>
       </c>
       <c r="J545">
-        <v>28125</v>
+        <v>29558.1</v>
       </c>
       <c r="K545">
-        <v>28125</v>
+        <v>26000</v>
       </c>
       <c r="L545">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M545">
         <v>0</v>
@@ -28082,7 +28082,7 @@
         <v>25000</v>
       </c>
       <c r="L546">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M546">
         <v>0</v>
@@ -28258,7 +28258,7 @@
         <v>24000</v>
       </c>
       <c r="L550">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M550">
         <v>0</v>
@@ -28560,7 +28560,7 @@
         <v>25000</v>
       </c>
       <c r="L557">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M557">
         <v>0</v>
@@ -28604,7 +28604,7 @@
         <v>23000</v>
       </c>
       <c r="L558">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M558">
         <v>0</v>
@@ -30568,7 +30568,7 @@
         <v>233</v>
       </c>
       <c r="L604">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M604">
         <v>0</v>
@@ -30612,7 +30612,7 @@
         <v>9000</v>
       </c>
       <c r="L605">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M605">
         <v>0</v>
@@ -30653,7 +30653,7 @@
         <v>8000</v>
       </c>
       <c r="L606">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M606">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>527</v>
       </c>
       <c r="L620">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M620">
         <v>0</v>
@@ -32716,7 +32716,7 @@
         <v>8000</v>
       </c>
       <c r="L655">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M655">
         <v>0</v>
@@ -32804,7 +32804,7 @@
         <v>10000</v>
       </c>
       <c r="L657">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M657">
         <v>0</v>
@@ -36551,7 +36551,7 @@
         <v>9493</v>
       </c>
       <c r="L744">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M744">
         <v>0</v>
@@ -40102,7 +40102,7 @@
         <v>12730</v>
       </c>
       <c r="L829">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M829">
         <v>0</v>
@@ -40395,7 +40395,7 @@
         <v>3613.6</v>
       </c>
       <c r="L836">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M836">
         <v>0</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{173ADEDD-713A-4DC5-B1C3-C0D5E44FA7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{911FE229-8046-4FBC-8FB7-91524BE71185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00B1A239-A322-4FBE-86A4-5F2F9A86D7DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B832782D-DF14-4080-911A-54E2E6E75704}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1589">
   <si>
     <t>CODIGO</t>
   </si>
@@ -1571,7 +1571,7 @@
     <t>CEPILLO MASAJEADOR B36</t>
   </si>
   <si>
-    <t>CEPILLO SECADOR ONE STEP</t>
+    <t>CEPILLO SECADOR 3 EN 1 HYTOSHY</t>
   </si>
   <si>
     <t>HYTOSHY</t>
@@ -1802,7 +1802,7 @@
     <t>DUCHA LORENZETTI</t>
   </si>
   <si>
-    <t>ELIMINADOR DE ARRUGAS OJERAS</t>
+    <t>ELIMINADOR DE ARRUGAS OJERAS B34</t>
   </si>
   <si>
     <t>ENCENDEDOR</t>
@@ -3074,7 +3074,7 @@
     <t>MODSAMA23</t>
   </si>
   <si>
-    <t xml:space="preserve">MOD SAMS A23 M33 </t>
+    <t>MOD SAMS A23 M33</t>
   </si>
   <si>
     <t>MODSAMA24IN</t>
@@ -4326,6 +4326,9 @@
   </si>
   <si>
     <t>REMOVEDOR PUNTOS NEGROS</t>
+  </si>
+  <si>
+    <t>REMOVEDOR PUNTOS NEGROS B34</t>
   </si>
   <si>
     <t>691782520248X</t>
@@ -5173,7 +5176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6A3A3-4604-49EA-90EB-3281858175EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B4DFA4-4840-4633-A54E-DC21D125F7E3}">
   <dimension ref="A1:N873"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6351,16 +6354,16 @@
         <v>30972</v>
       </c>
       <c r="G29">
-        <v>85720</v>
+        <v>60000</v>
       </c>
       <c r="H29">
         <v>21</v>
       </c>
       <c r="I29">
-        <v>60000</v>
+        <v>85000</v>
       </c>
       <c r="J29">
-        <v>35172</v>
+        <v>85000</v>
       </c>
       <c r="K29">
         <v>30972</v>
@@ -9801,16 +9804,16 @@
         <v>21</v>
       </c>
       <c r="I110">
-        <v>7700</v>
+        <v>28000</v>
       </c>
       <c r="J110">
-        <v>7700</v>
+        <v>18000</v>
       </c>
       <c r="K110">
         <v>18000</v>
       </c>
       <c r="L110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M110">
         <v>0</v>
@@ -15009,7 +15012,7 @@
         <v>1929</v>
       </c>
       <c r="L233">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M233">
         <v>0</v>
@@ -16686,7 +16689,7 @@
         <v>10000</v>
       </c>
       <c r="L272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -16917,16 +16920,16 @@
         <v>12740</v>
       </c>
       <c r="G278">
-        <v>26000</v>
+        <v>32000</v>
       </c>
       <c r="H278">
         <v>21</v>
       </c>
       <c r="I278">
-        <v>12740</v>
+        <v>32000</v>
       </c>
       <c r="J278">
-        <v>12740</v>
+        <v>32000</v>
       </c>
       <c r="K278">
         <v>12740</v>
@@ -18754,16 +18757,16 @@
         <v>3800</v>
       </c>
       <c r="G322">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H322">
         <v>21</v>
       </c>
       <c r="I322">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J322">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="K322">
         <v>0</v>
@@ -21800,16 +21803,16 @@
         <v>3500</v>
       </c>
       <c r="G396">
-        <v>8400</v>
+        <v>12000</v>
       </c>
       <c r="H396">
         <v>21</v>
       </c>
       <c r="I396">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="J396">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="K396">
         <v>0</v>
@@ -22993,10 +22996,10 @@
         <v>21</v>
       </c>
       <c r="I424">
-        <v>13702</v>
+        <v>45000</v>
       </c>
       <c r="J424">
-        <v>13702</v>
+        <v>24000</v>
       </c>
       <c r="K424">
         <v>24000</v>
@@ -23037,10 +23040,10 @@
         <v>21</v>
       </c>
       <c r="I425">
-        <v>13620</v>
+        <v>45000</v>
       </c>
       <c r="J425">
-        <v>13620</v>
+        <v>23000</v>
       </c>
       <c r="K425">
         <v>23000</v>
@@ -23081,10 +23084,10 @@
         <v>21</v>
       </c>
       <c r="I426">
-        <v>13465</v>
+        <v>48000</v>
       </c>
       <c r="J426">
-        <v>13465</v>
+        <v>23000</v>
       </c>
       <c r="K426">
         <v>23000</v>
@@ -23125,10 +23128,10 @@
         <v>21</v>
       </c>
       <c r="I427">
-        <v>15750</v>
+        <v>56000</v>
       </c>
       <c r="J427">
-        <v>15750</v>
+        <v>27000</v>
       </c>
       <c r="K427">
         <v>27000</v>
@@ -23213,13 +23216,13 @@
         <v>21</v>
       </c>
       <c r="I429">
-        <v>13650</v>
+        <v>48000</v>
       </c>
       <c r="J429">
-        <v>13650</v>
+        <v>23000</v>
       </c>
       <c r="K429">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="L429">
         <v>3</v>
@@ -23254,7 +23257,7 @@
         <v>21</v>
       </c>
       <c r="I430">
-        <v>9300</v>
+        <v>40000</v>
       </c>
       <c r="J430">
         <v>20000</v>
@@ -23298,10 +23301,10 @@
         <v>21</v>
       </c>
       <c r="I431">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="J431">
-        <v>20670</v>
+        <v>21000</v>
       </c>
       <c r="K431">
         <v>21000</v>
@@ -23342,10 +23345,10 @@
         <v>21</v>
       </c>
       <c r="I432">
-        <v>15785</v>
+        <v>55000</v>
       </c>
       <c r="J432">
-        <v>28229.9</v>
+        <v>27000</v>
       </c>
       <c r="K432">
         <v>27000</v>
@@ -23386,10 +23389,10 @@
         <v>21</v>
       </c>
       <c r="I433">
-        <v>13780</v>
+        <v>48000</v>
       </c>
       <c r="J433">
-        <v>13780</v>
+        <v>24000</v>
       </c>
       <c r="K433">
         <v>24000</v>
@@ -23430,10 +23433,10 @@
         <v>21</v>
       </c>
       <c r="I434">
-        <v>12900</v>
+        <v>45000</v>
       </c>
       <c r="J434">
-        <v>12900</v>
+        <v>22000</v>
       </c>
       <c r="K434">
         <v>22000</v>
@@ -23468,13 +23471,13 @@
         <v>14457</v>
       </c>
       <c r="G435">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="H435">
         <v>21</v>
       </c>
       <c r="I435">
-        <v>14457</v>
+        <v>50000</v>
       </c>
       <c r="J435">
         <v>25000</v>
@@ -23518,10 +23521,10 @@
         <v>21</v>
       </c>
       <c r="I436">
-        <v>11540</v>
+        <v>40000</v>
       </c>
       <c r="J436">
-        <v>11540</v>
+        <v>20000</v>
       </c>
       <c r="K436">
         <v>20000</v>
@@ -23556,16 +23559,16 @@
         <v>13400</v>
       </c>
       <c r="G437">
-        <v>42000</v>
+        <v>50000</v>
       </c>
       <c r="H437">
         <v>21</v>
       </c>
       <c r="I437">
-        <v>13400</v>
+        <v>50000</v>
       </c>
       <c r="J437">
-        <v>13400</v>
+        <v>26000</v>
       </c>
       <c r="K437">
         <v>26000</v>
@@ -23606,10 +23609,10 @@
         <v>21</v>
       </c>
       <c r="I438">
-        <v>13140</v>
+        <v>45000</v>
       </c>
       <c r="J438">
-        <v>13140</v>
+        <v>22000</v>
       </c>
       <c r="K438">
         <v>22000</v>
@@ -23650,10 +23653,10 @@
         <v>21</v>
       </c>
       <c r="I439">
-        <v>14740</v>
+        <v>50000</v>
       </c>
       <c r="J439">
-        <v>14740</v>
+        <v>25000</v>
       </c>
       <c r="K439">
         <v>25000</v>
@@ -23694,10 +23697,10 @@
         <v>21</v>
       </c>
       <c r="I440">
-        <v>12150</v>
+        <v>45000</v>
       </c>
       <c r="J440">
-        <v>12150</v>
+        <v>21000</v>
       </c>
       <c r="K440">
         <v>21000</v>
@@ -23729,19 +23732,19 @@
         <v>9270</v>
       </c>
       <c r="G441">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="H441">
         <v>21</v>
       </c>
       <c r="I441">
-        <v>9270</v>
+        <v>40000</v>
       </c>
       <c r="J441">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="K441">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L441">
         <v>1</v>
@@ -23770,16 +23773,16 @@
         <v>14000</v>
       </c>
       <c r="G442">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="H442">
         <v>21</v>
       </c>
       <c r="I442">
-        <v>14000</v>
+        <v>45000</v>
       </c>
       <c r="J442">
-        <v>22999.200000000001</v>
+        <v>23000</v>
       </c>
       <c r="K442">
         <v>23000</v>
@@ -23817,10 +23820,10 @@
         <v>21</v>
       </c>
       <c r="I443">
-        <v>13585</v>
+        <v>40000</v>
       </c>
       <c r="J443">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="K443">
         <v>23000</v>
@@ -23858,7 +23861,7 @@
         <v>21</v>
       </c>
       <c r="I444">
-        <v>12276</v>
+        <v>40000</v>
       </c>
       <c r="J444">
         <v>21000</v>
@@ -23899,10 +23902,10 @@
         <v>21</v>
       </c>
       <c r="I445">
-        <v>12240</v>
+        <v>42000</v>
       </c>
       <c r="J445">
-        <v>12240</v>
+        <v>21000</v>
       </c>
       <c r="K445">
         <v>21000</v>
@@ -23940,10 +23943,10 @@
         <v>21</v>
       </c>
       <c r="I446">
-        <v>13140.3</v>
+        <v>45000</v>
       </c>
       <c r="J446">
-        <v>13140.3</v>
+        <v>23000</v>
       </c>
       <c r="K446">
         <v>23000</v>
@@ -23981,13 +23984,13 @@
         <v>21</v>
       </c>
       <c r="I447">
-        <v>15793</v>
+        <v>45000</v>
       </c>
       <c r="J447">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="K447">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="L447">
         <v>1</v>
@@ -24022,10 +24025,10 @@
         <v>21</v>
       </c>
       <c r="I448">
-        <v>11012</v>
+        <v>40000</v>
       </c>
       <c r="J448">
-        <v>18696.2</v>
+        <v>20000</v>
       </c>
       <c r="K448">
         <v>20000</v>
@@ -24066,13 +24069,13 @@
         <v>21</v>
       </c>
       <c r="I449">
-        <v>14297</v>
+        <v>55000</v>
       </c>
       <c r="J449">
-        <v>14297</v>
+        <v>25000</v>
       </c>
       <c r="K449">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="L449">
         <v>1</v>
@@ -24110,10 +24113,10 @@
         <v>21</v>
       </c>
       <c r="I450">
-        <v>13345</v>
+        <v>45000</v>
       </c>
       <c r="J450">
-        <v>13345</v>
+        <v>23000</v>
       </c>
       <c r="K450">
         <v>23000</v>
@@ -24151,13 +24154,13 @@
         <v>21</v>
       </c>
       <c r="I451">
-        <v>15750</v>
+        <v>58000</v>
       </c>
       <c r="J451">
-        <v>29340.7</v>
+        <v>26000</v>
       </c>
       <c r="K451">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="L451">
         <v>1</v>
@@ -24189,19 +24192,19 @@
         <v>13420</v>
       </c>
       <c r="G452">
-        <v>52000</v>
+        <v>50000</v>
       </c>
       <c r="H452">
         <v>21</v>
       </c>
       <c r="I452">
-        <v>13420</v>
+        <v>50000</v>
       </c>
       <c r="J452">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="K452">
-        <v>26000</v>
+        <v>24000</v>
       </c>
       <c r="L452">
         <v>1</v>
@@ -24239,10 +24242,10 @@
         <v>21</v>
       </c>
       <c r="I453">
-        <v>12200</v>
+        <v>40000</v>
       </c>
       <c r="J453">
-        <v>12200</v>
+        <v>20000</v>
       </c>
       <c r="K453">
         <v>20000</v>
@@ -24283,7 +24286,7 @@
         <v>21</v>
       </c>
       <c r="I454">
-        <v>4740</v>
+        <v>40000</v>
       </c>
       <c r="J454">
         <v>20000</v>
@@ -24371,13 +24374,13 @@
         <v>21</v>
       </c>
       <c r="I456">
-        <v>14800</v>
+        <v>50000</v>
       </c>
       <c r="J456">
-        <v>14800</v>
+        <v>25000</v>
       </c>
       <c r="K456">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="L456">
         <v>3</v>
@@ -24415,10 +24418,10 @@
         <v>21</v>
       </c>
       <c r="I457">
-        <v>14490</v>
+        <v>50000</v>
       </c>
       <c r="J457">
-        <v>14490</v>
+        <v>24000</v>
       </c>
       <c r="K457">
         <v>24000</v>
@@ -24459,10 +24462,10 @@
         <v>21</v>
       </c>
       <c r="I458">
-        <v>11710</v>
+        <v>40000</v>
       </c>
       <c r="J458">
-        <v>11710</v>
+        <v>20000</v>
       </c>
       <c r="K458">
         <v>20000</v>
@@ -24503,7 +24506,7 @@
         <v>21</v>
       </c>
       <c r="I459">
-        <v>15860</v>
+        <v>58000</v>
       </c>
       <c r="J459">
         <v>27000</v>
@@ -24547,10 +24550,10 @@
         <v>21</v>
       </c>
       <c r="I460">
-        <v>13300</v>
+        <v>45000</v>
       </c>
       <c r="J460">
-        <v>23932</v>
+        <v>23000</v>
       </c>
       <c r="K460">
         <v>23000</v>
@@ -24591,10 +24594,10 @@
         <v>21</v>
       </c>
       <c r="I461">
-        <v>12666</v>
+        <v>50000</v>
       </c>
       <c r="J461">
-        <v>12666</v>
+        <v>22000</v>
       </c>
       <c r="K461">
         <v>22000</v>
@@ -24635,10 +24638,10 @@
         <v>21</v>
       </c>
       <c r="I462">
-        <v>15300</v>
+        <v>54000</v>
       </c>
       <c r="J462">
-        <v>15300</v>
+        <v>26500</v>
       </c>
       <c r="K462">
         <v>26500</v>
@@ -24676,7 +24679,7 @@
         <v>21</v>
       </c>
       <c r="I463">
-        <v>6500</v>
+        <v>40000</v>
       </c>
       <c r="J463">
         <v>20000</v>
@@ -24717,10 +24720,10 @@
         <v>21</v>
       </c>
       <c r="I464">
-        <v>17250</v>
+        <v>60000</v>
       </c>
       <c r="J464">
-        <v>17250</v>
+        <v>30000</v>
       </c>
       <c r="K464">
         <v>30000</v>
@@ -24802,10 +24805,10 @@
         <v>21</v>
       </c>
       <c r="I466">
-        <v>13000</v>
+        <v>45000</v>
       </c>
       <c r="J466">
-        <v>13000</v>
+        <v>23000</v>
       </c>
       <c r="K466">
         <v>23000</v>
@@ -24843,10 +24846,10 @@
         <v>21</v>
       </c>
       <c r="I467">
-        <v>14800</v>
+        <v>50000</v>
       </c>
       <c r="J467">
-        <v>14800</v>
+        <v>25000</v>
       </c>
       <c r="K467">
         <v>25000</v>
@@ -24887,10 +24890,10 @@
         <v>21</v>
       </c>
       <c r="I468">
-        <v>16800</v>
+        <v>58000</v>
       </c>
       <c r="J468">
-        <v>16800</v>
+        <v>28000</v>
       </c>
       <c r="K468">
         <v>28000</v>
@@ -24922,16 +24925,16 @@
         <v>11656</v>
       </c>
       <c r="G469">
-        <v>36000</v>
+        <v>40000</v>
       </c>
       <c r="H469">
         <v>21</v>
       </c>
       <c r="I469">
-        <v>11656</v>
+        <v>40000</v>
       </c>
       <c r="J469">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="K469">
         <v>20000</v>
@@ -24972,10 +24975,10 @@
         <v>21</v>
       </c>
       <c r="I470">
-        <v>18610</v>
+        <v>60000</v>
       </c>
       <c r="J470">
-        <v>18610</v>
+        <v>28000</v>
       </c>
       <c r="K470">
         <v>28000</v>
@@ -25016,13 +25019,13 @@
         <v>21</v>
       </c>
       <c r="I471">
-        <v>56250</v>
+        <v>140000</v>
       </c>
       <c r="J471">
-        <v>56250</v>
+        <v>82000</v>
       </c>
       <c r="K471">
-        <v>85000</v>
+        <v>82000</v>
       </c>
       <c r="L471">
         <v>1</v>
@@ -25057,7 +25060,7 @@
         <v>21</v>
       </c>
       <c r="I472">
-        <v>5952</v>
+        <v>40000</v>
       </c>
       <c r="J472">
         <v>20000</v>
@@ -25098,10 +25101,10 @@
         <v>21</v>
       </c>
       <c r="I473">
-        <v>11376</v>
+        <v>40000</v>
       </c>
       <c r="J473">
-        <v>20183.3</v>
+        <v>20000</v>
       </c>
       <c r="K473">
         <v>20000</v>
@@ -25133,19 +25136,19 @@
         <v>15872</v>
       </c>
       <c r="G474">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H474">
         <v>21</v>
       </c>
       <c r="I474">
-        <v>15872</v>
+        <v>50000</v>
       </c>
       <c r="J474">
         <v>26000</v>
       </c>
       <c r="K474">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="L474">
         <v>1</v>
@@ -25174,16 +25177,16 @@
         <v>14880</v>
       </c>
       <c r="G475">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H475">
         <v>21</v>
       </c>
       <c r="I475">
-        <v>14880</v>
+        <v>45000</v>
       </c>
       <c r="J475">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="K475">
         <v>23000</v>
@@ -25215,16 +25218,16 @@
         <v>10939</v>
       </c>
       <c r="G476">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="H476">
         <v>21</v>
       </c>
       <c r="I476">
-        <v>10939</v>
+        <v>40000</v>
       </c>
       <c r="J476">
-        <v>10939</v>
+        <v>20000</v>
       </c>
       <c r="K476">
         <v>20000</v>
@@ -25256,16 +25259,16 @@
         <v>13175</v>
       </c>
       <c r="G477">
-        <v>46304.9</v>
+        <v>45000</v>
       </c>
       <c r="H477">
         <v>21</v>
       </c>
       <c r="I477">
-        <v>13175</v>
+        <v>45000</v>
       </c>
       <c r="J477">
-        <v>13175</v>
+        <v>22000</v>
       </c>
       <c r="K477">
         <v>22000</v>
@@ -25297,16 +25300,16 @@
         <v>15872</v>
       </c>
       <c r="G478">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="H478">
         <v>21</v>
       </c>
       <c r="I478">
-        <v>15872</v>
+        <v>50000</v>
       </c>
       <c r="J478">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="K478">
         <v>25000</v>
@@ -25347,10 +25350,10 @@
         <v>21</v>
       </c>
       <c r="I479">
-        <v>19500</v>
+        <v>68000</v>
       </c>
       <c r="J479">
-        <v>19500</v>
+        <v>32000</v>
       </c>
       <c r="K479">
         <v>32000</v>
@@ -25388,10 +25391,10 @@
         <v>21</v>
       </c>
       <c r="I480">
-        <v>13640</v>
+        <v>40000</v>
       </c>
       <c r="J480">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="K480">
         <v>23000</v>
@@ -25429,7 +25432,7 @@
         <v>21</v>
       </c>
       <c r="I481">
-        <v>11160</v>
+        <v>40000</v>
       </c>
       <c r="J481">
         <v>20000</v>
@@ -25473,10 +25476,10 @@
         <v>21</v>
       </c>
       <c r="I482">
-        <v>12682</v>
+        <v>45000</v>
       </c>
       <c r="J482">
-        <v>21985.5</v>
+        <v>22000</v>
       </c>
       <c r="K482">
         <v>22000</v>
@@ -25514,13 +25517,13 @@
         <v>21</v>
       </c>
       <c r="I483">
-        <v>15264</v>
+        <v>48000</v>
       </c>
       <c r="J483">
-        <v>25544.3</v>
+        <v>25000</v>
       </c>
       <c r="K483">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="L483">
         <v>1</v>
@@ -25558,10 +25561,10 @@
         <v>21</v>
       </c>
       <c r="I484">
-        <v>12453</v>
+        <v>45000</v>
       </c>
       <c r="J484">
-        <v>21660.7</v>
+        <v>21500</v>
       </c>
       <c r="K484">
         <v>21500</v>
@@ -25599,10 +25602,10 @@
         <v>21</v>
       </c>
       <c r="I485">
-        <v>10184</v>
+        <v>40000</v>
       </c>
       <c r="J485">
-        <v>20242.7</v>
+        <v>20000</v>
       </c>
       <c r="K485">
         <v>20000</v>
@@ -25637,16 +25640,16 @@
         <v>13132</v>
       </c>
       <c r="G486">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="H486">
         <v>21</v>
       </c>
       <c r="I486">
-        <v>13132</v>
+        <v>45000</v>
       </c>
       <c r="J486">
-        <v>13132</v>
+        <v>22500</v>
       </c>
       <c r="K486">
         <v>22500</v>
@@ -25687,13 +25690,13 @@
         <v>21</v>
       </c>
       <c r="I487">
-        <v>15916</v>
+        <v>55000</v>
       </c>
       <c r="J487">
-        <v>15916</v>
+        <v>26000</v>
       </c>
       <c r="K487">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="L487">
         <v>2</v>
@@ -25728,13 +25731,13 @@
         <v>21</v>
       </c>
       <c r="I488">
-        <v>13780</v>
+        <v>45000</v>
       </c>
       <c r="J488">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="K488">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="L488">
         <v>1</v>
@@ -25772,10 +25775,10 @@
         <v>21</v>
       </c>
       <c r="I489">
-        <v>2600</v>
+        <v>40000</v>
       </c>
       <c r="J489">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="K489">
         <v>20000</v>
@@ -25816,10 +25819,10 @@
         <v>21</v>
       </c>
       <c r="I490">
-        <v>2600</v>
+        <v>40000</v>
       </c>
       <c r="J490">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="K490">
         <v>20000</v>
@@ -25860,10 +25863,10 @@
         <v>21</v>
       </c>
       <c r="I491">
-        <v>5200</v>
+        <v>45000</v>
       </c>
       <c r="J491">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="K491">
         <v>22000</v>
@@ -25904,10 +25907,10 @@
         <v>21</v>
       </c>
       <c r="I492">
-        <v>13796</v>
+        <v>48000</v>
       </c>
       <c r="J492">
-        <v>13796</v>
+        <v>24000</v>
       </c>
       <c r="K492">
         <v>24000</v>
@@ -25945,10 +25948,10 @@
         <v>21</v>
       </c>
       <c r="I493">
-        <v>9902</v>
+        <v>40000</v>
       </c>
       <c r="J493">
-        <v>9902</v>
+        <v>20000</v>
       </c>
       <c r="K493">
         <v>20000</v>
@@ -26074,7 +26077,7 @@
         <v>21</v>
       </c>
       <c r="I496">
-        <v>10500</v>
+        <v>40000</v>
       </c>
       <c r="J496">
         <v>20000</v>
@@ -26118,10 +26121,10 @@
         <v>21</v>
       </c>
       <c r="I497">
-        <v>11340</v>
+        <v>40000</v>
       </c>
       <c r="J497">
-        <v>11340</v>
+        <v>18000</v>
       </c>
       <c r="K497">
         <v>18000</v>
@@ -26156,16 +26159,16 @@
         <v>11270</v>
       </c>
       <c r="G498">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H498">
         <v>21</v>
       </c>
       <c r="I498">
-        <v>11270</v>
+        <v>45000</v>
       </c>
       <c r="J498">
-        <v>21011.8</v>
+        <v>24000</v>
       </c>
       <c r="K498">
         <v>24000</v>
@@ -26241,19 +26244,19 @@
         <v>13700</v>
       </c>
       <c r="G500">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="H500">
         <v>21</v>
       </c>
       <c r="I500">
-        <v>13700</v>
+        <v>50000</v>
       </c>
       <c r="J500">
-        <v>13700</v>
+        <v>24000</v>
       </c>
       <c r="K500">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="L500">
         <v>3</v>
@@ -26282,19 +26285,19 @@
         <v>13530</v>
       </c>
       <c r="G501">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H501">
         <v>21</v>
       </c>
       <c r="I501">
-        <v>13530</v>
+        <v>45000</v>
       </c>
       <c r="J501">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="K501">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="L501">
         <v>0</v>
@@ -26332,16 +26335,16 @@
         <v>21</v>
       </c>
       <c r="I502">
-        <v>12310</v>
+        <v>40000</v>
       </c>
       <c r="J502">
-        <v>12310</v>
+        <v>20000</v>
       </c>
       <c r="K502">
         <v>20000</v>
       </c>
       <c r="L502">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M502">
         <v>0</v>
@@ -26370,22 +26373,22 @@
         <v>14500</v>
       </c>
       <c r="G503">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H503">
         <v>21</v>
       </c>
       <c r="I503">
-        <v>14500</v>
+        <v>50000</v>
       </c>
       <c r="J503">
-        <v>26305.9</v>
+        <v>25000</v>
       </c>
       <c r="K503">
         <v>25000</v>
       </c>
       <c r="L503">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M503">
         <v>0</v>
@@ -26411,13 +26414,13 @@
         <v>14141.4</v>
       </c>
       <c r="G504">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="H504">
         <v>21</v>
       </c>
       <c r="I504">
-        <v>14141.4</v>
+        <v>40000</v>
       </c>
       <c r="J504">
         <v>22000</v>
@@ -26461,10 +26464,10 @@
         <v>21</v>
       </c>
       <c r="I505">
-        <v>16295</v>
+        <v>50000</v>
       </c>
       <c r="J505">
-        <v>33425.9</v>
+        <v>26000</v>
       </c>
       <c r="K505">
         <v>26000</v>
@@ -26505,10 +26508,10 @@
         <v>21</v>
       </c>
       <c r="I506">
-        <v>12500</v>
+        <v>40000</v>
       </c>
       <c r="J506">
-        <v>22401.200000000001</v>
+        <v>22000</v>
       </c>
       <c r="K506">
         <v>22000</v>
@@ -26543,16 +26546,16 @@
         <v>15510</v>
       </c>
       <c r="G507">
-        <v>47350.5</v>
+        <v>50000</v>
       </c>
       <c r="H507">
         <v>21</v>
       </c>
       <c r="I507">
-        <v>15510</v>
+        <v>50000</v>
       </c>
       <c r="J507">
-        <v>15510</v>
+        <v>26500</v>
       </c>
       <c r="K507">
         <v>26500</v>
@@ -26593,10 +26596,10 @@
         <v>21</v>
       </c>
       <c r="I508">
-        <v>13892</v>
+        <v>48000</v>
       </c>
       <c r="J508">
-        <v>13892</v>
+        <v>23000</v>
       </c>
       <c r="K508">
         <v>23000</v>
@@ -26637,10 +26640,10 @@
         <v>21</v>
       </c>
       <c r="I509">
-        <v>15100</v>
+        <v>55000</v>
       </c>
       <c r="J509">
-        <v>15100</v>
+        <v>26000</v>
       </c>
       <c r="K509">
         <v>26000</v>
@@ -26681,10 +26684,10 @@
         <v>21</v>
       </c>
       <c r="I510">
-        <v>12700</v>
+        <v>45000</v>
       </c>
       <c r="J510">
-        <v>22799</v>
+        <v>22000</v>
       </c>
       <c r="K510">
         <v>22000</v>
@@ -26725,13 +26728,13 @@
         <v>21</v>
       </c>
       <c r="I511">
-        <v>15400</v>
+        <v>58000</v>
       </c>
       <c r="J511">
-        <v>15400</v>
+        <v>26000</v>
       </c>
       <c r="K511">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="L511">
         <v>3</v>
@@ -26769,16 +26772,16 @@
         <v>21</v>
       </c>
       <c r="I512">
-        <v>13180</v>
+        <v>48000</v>
       </c>
       <c r="J512">
-        <v>13180</v>
+        <v>23000</v>
       </c>
       <c r="K512">
         <v>23000</v>
       </c>
       <c r="L512">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M512">
         <v>0</v>
@@ -26813,10 +26816,10 @@
         <v>21</v>
       </c>
       <c r="I513">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="J513">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="K513">
         <v>20000</v>
@@ -26857,10 +26860,10 @@
         <v>21</v>
       </c>
       <c r="I514">
-        <v>12408</v>
+        <v>45000</v>
       </c>
       <c r="J514">
-        <v>25129.9</v>
+        <v>24000</v>
       </c>
       <c r="K514">
         <v>24000</v>
@@ -26901,10 +26904,10 @@
         <v>21</v>
       </c>
       <c r="I515">
-        <v>10074</v>
+        <v>40000</v>
       </c>
       <c r="J515">
-        <v>22658.400000000001</v>
+        <v>20000</v>
       </c>
       <c r="K515">
         <v>20000</v>
@@ -26945,7 +26948,7 @@
         <v>21</v>
       </c>
       <c r="I516">
-        <v>11374</v>
+        <v>45000</v>
       </c>
       <c r="J516">
         <v>24000</v>
@@ -26989,7 +26992,7 @@
         <v>21</v>
       </c>
       <c r="I517">
-        <v>10578</v>
+        <v>40000</v>
       </c>
       <c r="J517">
         <v>20000</v>
@@ -27024,13 +27027,13 @@
         <v>13038</v>
       </c>
       <c r="G518">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H518">
         <v>21</v>
       </c>
       <c r="I518">
-        <v>13038</v>
+        <v>45000</v>
       </c>
       <c r="J518">
         <v>25000</v>
@@ -27109,19 +27112,19 @@
         <v>15000</v>
       </c>
       <c r="G520">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H520">
         <v>21</v>
       </c>
       <c r="I520">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="J520">
         <v>26000</v>
       </c>
       <c r="K520">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="L520">
         <v>1</v>
@@ -27150,13 +27153,13 @@
         <v>15000</v>
       </c>
       <c r="G521">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H521">
         <v>21</v>
       </c>
       <c r="I521">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="J521">
         <v>25000</v>
@@ -27288,10 +27291,10 @@
         <v>21</v>
       </c>
       <c r="I524">
-        <v>19860</v>
+        <v>50000</v>
       </c>
       <c r="J524">
-        <v>19860</v>
+        <v>26000</v>
       </c>
       <c r="K524">
         <v>26000</v>
@@ -27332,10 +27335,10 @@
         <v>21</v>
       </c>
       <c r="I525">
-        <v>49300</v>
+        <v>125000</v>
       </c>
       <c r="J525">
-        <v>49300</v>
+        <v>64000</v>
       </c>
       <c r="K525">
         <v>64000</v>
@@ -27376,10 +27379,10 @@
         <v>21</v>
       </c>
       <c r="I526">
-        <v>18500</v>
+        <v>60000</v>
       </c>
       <c r="J526">
-        <v>18500</v>
+        <v>30000</v>
       </c>
       <c r="K526">
         <v>30000</v>
@@ -27420,10 +27423,10 @@
         <v>21</v>
       </c>
       <c r="I527">
-        <v>18200</v>
+        <v>60000</v>
       </c>
       <c r="J527">
-        <v>18200</v>
+        <v>30000</v>
       </c>
       <c r="K527">
         <v>30000</v>
@@ -27464,10 +27467,10 @@
         <v>21</v>
       </c>
       <c r="I528">
-        <v>17941</v>
+        <v>55000</v>
       </c>
       <c r="J528">
-        <v>17941</v>
+        <v>28000</v>
       </c>
       <c r="K528">
         <v>28000</v>
@@ -27508,7 +27511,7 @@
         <v>21</v>
       </c>
       <c r="I529">
-        <v>2460</v>
+        <v>40000</v>
       </c>
       <c r="J529">
         <v>20000</v>
@@ -27552,10 +27555,10 @@
         <v>21</v>
       </c>
       <c r="I530">
-        <v>14060</v>
+        <v>45000</v>
       </c>
       <c r="J530">
-        <v>25346</v>
+        <v>23000</v>
       </c>
       <c r="K530">
         <v>23000</v>
@@ -27596,10 +27599,10 @@
         <v>21</v>
       </c>
       <c r="I531">
-        <v>30135</v>
+        <v>72000</v>
       </c>
       <c r="J531">
-        <v>49575.1</v>
+        <v>45000</v>
       </c>
       <c r="K531">
         <v>45000</v>
@@ -27637,10 +27640,10 @@
         <v>21</v>
       </c>
       <c r="I532">
-        <v>10634</v>
+        <v>40000</v>
       </c>
       <c r="J532">
-        <v>18545.7</v>
+        <v>20000</v>
       </c>
       <c r="K532">
         <v>20000</v>
@@ -27678,10 +27681,10 @@
         <v>21</v>
       </c>
       <c r="I533">
-        <v>22140</v>
+        <v>58000</v>
       </c>
       <c r="J533">
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="K533">
         <v>32000</v>
@@ -27757,16 +27760,16 @@
         <v>13700</v>
       </c>
       <c r="G535">
-        <v>46000</v>
+        <v>50000</v>
       </c>
       <c r="H535">
         <v>21</v>
       </c>
       <c r="I535">
-        <v>13700</v>
+        <v>50000</v>
       </c>
       <c r="J535">
-        <v>13700</v>
+        <v>24000</v>
       </c>
       <c r="K535">
         <v>24000</v>
@@ -27801,16 +27804,16 @@
         <v>16000</v>
       </c>
       <c r="G536">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H536">
         <v>21</v>
       </c>
       <c r="I536">
-        <v>16000</v>
+        <v>50000</v>
       </c>
       <c r="J536">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="K536">
         <v>26000</v>
@@ -27851,10 +27854,10 @@
         <v>21</v>
       </c>
       <c r="I537">
-        <v>12400</v>
+        <v>45000</v>
       </c>
       <c r="J537">
-        <v>22797.4</v>
+        <v>22000</v>
       </c>
       <c r="K537">
         <v>22000</v>
@@ -27895,10 +27898,10 @@
         <v>21</v>
       </c>
       <c r="I538">
-        <v>12470</v>
+        <v>45000</v>
       </c>
       <c r="J538">
-        <v>12470</v>
+        <v>22000</v>
       </c>
       <c r="K538">
         <v>22000</v>
@@ -27939,10 +27942,10 @@
         <v>21</v>
       </c>
       <c r="I539">
-        <v>18675</v>
+        <v>68000</v>
       </c>
       <c r="J539">
-        <v>18675</v>
+        <v>32000</v>
       </c>
       <c r="K539">
         <v>32000</v>
@@ -27983,10 +27986,10 @@
         <v>21</v>
       </c>
       <c r="I540">
-        <v>18370</v>
+        <v>68000</v>
       </c>
       <c r="J540">
-        <v>18370</v>
+        <v>32000</v>
       </c>
       <c r="K540">
         <v>32000</v>
@@ -28024,10 +28027,10 @@
         <v>21</v>
       </c>
       <c r="I541">
-        <v>20662</v>
+        <v>68000</v>
       </c>
       <c r="J541">
-        <v>20662</v>
+        <v>31000</v>
       </c>
       <c r="K541">
         <v>31000</v>
@@ -28068,10 +28071,10 @@
         <v>21</v>
       </c>
       <c r="I542">
-        <v>38250</v>
+        <v>92000</v>
       </c>
       <c r="J542">
-        <v>38250</v>
+        <v>57375</v>
       </c>
       <c r="K542">
         <v>57375</v>
@@ -28112,13 +28115,13 @@
         <v>21</v>
       </c>
       <c r="I543">
-        <v>39600</v>
+        <v>96000</v>
       </c>
       <c r="J543">
-        <v>39600</v>
+        <v>57000</v>
       </c>
       <c r="K543">
-        <v>59400</v>
+        <v>57000</v>
       </c>
       <c r="L543">
         <v>1</v>
@@ -28156,10 +28159,10 @@
         <v>21</v>
       </c>
       <c r="I544">
-        <v>18000</v>
+        <v>55000</v>
       </c>
       <c r="J544">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="K544">
         <v>30000</v>
@@ -28200,10 +28203,10 @@
         <v>21</v>
       </c>
       <c r="I545">
-        <v>38250</v>
+        <v>98000</v>
       </c>
       <c r="J545">
-        <v>38250</v>
+        <v>57375</v>
       </c>
       <c r="K545">
         <v>57375</v>
@@ -28244,10 +28247,10 @@
         <v>21</v>
       </c>
       <c r="I546">
-        <v>17760</v>
+        <v>55000</v>
       </c>
       <c r="J546">
-        <v>17760</v>
+        <v>30000</v>
       </c>
       <c r="K546">
         <v>30000</v>
@@ -28288,10 +28291,10 @@
         <v>21</v>
       </c>
       <c r="I547">
-        <v>18845</v>
+        <v>50000</v>
       </c>
       <c r="J547">
-        <v>18845</v>
+        <v>27000</v>
       </c>
       <c r="K547">
         <v>27000</v>
@@ -28332,10 +28335,10 @@
         <v>21</v>
       </c>
       <c r="I548">
-        <v>44300</v>
+        <v>90000</v>
       </c>
       <c r="J548">
-        <v>44300</v>
+        <v>55000</v>
       </c>
       <c r="K548">
         <v>55000</v>
@@ -28376,13 +28379,13 @@
         <v>21</v>
       </c>
       <c r="I549">
-        <v>17500</v>
+        <v>60000</v>
       </c>
       <c r="J549">
-        <v>17500</v>
+        <v>30000</v>
       </c>
       <c r="K549">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="L549">
         <v>6</v>
@@ -28420,10 +28423,10 @@
         <v>21</v>
       </c>
       <c r="I550">
-        <v>26825</v>
+        <v>75000</v>
       </c>
       <c r="J550">
-        <v>26825</v>
+        <v>40000</v>
       </c>
       <c r="K550">
         <v>40000</v>
@@ -28461,7 +28464,7 @@
         <v>21</v>
       </c>
       <c r="I551">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="J551">
         <v>20000</v>
@@ -28502,7 +28505,7 @@
         <v>21</v>
       </c>
       <c r="I552">
-        <v>4900</v>
+        <v>40000</v>
       </c>
       <c r="J552">
         <v>20000</v>
@@ -28546,10 +28549,10 @@
         <v>21</v>
       </c>
       <c r="I553">
-        <v>5040</v>
+        <v>40000</v>
       </c>
       <c r="J553">
-        <v>5040</v>
+        <v>20000</v>
       </c>
       <c r="K553">
         <v>20000</v>
@@ -28587,10 +28590,10 @@
         <v>21</v>
       </c>
       <c r="I554">
-        <v>12220.7</v>
+        <v>40000</v>
       </c>
       <c r="J554">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K554">
         <v>21000</v>
@@ -28628,10 +28631,10 @@
         <v>21</v>
       </c>
       <c r="I555">
-        <v>8466</v>
+        <v>40000</v>
       </c>
       <c r="J555">
-        <v>17160.599999999999</v>
+        <v>20000</v>
       </c>
       <c r="K555">
         <v>20000</v>
@@ -28666,19 +28669,19 @@
         <v>8064</v>
       </c>
       <c r="G556">
-        <v>26879.7</v>
+        <v>40000</v>
       </c>
       <c r="H556">
         <v>21</v>
       </c>
       <c r="I556">
-        <v>8064</v>
+        <v>40000</v>
       </c>
       <c r="J556">
-        <v>15360.3</v>
+        <v>20000</v>
       </c>
       <c r="K556">
-        <v>15360.3</v>
+        <v>20000</v>
       </c>
       <c r="L556">
         <v>4</v>
@@ -28710,16 +28713,16 @@
         <v>5040</v>
       </c>
       <c r="G557">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="H557">
         <v>21</v>
       </c>
       <c r="I557">
-        <v>5040</v>
+        <v>40000</v>
       </c>
       <c r="J557">
-        <v>5040</v>
+        <v>20000</v>
       </c>
       <c r="K557">
         <v>20000</v>
@@ -28757,10 +28760,10 @@
         <v>21</v>
       </c>
       <c r="I558">
-        <v>12300</v>
+        <v>42000</v>
       </c>
       <c r="J558">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K558">
         <v>21000</v>
@@ -28792,19 +28795,19 @@
         <v>15000</v>
       </c>
       <c r="G559">
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="H559">
         <v>21</v>
       </c>
       <c r="I559">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="J559">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="K559">
-        <v>22500</v>
+        <v>23000</v>
       </c>
       <c r="L559">
         <v>1</v>
@@ -28833,16 +28836,16 @@
         <v>14914.49</v>
       </c>
       <c r="G560">
-        <v>38000</v>
+        <v>4500</v>
       </c>
       <c r="H560">
         <v>21</v>
       </c>
       <c r="I560">
-        <v>14914.5</v>
+        <v>45000</v>
       </c>
       <c r="J560">
-        <v>14914.5</v>
+        <v>22000</v>
       </c>
       <c r="K560">
         <v>22000</v>
@@ -28880,10 +28883,10 @@
         <v>21</v>
       </c>
       <c r="I561">
-        <v>8183</v>
+        <v>40000</v>
       </c>
       <c r="J561">
-        <v>16586.900000000001</v>
+        <v>18000</v>
       </c>
       <c r="K561">
         <v>18000</v>
@@ -28924,10 +28927,10 @@
         <v>21</v>
       </c>
       <c r="I562">
-        <v>14350</v>
+        <v>50000</v>
       </c>
       <c r="J562">
-        <v>24219.9</v>
+        <v>24500</v>
       </c>
       <c r="K562">
         <v>24500</v>
@@ -28962,16 +28965,16 @@
         <v>14508</v>
       </c>
       <c r="G563">
-        <v>42000</v>
+        <v>50000</v>
       </c>
       <c r="H563">
         <v>21</v>
       </c>
       <c r="I563">
-        <v>14508</v>
+        <v>50000</v>
       </c>
       <c r="J563">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="K563">
         <v>25000</v>
@@ -29012,10 +29015,10 @@
         <v>21</v>
       </c>
       <c r="I564">
-        <v>13600</v>
+        <v>48000</v>
       </c>
       <c r="J564">
-        <v>13600</v>
+        <v>24000</v>
       </c>
       <c r="K564">
         <v>24000</v>
@@ -29056,7 +29059,7 @@
         <v>21</v>
       </c>
       <c r="I565">
-        <v>13050</v>
+        <v>45000</v>
       </c>
       <c r="J565">
         <v>23000</v>
@@ -29144,13 +29147,13 @@
         <v>21</v>
       </c>
       <c r="I567">
-        <v>13600</v>
+        <v>48000</v>
       </c>
       <c r="J567">
-        <v>13600</v>
+        <v>23000</v>
       </c>
       <c r="K567">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="L567">
         <v>6</v>
@@ -29188,10 +29191,10 @@
         <v>21</v>
       </c>
       <c r="I568">
-        <v>16500</v>
+        <v>55000</v>
       </c>
       <c r="J568">
-        <v>29558.1</v>
+        <v>26000</v>
       </c>
       <c r="K568">
         <v>26000</v>
@@ -29232,10 +29235,10 @@
         <v>21</v>
       </c>
       <c r="I569">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="J569">
-        <v>28673.599999999999</v>
+        <v>25000</v>
       </c>
       <c r="K569">
         <v>25000</v>
@@ -29276,10 +29279,10 @@
         <v>21</v>
       </c>
       <c r="I570">
-        <v>13961.4</v>
+        <v>48000</v>
       </c>
       <c r="J570">
-        <v>13961.4</v>
+        <v>24000</v>
       </c>
       <c r="K570">
         <v>24000</v>
@@ -29320,10 +29323,10 @@
         <v>21</v>
       </c>
       <c r="I571">
-        <v>16162</v>
+        <v>55000</v>
       </c>
       <c r="J571">
-        <v>16162</v>
+        <v>26000</v>
       </c>
       <c r="K571">
         <v>26000</v>
@@ -29358,19 +29361,19 @@
         <v>15300</v>
       </c>
       <c r="G572">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H572">
         <v>21</v>
       </c>
       <c r="I572">
-        <v>15300</v>
+        <v>50000</v>
       </c>
       <c r="J572">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="K572">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="L572">
         <v>2</v>
@@ -29408,10 +29411,10 @@
         <v>21</v>
       </c>
       <c r="I573">
-        <v>14362</v>
+        <v>48000</v>
       </c>
       <c r="J573">
-        <v>14362</v>
+        <v>24000</v>
       </c>
       <c r="K573">
         <v>24000</v>
@@ -29452,10 +29455,10 @@
         <v>21</v>
       </c>
       <c r="I574">
-        <v>12740</v>
+        <v>48000</v>
       </c>
       <c r="J574">
-        <v>12740</v>
+        <v>22000</v>
       </c>
       <c r="K574">
         <v>22000</v>
@@ -29496,13 +29499,13 @@
         <v>21</v>
       </c>
       <c r="I575">
-        <v>20170</v>
+        <v>65000</v>
       </c>
       <c r="J575">
-        <v>20170</v>
+        <v>32000</v>
       </c>
       <c r="K575">
-        <v>20170</v>
+        <v>32000</v>
       </c>
       <c r="L575">
         <v>0</v>
@@ -29540,10 +29543,10 @@
         <v>21</v>
       </c>
       <c r="I576">
-        <v>12000</v>
+        <v>45000</v>
       </c>
       <c r="J576">
-        <v>12000</v>
+        <v>21000</v>
       </c>
       <c r="K576">
         <v>21000</v>
@@ -29584,10 +29587,10 @@
         <v>21</v>
       </c>
       <c r="I577">
-        <v>42420</v>
+        <v>105000</v>
       </c>
       <c r="J577">
-        <v>42420</v>
+        <v>63630</v>
       </c>
       <c r="K577">
         <v>63630</v>
@@ -29625,10 +29628,10 @@
         <v>21</v>
       </c>
       <c r="I578">
-        <v>24000</v>
+        <v>65000</v>
       </c>
       <c r="J578">
-        <v>24000</v>
+        <v>35000</v>
       </c>
       <c r="K578">
         <v>35000</v>
@@ -29669,10 +29672,10 @@
         <v>21</v>
       </c>
       <c r="I579">
-        <v>12200</v>
+        <v>45000</v>
       </c>
       <c r="J579">
-        <v>12200</v>
+        <v>21000</v>
       </c>
       <c r="K579">
         <v>21000</v>
@@ -29710,10 +29713,10 @@
         <v>21</v>
       </c>
       <c r="I580">
-        <v>13400</v>
+        <v>48000</v>
       </c>
       <c r="J580">
-        <v>13400</v>
+        <v>23000</v>
       </c>
       <c r="K580">
         <v>23000</v>
@@ -29754,10 +29757,10 @@
         <v>21</v>
       </c>
       <c r="I581">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="J581">
-        <v>16000</v>
+        <v>25000</v>
       </c>
       <c r="K581">
         <v>25000</v>
@@ -29842,10 +29845,10 @@
         <v>21</v>
       </c>
       <c r="I583">
-        <v>15704</v>
+        <v>55000</v>
       </c>
       <c r="J583">
-        <v>15704</v>
+        <v>26000</v>
       </c>
       <c r="K583">
         <v>26000</v>
@@ -29886,10 +29889,10 @@
         <v>21</v>
       </c>
       <c r="I584">
-        <v>11722</v>
+        <v>40000</v>
       </c>
       <c r="J584">
-        <v>11722</v>
+        <v>20000</v>
       </c>
       <c r="K584">
         <v>20000</v>
@@ -29974,10 +29977,10 @@
         <v>21</v>
       </c>
       <c r="I586">
-        <v>18000</v>
+        <v>58000</v>
       </c>
       <c r="J586">
-        <v>18000</v>
+        <v>28800</v>
       </c>
       <c r="K586">
         <v>28800</v>
@@ -30018,10 +30021,10 @@
         <v>21</v>
       </c>
       <c r="I587">
-        <v>16362</v>
+        <v>50000</v>
       </c>
       <c r="J587">
-        <v>16362</v>
+        <v>26000</v>
       </c>
       <c r="K587">
         <v>26000</v>
@@ -30062,10 +30065,10 @@
         <v>21</v>
       </c>
       <c r="I588">
-        <v>16240</v>
+        <v>55000</v>
       </c>
       <c r="J588">
-        <v>16240</v>
+        <v>26000</v>
       </c>
       <c r="K588">
         <v>26000</v>
@@ -30106,13 +30109,13 @@
         <v>21</v>
       </c>
       <c r="I589">
-        <v>18500</v>
+        <v>65000</v>
       </c>
       <c r="J589">
-        <v>18500</v>
+        <v>32000</v>
       </c>
       <c r="K589">
-        <v>31450</v>
+        <v>32000</v>
       </c>
       <c r="L589">
         <v>2</v>
@@ -30150,10 +30153,10 @@
         <v>21</v>
       </c>
       <c r="I590">
-        <v>20600</v>
+        <v>68000</v>
       </c>
       <c r="J590">
-        <v>20600</v>
+        <v>32960</v>
       </c>
       <c r="K590">
         <v>32960</v>
@@ -32272,16 +32275,16 @@
         <v>1460</v>
       </c>
       <c r="G640">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="H640">
         <v>21</v>
       </c>
       <c r="I640">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="J640">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="K640">
         <v>1460</v>
@@ -33640,10 +33643,10 @@
         <v>21</v>
       </c>
       <c r="I673">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="J673">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K673">
         <v>10000</v>
@@ -33684,10 +33687,10 @@
         <v>21</v>
       </c>
       <c r="I674">
-        <v>3610.5</v>
+        <v>25000</v>
       </c>
       <c r="J674">
-        <v>3610.5</v>
+        <v>120000</v>
       </c>
       <c r="K674">
         <v>12000</v>
@@ -33766,19 +33769,19 @@
         <v>2600</v>
       </c>
       <c r="G676">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H676">
         <v>21</v>
       </c>
       <c r="I676">
-        <v>2600</v>
+        <v>24000</v>
       </c>
       <c r="J676">
-        <v>2600</v>
+        <v>12000</v>
       </c>
       <c r="K676">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L676">
         <v>0</v>
@@ -33810,19 +33813,19 @@
         <v>2600</v>
       </c>
       <c r="G677">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H677">
         <v>21</v>
       </c>
       <c r="I677">
-        <v>2600</v>
+        <v>24000</v>
       </c>
       <c r="J677">
-        <v>2600</v>
+        <v>12000</v>
       </c>
       <c r="K677">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L677">
         <v>1</v>
@@ -33854,19 +33857,19 @@
         <v>2400</v>
       </c>
       <c r="G678">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H678">
         <v>21</v>
       </c>
       <c r="I678">
-        <v>2400</v>
+        <v>24000</v>
       </c>
       <c r="J678">
-        <v>2400</v>
+        <v>12000</v>
       </c>
       <c r="K678">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L678">
         <v>1</v>
@@ -33898,16 +33901,16 @@
         <v>2000</v>
       </c>
       <c r="G679">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H679">
         <v>21</v>
       </c>
       <c r="I679">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J679">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K679">
         <v>10000</v>
@@ -33942,19 +33945,19 @@
         <v>2300</v>
       </c>
       <c r="G680">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H680">
         <v>21</v>
       </c>
       <c r="I680">
-        <v>2300</v>
+        <v>22000</v>
       </c>
       <c r="J680">
-        <v>2300</v>
+        <v>10000</v>
       </c>
       <c r="K680">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="L680">
         <v>1</v>
@@ -33986,16 +33989,16 @@
         <v>2900</v>
       </c>
       <c r="G681">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H681">
         <v>21</v>
       </c>
       <c r="I681">
-        <v>2900</v>
+        <v>22000</v>
       </c>
       <c r="J681">
-        <v>2900</v>
+        <v>10000</v>
       </c>
       <c r="K681">
         <v>10000</v>
@@ -34030,19 +34033,19 @@
         <v>2000</v>
       </c>
       <c r="G682">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H682">
         <v>21</v>
       </c>
       <c r="I682">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="J682">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K682">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="L682">
         <v>1</v>
@@ -34080,10 +34083,10 @@
         <v>21</v>
       </c>
       <c r="I683">
-        <v>2600</v>
+        <v>22000</v>
       </c>
       <c r="J683">
-        <v>2600</v>
+        <v>10000</v>
       </c>
       <c r="K683">
         <v>10000</v>
@@ -34124,10 +34127,10 @@
         <v>21</v>
       </c>
       <c r="I684">
-        <v>1800</v>
+        <v>22000</v>
       </c>
       <c r="J684">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="K684">
         <v>10000</v>
@@ -34168,10 +34171,10 @@
         <v>21</v>
       </c>
       <c r="I685">
-        <v>2600</v>
+        <v>22000</v>
       </c>
       <c r="J685">
-        <v>2600</v>
+        <v>10000</v>
       </c>
       <c r="K685">
         <v>10000</v>
@@ -34206,19 +34209,19 @@
         <v>2500</v>
       </c>
       <c r="G686">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H686">
         <v>21</v>
       </c>
       <c r="I686">
-        <v>2500</v>
+        <v>24000</v>
       </c>
       <c r="J686">
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="K686">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L686">
         <v>2</v>
@@ -34250,19 +34253,19 @@
         <v>2000</v>
       </c>
       <c r="G687">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H687">
         <v>21</v>
       </c>
       <c r="I687">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J687">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="K687">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L687">
         <v>1</v>
@@ -34294,16 +34297,16 @@
         <v>2000</v>
       </c>
       <c r="G688">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H688">
         <v>21</v>
       </c>
       <c r="I688">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J688">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K688">
         <v>10000</v>
@@ -34344,10 +34347,10 @@
         <v>21</v>
       </c>
       <c r="I689">
-        <v>3800</v>
+        <v>22000</v>
       </c>
       <c r="J689">
-        <v>3800</v>
+        <v>10000</v>
       </c>
       <c r="K689">
         <v>10000</v>
@@ -34382,16 +34385,16 @@
         <v>2200</v>
       </c>
       <c r="G690">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H690">
         <v>21</v>
       </c>
       <c r="I690">
-        <v>2200</v>
+        <v>24000</v>
       </c>
       <c r="J690">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K690">
         <v>10000</v>
@@ -34426,19 +34429,19 @@
         <v>2200</v>
       </c>
       <c r="G691">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H691">
         <v>21</v>
       </c>
       <c r="I691">
-        <v>2200</v>
+        <v>24000</v>
       </c>
       <c r="J691">
-        <v>2200</v>
+        <v>12000</v>
       </c>
       <c r="K691">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L691">
         <v>0</v>
@@ -34476,10 +34479,10 @@
         <v>21</v>
       </c>
       <c r="I692">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="J692">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K692">
         <v>10000</v>
@@ -34520,10 +34523,10 @@
         <v>21</v>
       </c>
       <c r="I693">
-        <v>3277</v>
+        <v>25000</v>
       </c>
       <c r="J693">
-        <v>3277</v>
+        <v>12000</v>
       </c>
       <c r="K693">
         <v>12000</v>
@@ -34558,16 +34561,16 @@
         <v>2300</v>
       </c>
       <c r="G694">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H694">
         <v>21</v>
       </c>
       <c r="I694">
-        <v>2300</v>
+        <v>24000</v>
       </c>
       <c r="J694">
-        <v>2300</v>
+        <v>10000</v>
       </c>
       <c r="K694">
         <v>10000</v>
@@ -34608,10 +34611,10 @@
         <v>21</v>
       </c>
       <c r="I695">
-        <v>3132</v>
+        <v>25000</v>
       </c>
       <c r="J695">
-        <v>3132</v>
+        <v>12000</v>
       </c>
       <c r="K695">
         <v>12000</v>
@@ -34649,10 +34652,10 @@
         <v>21</v>
       </c>
       <c r="I696">
-        <v>4988</v>
+        <v>25000</v>
       </c>
       <c r="J696">
-        <v>4988</v>
+        <v>14000</v>
       </c>
       <c r="K696">
         <v>14000</v>
@@ -34693,10 +34696,10 @@
         <v>21</v>
       </c>
       <c r="I697">
-        <v>2200</v>
+        <v>22000</v>
       </c>
       <c r="J697">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K697">
         <v>10000</v>
@@ -34737,10 +34740,10 @@
         <v>21</v>
       </c>
       <c r="I698">
-        <v>2900</v>
+        <v>22000</v>
       </c>
       <c r="J698">
-        <v>2900</v>
+        <v>10000</v>
       </c>
       <c r="K698">
         <v>10000</v>
@@ -34781,10 +34784,10 @@
         <v>21</v>
       </c>
       <c r="I699">
-        <v>2200</v>
+        <v>22000</v>
       </c>
       <c r="J699">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K699">
         <v>10000</v>
@@ -34825,10 +34828,10 @@
         <v>21</v>
       </c>
       <c r="I700">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="J700">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="K700">
         <v>10000</v>
@@ -34869,10 +34872,10 @@
         <v>21</v>
       </c>
       <c r="I701">
-        <v>2200</v>
+        <v>22000</v>
       </c>
       <c r="J701">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K701">
         <v>10000</v>
@@ -34907,16 +34910,16 @@
         <v>2711</v>
       </c>
       <c r="G702">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H702">
         <v>21</v>
       </c>
       <c r="I702">
-        <v>2711</v>
+        <v>22000</v>
       </c>
       <c r="J702">
-        <v>2711</v>
+        <v>10000</v>
       </c>
       <c r="K702">
         <v>10000</v>
@@ -34957,10 +34960,10 @@
         <v>21</v>
       </c>
       <c r="I703">
-        <v>2200</v>
+        <v>22000</v>
       </c>
       <c r="J703">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K703">
         <v>10000</v>
@@ -34995,16 +34998,16 @@
         <v>2000</v>
       </c>
       <c r="G704">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H704">
         <v>21</v>
       </c>
       <c r="I704">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J704">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K704">
         <v>10000</v>
@@ -35045,10 +35048,10 @@
         <v>21</v>
       </c>
       <c r="I705">
-        <v>2900</v>
+        <v>25000</v>
       </c>
       <c r="J705">
-        <v>2900</v>
+        <v>12000</v>
       </c>
       <c r="K705">
         <v>12000</v>
@@ -35089,10 +35092,10 @@
         <v>21</v>
       </c>
       <c r="I706">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="J706">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K706">
         <v>10000</v>
@@ -35127,16 +35130,16 @@
         <v>1800</v>
       </c>
       <c r="G707">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H707">
         <v>21</v>
       </c>
       <c r="I707">
-        <v>1800</v>
+        <v>24000</v>
       </c>
       <c r="J707">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="K707">
         <v>10000</v>
@@ -35177,13 +35180,13 @@
         <v>21</v>
       </c>
       <c r="I708">
-        <v>2813</v>
+        <v>25000</v>
       </c>
       <c r="J708">
-        <v>2813</v>
+        <v>12000</v>
       </c>
       <c r="K708">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L708">
         <v>5</v>
@@ -35215,19 +35218,19 @@
         <v>1900</v>
       </c>
       <c r="G709">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H709">
         <v>21</v>
       </c>
       <c r="I709">
-        <v>1900</v>
+        <v>24000</v>
       </c>
       <c r="J709">
-        <v>1900</v>
+        <v>12000</v>
       </c>
       <c r="K709">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L709">
         <v>3</v>
@@ -35259,16 +35262,16 @@
         <v>2000</v>
       </c>
       <c r="G710">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H710">
         <v>21</v>
       </c>
       <c r="I710">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J710">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K710">
         <v>10000</v>
@@ -35303,16 +35306,16 @@
         <v>2200</v>
       </c>
       <c r="G711">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H711">
         <v>21</v>
       </c>
       <c r="I711">
-        <v>2200</v>
+        <v>24000</v>
       </c>
       <c r="J711">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K711">
         <v>10000</v>
@@ -35353,10 +35356,10 @@
         <v>21</v>
       </c>
       <c r="I712">
-        <v>2900</v>
+        <v>24000</v>
       </c>
       <c r="J712">
-        <v>2900</v>
+        <v>10000</v>
       </c>
       <c r="K712">
         <v>10000</v>
@@ -35391,16 +35394,16 @@
         <v>2200</v>
       </c>
       <c r="G713">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H713">
         <v>21</v>
       </c>
       <c r="I713">
-        <v>2200</v>
+        <v>24000</v>
       </c>
       <c r="J713">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="K713">
         <v>10000</v>
@@ -35435,19 +35438,19 @@
         <v>2600</v>
       </c>
       <c r="G714">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H714">
         <v>21</v>
       </c>
       <c r="I714">
-        <v>2600</v>
+        <v>24000</v>
       </c>
       <c r="J714">
-        <v>2600</v>
+        <v>12000</v>
       </c>
       <c r="K714">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L714">
         <v>1</v>
@@ -35476,16 +35479,16 @@
         <v>3000</v>
       </c>
       <c r="G715">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H715">
         <v>21</v>
       </c>
       <c r="I715">
-        <v>3000</v>
+        <v>24000</v>
       </c>
       <c r="J715">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="K715">
         <v>12000</v>
@@ -35520,16 +35523,16 @@
         <v>2000</v>
       </c>
       <c r="G716">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H716">
         <v>21</v>
       </c>
       <c r="I716">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J716">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K716">
         <v>10000</v>
@@ -35564,16 +35567,16 @@
         <v>2000</v>
       </c>
       <c r="G717">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H717">
         <v>21</v>
       </c>
       <c r="I717">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="J717">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K717">
         <v>10000</v>
@@ -35652,19 +35655,19 @@
         <v>3200</v>
       </c>
       <c r="G719">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H719">
         <v>21</v>
       </c>
       <c r="I719">
-        <v>3200</v>
+        <v>24000</v>
       </c>
       <c r="J719">
-        <v>3200</v>
+        <v>12000</v>
       </c>
       <c r="K719">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L719">
         <v>2</v>
@@ -35702,10 +35705,10 @@
         <v>21</v>
       </c>
       <c r="I720">
-        <v>3550</v>
+        <v>24000</v>
       </c>
       <c r="J720">
-        <v>3550</v>
+        <v>12000</v>
       </c>
       <c r="K720">
         <v>12000</v>
@@ -35746,10 +35749,10 @@
         <v>21</v>
       </c>
       <c r="I721">
-        <v>2400</v>
+        <v>22000</v>
       </c>
       <c r="J721">
-        <v>2400</v>
+        <v>10000</v>
       </c>
       <c r="K721">
         <v>10000</v>
@@ -35790,10 +35793,10 @@
         <v>21</v>
       </c>
       <c r="I722">
-        <v>1800</v>
+        <v>22000</v>
       </c>
       <c r="J722">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="K722">
         <v>10000</v>
@@ -35828,16 +35831,16 @@
         <v>2400</v>
       </c>
       <c r="G723">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H723">
         <v>21</v>
       </c>
       <c r="I723">
-        <v>2400</v>
+        <v>24000</v>
       </c>
       <c r="J723">
-        <v>2400</v>
+        <v>10000</v>
       </c>
       <c r="K723">
         <v>10000</v>
@@ -35872,16 +35875,16 @@
         <v>2000</v>
       </c>
       <c r="G724">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H724">
         <v>21</v>
       </c>
       <c r="I724">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J724">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K724">
         <v>10000</v>
@@ -35922,10 +35925,10 @@
         <v>21</v>
       </c>
       <c r="I725">
-        <v>7857</v>
+        <v>26000</v>
       </c>
       <c r="J725">
-        <v>7857</v>
+        <v>14000</v>
       </c>
       <c r="K725">
         <v>14000</v>
@@ -35960,16 +35963,16 @@
         <v>2000</v>
       </c>
       <c r="G726">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H726">
         <v>21</v>
       </c>
       <c r="I726">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J726">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K726">
         <v>10000</v>
@@ -36004,16 +36007,16 @@
         <v>2000</v>
       </c>
       <c r="G727">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H727">
         <v>21</v>
       </c>
       <c r="I727">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J727">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K727">
         <v>10000</v>
@@ -36048,16 +36051,16 @@
         <v>2000</v>
       </c>
       <c r="G728">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H728">
         <v>21</v>
       </c>
       <c r="I728">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J728">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K728">
         <v>10000</v>
@@ -36098,10 +36101,10 @@
         <v>21</v>
       </c>
       <c r="I729">
-        <v>3436.5</v>
+        <v>25000</v>
       </c>
       <c r="J729">
-        <v>3436.5</v>
+        <v>12000</v>
       </c>
       <c r="K729">
         <v>12000</v>
@@ -36136,19 +36139,19 @@
         <v>2400</v>
       </c>
       <c r="G730">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H730">
         <v>21</v>
       </c>
       <c r="I730">
-        <v>2400</v>
+        <v>24000</v>
       </c>
       <c r="J730">
-        <v>2400</v>
+        <v>12000</v>
       </c>
       <c r="K730">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L730">
         <v>1</v>
@@ -36224,19 +36227,19 @@
         <v>2500</v>
       </c>
       <c r="G732">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="H732">
         <v>21</v>
       </c>
       <c r="I732">
-        <v>2500</v>
+        <v>25000</v>
       </c>
       <c r="J732">
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="K732">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L732">
         <v>2</v>
@@ -36268,19 +36271,19 @@
         <v>2200</v>
       </c>
       <c r="G733">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H733">
         <v>21</v>
       </c>
       <c r="I733">
-        <v>2200</v>
+        <v>24000</v>
       </c>
       <c r="J733">
-        <v>2200</v>
+        <v>12000</v>
       </c>
       <c r="K733">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L733">
         <v>2</v>
@@ -36309,16 +36312,16 @@
         <v>650</v>
       </c>
       <c r="G734">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H734">
         <v>21</v>
       </c>
       <c r="I734">
-        <v>650</v>
+        <v>6000</v>
       </c>
       <c r="J734">
-        <v>650</v>
+        <v>6000</v>
       </c>
       <c r="K734">
         <v>650</v>
@@ -37906,22 +37909,22 @@
         <v>7800</v>
       </c>
       <c r="G772">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="H772">
         <v>21</v>
       </c>
       <c r="I772">
-        <v>7800</v>
+        <v>18000</v>
       </c>
       <c r="J772">
-        <v>7800</v>
+        <v>18000</v>
       </c>
       <c r="K772">
         <v>7800</v>
       </c>
       <c r="L772">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M772">
         <v>0</v>
@@ -37976,7 +37979,7 @@
         <v>7798347600801</v>
       </c>
       <c r="B774" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C774" t="s">
         <v>306</v>
@@ -37994,10 +37997,10 @@
         <v>21</v>
       </c>
       <c r="I774">
-        <v>5000</v>
+        <v>12500</v>
       </c>
       <c r="J774">
-        <v>5000</v>
+        <v>12500</v>
       </c>
       <c r="K774">
         <v>5000</v>
@@ -38014,10 +38017,10 @@
     </row>
     <row r="775" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B775" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C775" t="s">
         <v>516</v>
@@ -38055,10 +38058,10 @@
     </row>
     <row r="776" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B776" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C776" t="s">
         <v>421</v>
@@ -38099,7 +38102,7 @@
         <v>7798145004559</v>
       </c>
       <c r="B777" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C777" t="s">
         <v>303</v>
@@ -38137,10 +38140,10 @@
     </row>
     <row r="778" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B778" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C778" t="s">
         <v>38</v>
@@ -38178,10 +38181,10 @@
     </row>
     <row r="779" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B779" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C779" t="s">
         <v>38</v>
@@ -38219,10 +38222,10 @@
     </row>
     <row r="780" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B780" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C780" t="s">
         <v>421</v>
@@ -38263,7 +38266,7 @@
         <v>6904004020214</v>
       </c>
       <c r="B781" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C781" t="s">
         <v>58</v>
@@ -38275,16 +38278,16 @@
         <v>16300</v>
       </c>
       <c r="G781">
-        <v>37999</v>
+        <v>38000</v>
       </c>
       <c r="H781">
         <v>21</v>
       </c>
       <c r="I781">
-        <v>16300</v>
+        <v>38000</v>
       </c>
       <c r="J781">
-        <v>16300</v>
+        <v>38000</v>
       </c>
       <c r="K781">
         <v>16300</v>
@@ -38301,10 +38304,10 @@
     </row>
     <row r="782" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B782" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C782" t="s">
         <v>58</v>
@@ -38348,7 +38351,7 @@
         <v>6972831212331</v>
       </c>
       <c r="B783" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C783" t="s">
         <v>303</v>
@@ -38389,10 +38392,10 @@
     </row>
     <row r="784" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B784" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C784" t="s">
         <v>303</v>
@@ -38436,7 +38439,7 @@
         <v>723540564824</v>
       </c>
       <c r="B785" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C785" t="s">
         <v>306</v>
@@ -38477,7 +38480,7 @@
         <v>6958210712401</v>
       </c>
       <c r="B786" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C786" t="s">
         <v>303</v>
@@ -38521,7 +38524,7 @@
         <v>6963490162686</v>
       </c>
       <c r="B787" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C787" t="s">
         <v>303</v>
@@ -38562,7 +38565,7 @@
         <v>6955549333260</v>
       </c>
       <c r="B788" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C788" t="s">
         <v>303</v>
@@ -38571,7 +38574,7 @@
         <v>49</v>
       </c>
       <c r="E788" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="F788">
         <v>10500</v>
@@ -38606,7 +38609,7 @@
         <v>6958210701405</v>
       </c>
       <c r="B789" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C789" t="s">
         <v>303</v>
@@ -38650,7 +38653,7 @@
         <v>8201756735006</v>
       </c>
       <c r="B790" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C790" t="s">
         <v>433</v>
@@ -38694,7 +38697,7 @@
         <v>763571815083</v>
       </c>
       <c r="B791" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C791" t="s">
         <v>77</v>
@@ -38735,7 +38738,7 @@
         <v>8214729653849</v>
       </c>
       <c r="B792" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C792" t="s">
         <v>77</v>
@@ -38773,10 +38776,10 @@
     </row>
     <row r="793" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B793" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C793" t="s">
         <v>77</v>
@@ -38817,7 +38820,7 @@
         <v>5901234123457</v>
       </c>
       <c r="B794" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C794" t="s">
         <v>64</v>
@@ -38858,7 +38861,7 @@
         <v>723540564831</v>
       </c>
       <c r="B795" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C795" t="s">
         <v>64</v>
@@ -38867,7 +38870,7 @@
         <v>31</v>
       </c>
       <c r="E795" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="F795">
         <v>21500</v>
@@ -38902,7 +38905,7 @@
         <v>7799135013018</v>
       </c>
       <c r="B796" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C796" t="s">
         <v>64</v>
@@ -38946,7 +38949,7 @@
         <v>6988886869543</v>
       </c>
       <c r="B797" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C797" t="s">
         <v>74</v>
@@ -38984,10 +38987,10 @@
     </row>
     <row r="798" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B798" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C798" t="s">
         <v>74</v>
@@ -39025,10 +39028,10 @@
     </row>
     <row r="799" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B799" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C799" t="s">
         <v>74</v>
@@ -39066,10 +39069,10 @@
     </row>
     <row r="800" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B800" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C800" t="s">
         <v>74</v>
@@ -39107,10 +39110,10 @@
     </row>
     <row r="801" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B801" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C801" t="s">
         <v>74</v>
@@ -39148,10 +39151,10 @@
     </row>
     <row r="802" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B802" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C802" t="s">
         <v>74</v>
@@ -39192,7 +39195,7 @@
         <v>7821234522365</v>
       </c>
       <c r="B803" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="C803" t="s">
         <v>74</v>
@@ -39230,10 +39233,10 @@
     </row>
     <row r="804" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B804" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C804" t="s">
         <v>74</v>
@@ -39271,10 +39274,10 @@
     </row>
     <row r="805" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B805" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C805" t="s">
         <v>74</v>
@@ -39312,10 +39315,10 @@
     </row>
     <row r="806" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B806" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C806" t="s">
         <v>74</v>
@@ -39356,10 +39359,10 @@
     </row>
     <row r="807" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B807" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C807" t="s">
         <v>74</v>
@@ -39400,7 +39403,7 @@
         <v>7798145005969</v>
       </c>
       <c r="B808" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C808" t="s">
         <v>74</v>
@@ -39441,7 +39444,7 @@
         <v>723540565012</v>
       </c>
       <c r="B809" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C809" t="s">
         <v>64</v>
@@ -39450,22 +39453,22 @@
         <v>31</v>
       </c>
       <c r="F809">
-        <v>2350</v>
+        <v>2129</v>
       </c>
       <c r="G809">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H809">
         <v>21</v>
       </c>
       <c r="I809">
-        <v>10000</v>
+        <v>9059.5</v>
       </c>
       <c r="J809">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="K809">
-        <v>2350</v>
+        <v>2129</v>
       </c>
       <c r="L809">
         <v>5</v>
@@ -39482,7 +39485,7 @@
         <v>7799135001664</v>
       </c>
       <c r="B810" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C810" t="s">
         <v>64</v>
@@ -39526,7 +39529,7 @@
         <v>7798423540649</v>
       </c>
       <c r="B811" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C811" t="s">
         <v>64</v>
@@ -39567,7 +39570,7 @@
         <v>6974504501018</v>
       </c>
       <c r="B812" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C812" t="s">
         <v>64</v>
@@ -39605,10 +39608,10 @@
     </row>
     <row r="813" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B813" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D813" t="s">
         <v>31</v>
@@ -39646,7 +39649,7 @@
         <v>843367116218</v>
       </c>
       <c r="B814" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C814" t="s">
         <v>722</v>
@@ -39655,7 +39658,7 @@
         <v>359</v>
       </c>
       <c r="E814" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="F814">
         <v>18444</v>
@@ -39690,7 +39693,7 @@
         <v>7448070134219</v>
       </c>
       <c r="B815" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C815" t="s">
         <v>722</v>
@@ -39699,7 +39702,7 @@
         <v>359</v>
       </c>
       <c r="E815" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="F815">
         <v>17600</v>
@@ -39731,10 +39734,10 @@
     </row>
     <row r="816" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B816" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C816" t="s">
         <v>38</v>
@@ -39772,10 +39775,10 @@
     </row>
     <row r="817" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B817" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C817" t="s">
         <v>38</v>
@@ -39813,10 +39816,10 @@
     </row>
     <row r="818" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B818" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C818" t="s">
         <v>418</v>
@@ -39857,10 +39860,10 @@
     </row>
     <row r="819" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B819" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C819" t="s">
         <v>506</v>
@@ -39898,16 +39901,16 @@
     </row>
     <row r="820" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B820" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C820" t="s">
         <v>516</v>
       </c>
       <c r="E820" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="F820">
         <v>1000</v>
@@ -39928,7 +39931,7 @@
         <v>1000</v>
       </c>
       <c r="L820">
-        <v>-0.5</v>
+        <v>-2.2000000476837198</v>
       </c>
       <c r="M820">
         <v>0</v>
@@ -39942,7 +39945,7 @@
         <v>7799135009790</v>
       </c>
       <c r="B821" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C821" t="s">
         <v>433</v>
@@ -39983,7 +39986,7 @@
         <v>700306601221</v>
       </c>
       <c r="B822" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C822" t="s">
         <v>433</v>
@@ -40021,10 +40024,10 @@
     </row>
     <row r="823" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B823" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="C823" t="s">
         <v>1130</v>
@@ -40062,10 +40065,10 @@
     </row>
     <row r="824" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B824" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C824" t="s">
         <v>58</v>
@@ -40103,10 +40106,10 @@
     </row>
     <row r="825" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B825" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C825" t="s">
         <v>421</v>
@@ -40147,7 +40150,7 @@
         <v>7798423541356</v>
       </c>
       <c r="B826" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C826" t="s">
         <v>77</v>
@@ -40188,7 +40191,7 @@
         <v>7798145006027</v>
       </c>
       <c r="B827" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C827" t="s">
         <v>506</v>
@@ -40229,7 +40232,7 @@
         <v>69855646885262</v>
       </c>
       <c r="B828" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C828" t="s">
         <v>506</v>
@@ -40238,7 +40241,7 @@
         <v>31</v>
       </c>
       <c r="E828" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F828">
         <v>2629</v>
@@ -40273,7 +40276,7 @@
         <v>6985564688526</v>
       </c>
       <c r="B829" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C829" t="s">
         <v>506</v>
@@ -40282,7 +40285,7 @@
         <v>31</v>
       </c>
       <c r="E829" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F829">
         <v>2629</v>
@@ -40317,7 +40320,7 @@
         <v>7790000111020</v>
       </c>
       <c r="B830" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C830" t="s">
         <v>421</v>
@@ -40358,7 +40361,7 @@
         <v>6920220096888</v>
       </c>
       <c r="B831" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C831" t="s">
         <v>53</v>
@@ -40396,10 +40399,10 @@
     </row>
     <row r="832" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B832" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C832" t="s">
         <v>67</v>
@@ -40420,7 +40423,7 @@
         <v>9000</v>
       </c>
       <c r="J832">
-        <v>9000</v>
+        <v>5800</v>
       </c>
       <c r="K832">
         <v>3615</v>
@@ -40440,7 +40443,7 @@
         <v>7795234526572</v>
       </c>
       <c r="B833" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C833" t="s">
         <v>67</v>
@@ -40449,7 +40452,7 @@
         <v>31</v>
       </c>
       <c r="F833">
-        <v>4900</v>
+        <v>4126</v>
       </c>
       <c r="G833">
         <v>12000</v>
@@ -40458,13 +40461,13 @@
         <v>21</v>
       </c>
       <c r="I833">
-        <v>4900</v>
+        <v>12000</v>
       </c>
       <c r="J833">
-        <v>4900</v>
+        <v>6200</v>
       </c>
       <c r="K833">
-        <v>4900</v>
+        <v>4126</v>
       </c>
       <c r="L833">
         <v>6</v>
@@ -40478,10 +40481,10 @@
     </row>
     <row r="834" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B834" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C834" t="s">
         <v>67</v>
@@ -40490,7 +40493,7 @@
         <v>31</v>
       </c>
       <c r="F834">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="G834">
         <v>18000</v>
@@ -40499,13 +40502,13 @@
         <v>21</v>
       </c>
       <c r="I834">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="J834">
-        <v>7000</v>
+        <v>9600</v>
       </c>
       <c r="K834">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="L834">
         <v>3</v>
@@ -40519,10 +40522,10 @@
     </row>
     <row r="835" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B835" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C835" t="s">
         <v>67</v>
@@ -40543,13 +40546,13 @@
         <v>26000</v>
       </c>
       <c r="J835">
-        <v>26000</v>
+        <v>12000</v>
       </c>
       <c r="K835">
         <v>7245</v>
       </c>
       <c r="L835">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M835">
         <v>0</v>
@@ -40560,10 +40563,10 @@
     </row>
     <row r="836" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B836" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C836" t="s">
         <v>306</v>
@@ -40601,10 +40604,10 @@
     </row>
     <row r="837" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B837" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C837" t="s">
         <v>306</v>
@@ -40616,16 +40619,16 @@
         <v>6815</v>
       </c>
       <c r="G837">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H837">
         <v>21</v>
       </c>
       <c r="I837">
-        <v>6815</v>
+        <v>20000</v>
       </c>
       <c r="J837">
-        <v>6815</v>
+        <v>20000</v>
       </c>
       <c r="K837">
         <v>6815</v>
@@ -40645,7 +40648,7 @@
         <v>6902540752361</v>
       </c>
       <c r="B838" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C838" t="s">
         <v>306</v>
@@ -40657,16 +40660,16 @@
         <v>5800</v>
       </c>
       <c r="G838">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H838">
         <v>21</v>
       </c>
       <c r="I838">
-        <v>5800</v>
+        <v>15000</v>
       </c>
       <c r="J838">
-        <v>5800</v>
+        <v>15000</v>
       </c>
       <c r="K838">
         <v>5800</v>
@@ -40683,10 +40686,10 @@
     </row>
     <row r="839" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B839" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C839" t="s">
         <v>58</v>
@@ -40727,7 +40730,7 @@
         <v>723540564022</v>
       </c>
       <c r="B840" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C840" t="s">
         <v>461</v>
@@ -40768,10 +40771,10 @@
     </row>
     <row r="841" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B841" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C841" t="s">
         <v>461</v>
@@ -40809,10 +40812,10 @@
     </row>
     <row r="842" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B842" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="C842" t="s">
         <v>596</v>
@@ -40850,10 +40853,10 @@
     </row>
     <row r="843" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B843" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C843" t="s">
         <v>596</v>
@@ -40894,7 +40897,7 @@
         <v>7798347810224</v>
       </c>
       <c r="B844" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="C844" t="s">
         <v>596</v>
@@ -40903,7 +40906,7 @@
         <v>49</v>
       </c>
       <c r="E844" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F844">
         <v>3260</v>
@@ -40938,7 +40941,7 @@
         <v>7798347810569</v>
       </c>
       <c r="B845" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="C845" t="s">
         <v>596</v>
@@ -40947,7 +40950,7 @@
         <v>49</v>
       </c>
       <c r="E845" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F845">
         <v>3261</v>
@@ -40982,7 +40985,7 @@
         <v>6905416583656</v>
       </c>
       <c r="B846" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C846" t="s">
         <v>421</v>
@@ -41017,10 +41020,10 @@
     </row>
     <row r="847" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B847" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C847" t="s">
         <v>77</v>
@@ -41058,10 +41061,10 @@
     </row>
     <row r="848" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B848" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="C848" t="s">
         <v>67</v>
@@ -41102,7 +41105,7 @@
         <v>6459751458518</v>
       </c>
       <c r="B849" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C849" t="s">
         <v>74</v>
@@ -41140,10 +41143,10 @@
     </row>
     <row r="850" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B850" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C850" t="s">
         <v>74</v>
@@ -41152,7 +41155,7 @@
         <v>31</v>
       </c>
       <c r="E850" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F850">
         <v>5887</v>
@@ -41184,10 +41187,10 @@
     </row>
     <row r="851" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B851" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="C851" t="s">
         <v>74</v>
@@ -41228,10 +41231,10 @@
     </row>
     <row r="852" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B852" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C852" t="s">
         <v>38</v>
@@ -41272,7 +41275,7 @@
         <v>6989526542239</v>
       </c>
       <c r="B853" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C853" t="s">
         <v>74</v>
@@ -41310,10 +41313,10 @@
     </row>
     <row r="854" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B854" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="C854" t="s">
         <v>299</v>
@@ -41351,10 +41354,10 @@
     </row>
     <row r="855" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B855" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C855" t="s">
         <v>299</v>
@@ -41392,10 +41395,10 @@
     </row>
     <row r="856" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B856" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C856" t="s">
         <v>299</v>
@@ -41436,7 +41439,7 @@
         <v>153500580</v>
       </c>
       <c r="B857" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C857" t="s">
         <v>67</v>
@@ -41474,10 +41477,10 @@
     </row>
     <row r="858" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B858" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C858" t="s">
         <v>67</v>
@@ -41515,10 +41518,10 @@
     </row>
     <row r="859" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B859" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C859" t="s">
         <v>67</v>
@@ -41556,10 +41559,10 @@
     </row>
     <row r="860" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B860" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C860" t="s">
         <v>67</v>
@@ -41603,7 +41606,7 @@
         <v>723540563780</v>
       </c>
       <c r="B861" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C861" t="s">
         <v>67</v>
@@ -41644,10 +41647,10 @@
     </row>
     <row r="862" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B862" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="C862" t="s">
         <v>67</v>
@@ -41688,7 +41691,7 @@
         <v>7769528971157</v>
       </c>
       <c r="B863" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C863" t="s">
         <v>67</v>
@@ -41726,10 +41729,10 @@
     </row>
     <row r="864" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B864" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C864" t="s">
         <v>67</v>
@@ -41770,10 +41773,10 @@
     </row>
     <row r="865" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B865" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="C865" t="s">
         <v>38</v>
@@ -41800,7 +41803,7 @@
         <v>500</v>
       </c>
       <c r="L865">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M865">
         <v>0</v>
@@ -41814,7 +41817,7 @@
         <v>701575361335</v>
       </c>
       <c r="B866" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="C866" t="s">
         <v>641</v>
@@ -41855,10 +41858,10 @@
     </row>
     <row r="867" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B867" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C867" t="s">
         <v>599</v>
@@ -41896,10 +41899,10 @@
     </row>
     <row r="868" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B868" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C868" t="s">
         <v>58</v>
@@ -41937,10 +41940,10 @@
     </row>
     <row r="869" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B869" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C869" t="s">
         <v>20</v>
@@ -41978,10 +41981,10 @@
     </row>
     <row r="870" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B870" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="C870" t="s">
         <v>20</v>
@@ -42008,7 +42011,7 @@
         <v>3613.6</v>
       </c>
       <c r="L870">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M870">
         <v>0</v>
@@ -42019,10 +42022,10 @@
     </row>
     <row r="871" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B871" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C871" t="s">
         <v>20</v>
@@ -42049,7 +42052,7 @@
         <v>4000</v>
       </c>
       <c r="L871">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M871">
         <v>0</v>
@@ -42060,10 +42063,10 @@
     </row>
     <row r="872" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B872" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C872" t="s">
         <v>20</v>
@@ -42072,7 +42075,7 @@
         <v>49</v>
       </c>
       <c r="E872" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F872">
         <v>4588</v>
@@ -42107,7 +42110,7 @@
         <v>7796941141133</v>
       </c>
       <c r="B873" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C873" t="s">
         <v>508</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911FE229-8046-4FBC-8FB7-91524BE71185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BB3132E-8F80-4200-91B1-EA04B6A4A61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B832782D-DF14-4080-911A-54E2E6E75704}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{067F0ED1-C248-4084-B20C-72AD974D0B32}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1590">
   <si>
     <t>CODIGO</t>
   </si>
@@ -320,7 +320,7 @@
     <t>CONEJO</t>
   </si>
   <si>
-    <t xml:space="preserve">AURICULAR BT CONEJO </t>
+    <t>AURICULAR BT CONEJO</t>
   </si>
   <si>
     <t>AURICULAR BT DEKKIN CB032 CELESTE</t>
@@ -1415,7 +1415,10 @@
     <t>CARGADOR CABEZAL TIPO C SAMSUNG 65W</t>
   </si>
   <si>
-    <t xml:space="preserve">CARGADOR DE NOTEBOOK C/FICHA LENOVO </t>
+    <t>CARGADOR DE NOTEBOOK C/FICHA LENOVO</t>
+  </si>
+  <si>
+    <t>CARGADORES Y CABLES USB &gt; UNIVERSAL</t>
   </si>
   <si>
     <t>CARGPILA</t>
@@ -1424,9 +1427,6 @@
     <t>CARGADOR DE PILA RECARGABLE</t>
   </si>
   <si>
-    <t>CARGADORES Y CABLES USB &gt; UNIVERSAL</t>
-  </si>
-  <si>
     <t>CARGADOR DE PILA USB</t>
   </si>
   <si>
@@ -2021,7 +2021,7 @@
     <t>Kit de Fusibles Automotor</t>
   </si>
   <si>
-    <t xml:space="preserve">LAMPARA LED RECARGABLE 52CM </t>
+    <t>LAMPARA LED RECARGABLE 52CM</t>
   </si>
   <si>
     <t>LAMPARA MINI 20 LED MAGNETICO RECARGABLE</t>
@@ -4418,7 +4418,7 @@
     <t>SMART TV BOX AITECH CON MAGIS TV</t>
   </si>
   <si>
-    <t xml:space="preserve">SMART TV BOX CON MAGIS TV 4K </t>
+    <t>SMART TV BOX CON MAGIS TV 4K</t>
   </si>
   <si>
     <t>NOVACENTER</t>
@@ -4499,13 +4499,16 @@
     <t>SOPORTE TV FIJO 26 A 63 PULGADAS</t>
   </si>
   <si>
+    <t>SOPORTE TV FIJO 32 A 55 PULGADAS HASTA 30 KG</t>
+  </si>
+  <si>
     <t>SOPORTE TV MOVIL 14 A 55 PULGADAS</t>
   </si>
   <si>
     <t>SOPORTREFORZ</t>
   </si>
   <si>
-    <t>SOPORTE TV REFORZADO MOVIL 32-65 PLG</t>
+    <t>SOPORTE TV MOVIL REFORZADO 32 A 65 PLG</t>
   </si>
   <si>
     <t>SSD DISCO SOLIDO 120 GB LEXAR</t>
@@ -5176,8 +5179,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B4DFA4-4840-4633-A54E-DC21D125F7E3}">
-  <dimension ref="A1:N873"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6633F7A3-0898-4B5A-8568-2C4E45181639}">
+  <dimension ref="A1:N874"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -6085,7 +6088,7 @@
         <v>10000</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -6986,6 +6989,9 @@
       <c r="B44" t="s">
         <v>93</v>
       </c>
+      <c r="C44" t="s">
+        <v>80</v>
+      </c>
       <c r="D44" t="s">
         <v>31</v>
       </c>
@@ -7140,7 +7146,7 @@
         <v>5090</v>
       </c>
       <c r="L47">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -9303,7 +9309,7 @@
         <v>4000</v>
       </c>
       <c r="L98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -9898,7 +9904,7 @@
         <v>18000</v>
       </c>
       <c r="L112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M112">
         <v>0</v>
@@ -10270,22 +10276,22 @@
         <v>8874</v>
       </c>
       <c r="G121">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H121">
         <v>21</v>
       </c>
       <c r="I121">
-        <v>8874</v>
+        <v>30000</v>
       </c>
       <c r="J121">
-        <v>8874</v>
+        <v>18000</v>
       </c>
       <c r="K121">
         <v>18000</v>
       </c>
       <c r="L121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M121">
         <v>0</v>
@@ -10320,10 +10326,10 @@
         <v>21</v>
       </c>
       <c r="I122">
-        <v>9454</v>
+        <v>30000</v>
       </c>
       <c r="J122">
-        <v>9454</v>
+        <v>18000</v>
       </c>
       <c r="K122">
         <v>18000</v>
@@ -10965,16 +10971,16 @@
         <v>9360</v>
       </c>
       <c r="G137">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H137">
         <v>21</v>
       </c>
       <c r="I137">
-        <v>9360</v>
+        <v>30000</v>
       </c>
       <c r="J137">
-        <v>9360</v>
+        <v>18000</v>
       </c>
       <c r="K137">
         <v>18000</v>
@@ -11358,7 +11364,7 @@
         <v>1389</v>
       </c>
       <c r="L146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -13693,7 +13699,7 @@
         <v>689</v>
       </c>
       <c r="L202">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M202">
         <v>0</v>
@@ -14103,22 +14109,22 @@
         <v>21</v>
       </c>
       <c r="I212">
-        <v>2085</v>
+        <v>7500</v>
       </c>
       <c r="J212">
-        <v>2352</v>
+        <v>7500</v>
       </c>
       <c r="K212">
         <v>2085</v>
       </c>
       <c r="L212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M212">
         <v>0</v>
       </c>
       <c r="N212">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
@@ -14153,7 +14159,7 @@
         <v>3034</v>
       </c>
       <c r="L213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M213">
         <v>0</v>
@@ -14836,7 +14842,7 @@
         <v>1365</v>
       </c>
       <c r="L229">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M229">
         <v>0</v>
@@ -15012,7 +15018,7 @@
         <v>1929</v>
       </c>
       <c r="L233">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M233">
         <v>0</v>
@@ -15170,7 +15176,7 @@
         <v>385</v>
       </c>
       <c r="F237">
-        <v>5418</v>
+        <v>5058</v>
       </c>
       <c r="G237">
         <v>18000</v>
@@ -15179,16 +15185,16 @@
         <v>21</v>
       </c>
       <c r="I237">
-        <v>5418</v>
+        <v>26000</v>
       </c>
       <c r="J237">
-        <v>5418</v>
+        <v>9000</v>
       </c>
       <c r="K237">
-        <v>5418</v>
+        <v>9000</v>
       </c>
       <c r="L237">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M237">
         <v>0</v>
@@ -15232,7 +15238,7 @@
         <v>3751</v>
       </c>
       <c r="L238">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M238">
         <v>0</v>
@@ -15424,6 +15430,12 @@
       <c r="B243" t="s">
         <v>458</v>
       </c>
+      <c r="C243" t="s">
+        <v>459</v>
+      </c>
+      <c r="D243" t="s">
+        <v>31</v>
+      </c>
       <c r="F243">
         <v>6885</v>
       </c>
@@ -15454,13 +15466,13 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>460</v>
+      </c>
+      <c r="B244" t="s">
+        <v>461</v>
+      </c>
+      <c r="C244" t="s">
         <v>459</v>
-      </c>
-      <c r="B244" t="s">
-        <v>460</v>
-      </c>
-      <c r="C244" t="s">
-        <v>461</v>
       </c>
       <c r="D244" t="s">
         <v>294</v>
@@ -15501,7 +15513,7 @@
         <v>462</v>
       </c>
       <c r="C245" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D245" t="s">
         <v>31</v>
@@ -16073,7 +16085,7 @@
         <v>477</v>
       </c>
       <c r="C258" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D258" t="s">
         <v>49</v>
@@ -16100,7 +16112,7 @@
         <v>4139.2</v>
       </c>
       <c r="L258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M258">
         <v>0</v>
@@ -16223,7 +16235,7 @@
         <v>7500</v>
       </c>
       <c r="L261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M261">
         <v>0</v>
@@ -16328,7 +16340,7 @@
         <v>487</v>
       </c>
       <c r="C264" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D264" t="s">
         <v>31</v>
@@ -16369,7 +16381,7 @@
         <v>489</v>
       </c>
       <c r="C265" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D265" t="s">
         <v>31</v>
@@ -16393,7 +16405,7 @@
         <v>2450</v>
       </c>
       <c r="L265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M265">
         <v>0</v>
@@ -16410,7 +16422,7 @@
         <v>491</v>
       </c>
       <c r="C266" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D266" t="s">
         <v>28</v>
@@ -16428,16 +16440,16 @@
         <v>21</v>
       </c>
       <c r="I266">
-        <v>1952</v>
+        <v>8000</v>
       </c>
       <c r="J266">
-        <v>1952</v>
+        <v>8000</v>
       </c>
       <c r="K266">
-        <v>1952</v>
+        <v>8000</v>
       </c>
       <c r="L266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M266">
         <v>0</v>
@@ -16454,7 +16466,7 @@
         <v>493</v>
       </c>
       <c r="C267" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D267" t="s">
         <v>31</v>
@@ -16495,7 +16507,7 @@
         <v>494</v>
       </c>
       <c r="C268" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D268" t="s">
         <v>31</v>
@@ -16536,7 +16548,7 @@
         <v>495</v>
       </c>
       <c r="C269" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D269" t="s">
         <v>24</v>
@@ -16580,7 +16592,7 @@
         <v>496</v>
       </c>
       <c r="C270" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D270" t="s">
         <v>24</v>
@@ -16689,7 +16701,7 @@
         <v>10000</v>
       </c>
       <c r="L272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -17480,7 +17492,7 @@
         <v>2500</v>
       </c>
       <c r="L291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M291">
         <v>0</v>
@@ -17606,7 +17618,7 @@
         <v>2700</v>
       </c>
       <c r="L294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M294">
         <v>0</v>
@@ -18236,7 +18248,7 @@
         <v>3225.8</v>
       </c>
       <c r="L309">
-        <v>-2</v>
+        <v>-16.700000762939499</v>
       </c>
       <c r="M309">
         <v>0</v>
@@ -18640,10 +18652,10 @@
         <v>21</v>
       </c>
       <c r="I319">
-        <v>1435</v>
+        <v>6501</v>
       </c>
       <c r="J319">
-        <v>1435</v>
+        <v>6500</v>
       </c>
       <c r="K319">
         <v>6500</v>
@@ -18681,16 +18693,16 @@
         <v>21</v>
       </c>
       <c r="I320">
-        <v>2009</v>
+        <v>7501</v>
       </c>
       <c r="J320">
-        <v>2009</v>
+        <v>7500</v>
       </c>
       <c r="K320">
         <v>7500</v>
       </c>
       <c r="L320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M320">
         <v>0</v>
@@ -19513,7 +19525,7 @@
         <v>4800</v>
       </c>
       <c r="L340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M340">
         <v>0</v>
@@ -20005,7 +20017,7 @@
         <v>2300</v>
       </c>
       <c r="L352">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M352">
         <v>0</v>
@@ -20298,7 +20310,7 @@
         <v>3169</v>
       </c>
       <c r="L359">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M359">
         <v>0</v>
@@ -23075,7 +23087,7 @@
         <v>770</v>
       </c>
       <c r="F426">
-        <v>13465</v>
+        <v>13411</v>
       </c>
       <c r="G426">
         <v>48000</v>
@@ -23093,7 +23105,7 @@
         <v>23000</v>
       </c>
       <c r="L426">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M426">
         <v>0</v>
@@ -23310,7 +23322,7 @@
         <v>21000</v>
       </c>
       <c r="L431">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M431">
         <v>0</v>
@@ -23398,7 +23410,7 @@
         <v>24000</v>
       </c>
       <c r="L433">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M433">
         <v>0</v>
@@ -23424,7 +23436,7 @@
         <v>264</v>
       </c>
       <c r="F434">
-        <v>12900</v>
+        <v>12295</v>
       </c>
       <c r="G434">
         <v>45000</v>
@@ -23436,13 +23448,13 @@
         <v>45000</v>
       </c>
       <c r="J434">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K434">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="L434">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M434">
         <v>0</v>
@@ -23486,7 +23498,7 @@
         <v>25000</v>
       </c>
       <c r="L435">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M435">
         <v>0</v>
@@ -23530,7 +23542,7 @@
         <v>20000</v>
       </c>
       <c r="L436">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -23618,7 +23630,7 @@
         <v>22000</v>
       </c>
       <c r="L438">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M438">
         <v>0</v>
@@ -23656,13 +23668,13 @@
         <v>50000</v>
       </c>
       <c r="J439">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="K439">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="L439">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M439">
         <v>0</v>
@@ -23688,7 +23700,7 @@
         <v>202</v>
       </c>
       <c r="F440">
-        <v>12150</v>
+        <v>12842</v>
       </c>
       <c r="G440">
         <v>45000</v>
@@ -23700,13 +23712,13 @@
         <v>45000</v>
       </c>
       <c r="J440">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K440">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="L440">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M440">
         <v>0</v>
@@ -23770,25 +23782,25 @@
         <v>814</v>
       </c>
       <c r="F442">
-        <v>14000</v>
+        <v>10930</v>
       </c>
       <c r="G442">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="H442">
         <v>21</v>
       </c>
       <c r="I442">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="J442">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="K442">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="L442">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -24016,7 +24028,7 @@
         <v>28</v>
       </c>
       <c r="F448">
-        <v>11012</v>
+        <v>9964</v>
       </c>
       <c r="G448">
         <v>40000</v>
@@ -24034,7 +24046,7 @@
         <v>20000</v>
       </c>
       <c r="L448">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M448">
         <v>0</v>
@@ -24078,7 +24090,7 @@
         <v>25000</v>
       </c>
       <c r="L449">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M449">
         <v>0</v>
@@ -24104,25 +24116,25 @@
         <v>202</v>
       </c>
       <c r="F450">
-        <v>13345</v>
+        <v>10700</v>
       </c>
       <c r="G450">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="H450">
         <v>21</v>
       </c>
       <c r="I450">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="J450">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="K450">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="L450">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M450">
         <v>0</v>
@@ -24233,22 +24245,22 @@
         <v>202</v>
       </c>
       <c r="F453">
-        <v>12200</v>
+        <v>12116</v>
       </c>
       <c r="G453">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="H453">
         <v>21</v>
       </c>
       <c r="I453">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="J453">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="K453">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="L453">
         <v>8</v>
@@ -24339,7 +24351,7 @@
         <v>22000</v>
       </c>
       <c r="L455">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M455">
         <v>0</v>
@@ -24471,7 +24483,7 @@
         <v>20000</v>
       </c>
       <c r="L458">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -24559,7 +24571,7 @@
         <v>23000</v>
       </c>
       <c r="L460">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M460">
         <v>0</v>
@@ -24603,7 +24615,7 @@
         <v>22000</v>
       </c>
       <c r="L461">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M461">
         <v>0</v>
@@ -24629,25 +24641,25 @@
         <v>202</v>
       </c>
       <c r="F462">
-        <v>15300</v>
+        <v>14480</v>
       </c>
       <c r="G462">
-        <v>54000</v>
+        <v>50000</v>
       </c>
       <c r="H462">
         <v>21</v>
       </c>
       <c r="I462">
-        <v>54000</v>
+        <v>50000</v>
       </c>
       <c r="J462">
-        <v>26500</v>
+        <v>25000</v>
       </c>
       <c r="K462">
-        <v>26500</v>
+        <v>25000</v>
       </c>
       <c r="L462">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M462">
         <v>0</v>
@@ -24767,7 +24779,7 @@
         <v>28000</v>
       </c>
       <c r="K465">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="L465">
         <v>3</v>
@@ -24855,7 +24867,7 @@
         <v>25000</v>
       </c>
       <c r="L467">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M467">
         <v>0</v>
@@ -25215,7 +25227,7 @@
         <v>28</v>
       </c>
       <c r="F476">
-        <v>10939</v>
+        <v>11440</v>
       </c>
       <c r="G476">
         <v>40000</v>
@@ -25233,7 +25245,7 @@
         <v>20000</v>
       </c>
       <c r="L476">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M476">
         <v>0</v>
@@ -25359,7 +25371,7 @@
         <v>32000</v>
       </c>
       <c r="L479">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M479">
         <v>0</v>
@@ -25423,7 +25435,7 @@
         <v>28</v>
       </c>
       <c r="F481">
-        <v>11160</v>
+        <v>10790</v>
       </c>
       <c r="G481">
         <v>40000</v>
@@ -25441,7 +25453,7 @@
         <v>20000</v>
       </c>
       <c r="L481">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M481">
         <v>0</v>
@@ -25467,7 +25479,7 @@
         <v>846</v>
       </c>
       <c r="F482">
-        <v>12682</v>
+        <v>12225</v>
       </c>
       <c r="G482">
         <v>45000</v>
@@ -25479,13 +25491,13 @@
         <v>45000</v>
       </c>
       <c r="J482">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K482">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="L482">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M482">
         <v>0</v>
@@ -25552,7 +25564,7 @@
         <v>846</v>
       </c>
       <c r="F484">
-        <v>12453</v>
+        <v>12489</v>
       </c>
       <c r="G484">
         <v>45000</v>
@@ -25564,13 +25576,13 @@
         <v>45000</v>
       </c>
       <c r="J484">
-        <v>21500</v>
+        <v>22000</v>
       </c>
       <c r="K484">
-        <v>21500</v>
+        <v>22000</v>
       </c>
       <c r="L484">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M484">
         <v>0</v>
@@ -25611,7 +25623,7 @@
         <v>20000</v>
       </c>
       <c r="L485">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -25957,7 +25969,7 @@
         <v>20000</v>
       </c>
       <c r="L493">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M493">
         <v>0</v>
@@ -26024,7 +26036,7 @@
         <v>264</v>
       </c>
       <c r="F495">
-        <v>11550</v>
+        <v>11460</v>
       </c>
       <c r="G495">
         <v>40000</v>
@@ -26042,7 +26054,7 @@
         <v>20000</v>
       </c>
       <c r="L495">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M495">
         <v>0</v>
@@ -26112,7 +26124,7 @@
         <v>264</v>
       </c>
       <c r="F497">
-        <v>11340</v>
+        <v>11265</v>
       </c>
       <c r="G497">
         <v>40000</v>
@@ -26130,7 +26142,7 @@
         <v>18000</v>
       </c>
       <c r="L497">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M497">
         <v>0</v>
@@ -26200,7 +26212,7 @@
         <v>264</v>
       </c>
       <c r="F499">
-        <v>11600</v>
+        <v>11336</v>
       </c>
       <c r="G499">
         <v>40000</v>
@@ -26218,7 +26230,7 @@
         <v>20000</v>
       </c>
       <c r="L499">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M499">
         <v>0</v>
@@ -26326,7 +26338,7 @@
         <v>264</v>
       </c>
       <c r="F502">
-        <v>12310</v>
+        <v>11679</v>
       </c>
       <c r="G502">
         <v>40000</v>
@@ -26344,7 +26356,7 @@
         <v>20000</v>
       </c>
       <c r="L502">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M502">
         <v>0</v>
@@ -26473,7 +26485,7 @@
         <v>26000</v>
       </c>
       <c r="L505">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M505">
         <v>0</v>
@@ -26517,7 +26529,7 @@
         <v>22000</v>
       </c>
       <c r="L506">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M506">
         <v>0</v>
@@ -26605,7 +26617,7 @@
         <v>23000</v>
       </c>
       <c r="L508">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M508">
         <v>0</v>
@@ -26675,7 +26687,7 @@
         <v>264</v>
       </c>
       <c r="F510">
-        <v>12700</v>
+        <v>12420</v>
       </c>
       <c r="G510">
         <v>45000</v>
@@ -26693,7 +26705,7 @@
         <v>22000</v>
       </c>
       <c r="L510">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M510">
         <v>0</v>
@@ -26807,7 +26819,7 @@
         <v>178</v>
       </c>
       <c r="F513">
-        <v>10000</v>
+        <v>9940</v>
       </c>
       <c r="G513">
         <v>40000</v>
@@ -26816,7 +26828,7 @@
         <v>21</v>
       </c>
       <c r="I513">
-        <v>40000</v>
+        <v>39760</v>
       </c>
       <c r="J513">
         <v>20000</v>
@@ -26825,7 +26837,7 @@
         <v>20000</v>
       </c>
       <c r="L513">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M513">
         <v>0</v>
@@ -26895,7 +26907,7 @@
         <v>178</v>
       </c>
       <c r="F515">
-        <v>10074</v>
+        <v>10267</v>
       </c>
       <c r="G515">
         <v>40000</v>
@@ -26913,7 +26925,7 @@
         <v>20000</v>
       </c>
       <c r="L515">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M515">
         <v>0</v>
@@ -26983,7 +26995,7 @@
         <v>178</v>
       </c>
       <c r="F517">
-        <v>10578</v>
+        <v>12182</v>
       </c>
       <c r="G517">
         <v>40000</v>
@@ -26995,13 +27007,13 @@
         <v>40000</v>
       </c>
       <c r="J517">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="K517">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="L517">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M517">
         <v>0</v>
@@ -27042,7 +27054,7 @@
         <v>25000</v>
       </c>
       <c r="L518">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M518">
         <v>0</v>
@@ -27086,7 +27098,7 @@
         <v>20000</v>
       </c>
       <c r="L519">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M519">
         <v>0</v>
@@ -27194,7 +27206,7 @@
         <v>264</v>
       </c>
       <c r="F522">
-        <v>12440</v>
+        <v>12624</v>
       </c>
       <c r="G522">
         <v>45000</v>
@@ -27206,13 +27218,13 @@
         <v>45000</v>
       </c>
       <c r="J522">
-        <v>22000</v>
+        <v>2200</v>
       </c>
       <c r="K522">
         <v>22000</v>
       </c>
       <c r="L522">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M522">
         <v>0</v>
@@ -27256,7 +27268,7 @@
         <v>30000</v>
       </c>
       <c r="L523">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M523">
         <v>0</v>
@@ -27388,7 +27400,7 @@
         <v>30000</v>
       </c>
       <c r="L526">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M526">
         <v>0</v>
@@ -27432,7 +27444,7 @@
         <v>30000</v>
       </c>
       <c r="L527">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M527">
         <v>0</v>
@@ -27631,25 +27643,25 @@
         <v>28</v>
       </c>
       <c r="F532">
-        <v>10634</v>
+        <v>10266</v>
       </c>
       <c r="G532">
-        <v>40000</v>
+        <v>38615.599999999999</v>
       </c>
       <c r="H532">
         <v>21</v>
       </c>
       <c r="I532">
-        <v>40000</v>
+        <v>38615.599999999999</v>
       </c>
       <c r="J532">
-        <v>20000</v>
+        <v>19308.3</v>
       </c>
       <c r="K532">
-        <v>20000</v>
+        <v>19308.3</v>
       </c>
       <c r="L532">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M532">
         <v>0</v>
@@ -27716,25 +27728,25 @@
         <v>178</v>
       </c>
       <c r="F534">
-        <v>13278</v>
+        <v>13492</v>
       </c>
       <c r="G534">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="H534">
         <v>21</v>
       </c>
       <c r="I534">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="J534">
-        <v>22000</v>
+        <v>23000</v>
       </c>
       <c r="K534">
-        <v>22000</v>
+        <v>23000</v>
       </c>
       <c r="L534">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M534">
         <v>0</v>
@@ -27760,22 +27772,22 @@
         <v>13700</v>
       </c>
       <c r="G535">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="H535">
         <v>21</v>
       </c>
       <c r="I535">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="J535">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="K535">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="L535">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M535">
         <v>0</v>
@@ -27845,7 +27857,7 @@
         <v>264</v>
       </c>
       <c r="F537">
-        <v>12400</v>
+        <v>12428</v>
       </c>
       <c r="G537">
         <v>45000</v>
@@ -27863,7 +27875,7 @@
         <v>22000</v>
       </c>
       <c r="L537">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M537">
         <v>0</v>
@@ -28036,7 +28048,7 @@
         <v>31000</v>
       </c>
       <c r="L541">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M541">
         <v>0</v>
@@ -28168,7 +28180,7 @@
         <v>30000</v>
       </c>
       <c r="L544">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M544">
         <v>0</v>
@@ -28256,7 +28268,7 @@
         <v>30000</v>
       </c>
       <c r="L546">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M546">
         <v>0</v>
@@ -28388,7 +28400,7 @@
         <v>30000</v>
       </c>
       <c r="L549">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M549">
         <v>0</v>
@@ -28599,7 +28611,7 @@
         <v>21000</v>
       </c>
       <c r="L554">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M554">
         <v>0</v>
@@ -28622,7 +28634,7 @@
         <v>28</v>
       </c>
       <c r="F555">
-        <v>8466</v>
+        <v>8423</v>
       </c>
       <c r="G555">
         <v>40000</v>
@@ -28634,13 +28646,13 @@
         <v>40000</v>
       </c>
       <c r="J555">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="K555">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="L555">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M555">
         <v>0</v>
@@ -28892,7 +28904,7 @@
         <v>18000</v>
       </c>
       <c r="L561">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M561">
         <v>0</v>
@@ -28962,7 +28974,7 @@
         <v>1063</v>
       </c>
       <c r="F563">
-        <v>14508</v>
+        <v>15050</v>
       </c>
       <c r="G563">
         <v>50000</v>
@@ -28980,7 +28992,7 @@
         <v>25000</v>
       </c>
       <c r="L563">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M563">
         <v>0</v>
@@ -29244,7 +29256,7 @@
         <v>25000</v>
       </c>
       <c r="L569">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M569">
         <v>0</v>
@@ -29270,7 +29282,7 @@
         <v>264</v>
       </c>
       <c r="F570">
-        <v>13961.4</v>
+        <v>13620</v>
       </c>
       <c r="G570">
         <v>48000</v>
@@ -29288,7 +29300,7 @@
         <v>24000</v>
       </c>
       <c r="L570">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M570">
         <v>0</v>
@@ -29332,7 +29344,7 @@
         <v>26000</v>
       </c>
       <c r="L571">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M571">
         <v>0</v>
@@ -29402,7 +29414,7 @@
         <v>1084</v>
       </c>
       <c r="F573">
-        <v>14362</v>
+        <v>13592</v>
       </c>
       <c r="G573">
         <v>48000</v>
@@ -29420,7 +29432,7 @@
         <v>24000</v>
       </c>
       <c r="L573">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M573">
         <v>0</v>
@@ -29748,25 +29760,25 @@
         <v>1093</v>
       </c>
       <c r="F581">
-        <v>16000</v>
+        <v>13030</v>
       </c>
       <c r="G581">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="H581">
         <v>21</v>
       </c>
       <c r="I581">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="J581">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="K581">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="L581">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M581">
         <v>0</v>
@@ -30012,7 +30024,7 @@
         <v>1112</v>
       </c>
       <c r="F587">
-        <v>16362</v>
+        <v>16236</v>
       </c>
       <c r="G587">
         <v>50000</v>
@@ -30021,7 +30033,7 @@
         <v>21</v>
       </c>
       <c r="I587">
-        <v>50000</v>
+        <v>49615.6</v>
       </c>
       <c r="J587">
         <v>26000</v>
@@ -30030,7 +30042,7 @@
         <v>26000</v>
       </c>
       <c r="L587">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M587">
         <v>0</v>
@@ -30338,7 +30350,7 @@
         <v>2835</v>
       </c>
       <c r="L594">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M594">
         <v>0</v>
@@ -30420,7 +30432,7 @@
         <v>4070</v>
       </c>
       <c r="L596">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M596">
         <v>0</v>
@@ -31059,7 +31071,7 @@
         <v>13216</v>
       </c>
       <c r="L611">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M611">
         <v>0</v>
@@ -31894,10 +31906,10 @@
         <v>21</v>
       </c>
       <c r="I631">
-        <v>4428</v>
+        <v>9001</v>
       </c>
       <c r="J631">
-        <v>4428</v>
+        <v>9000</v>
       </c>
       <c r="K631">
         <v>9000</v>
@@ -31935,16 +31947,16 @@
         <v>21</v>
       </c>
       <c r="I632">
-        <v>2993</v>
+        <v>8001</v>
       </c>
       <c r="J632">
-        <v>2993</v>
+        <v>8000</v>
       </c>
       <c r="K632">
         <v>8000</v>
       </c>
       <c r="L632">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M632">
         <v>0</v>
@@ -32747,7 +32759,7 @@
         <v>112</v>
       </c>
       <c r="L651">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M651">
         <v>0</v>
@@ -33690,7 +33702,7 @@
         <v>25000</v>
       </c>
       <c r="J674">
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="K674">
         <v>12000</v>
@@ -38047,7 +38059,7 @@
         <v>9493</v>
       </c>
       <c r="L775">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M775">
         <v>0</v>
@@ -38381,7 +38393,7 @@
         <v>7712</v>
       </c>
       <c r="L783">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M783">
         <v>0</v>
@@ -38551,7 +38563,7 @@
         <v>5586</v>
       </c>
       <c r="L787">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M787">
         <v>0</v>
@@ -38891,7 +38903,7 @@
         <v>21500</v>
       </c>
       <c r="L795">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M795">
         <v>0</v>
@@ -39462,16 +39474,16 @@
         <v>21</v>
       </c>
       <c r="I809">
-        <v>9059.5</v>
+        <v>8000</v>
       </c>
       <c r="J809">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="K809">
         <v>2129</v>
       </c>
       <c r="L809">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M809">
         <v>0</v>
@@ -39567,7 +39579,7 @@
     </row>
     <row r="812" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A812">
-        <v>6974504501018</v>
+        <v>7799135022195</v>
       </c>
       <c r="B812" t="s">
         <v>1486</v>
@@ -39576,13 +39588,13 @@
         <v>64</v>
       </c>
       <c r="D812" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F812">
-        <v>6339</v>
+        <v>4917.5</v>
       </c>
       <c r="G812">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H812">
         <v>21</v>
@@ -39591,95 +39603,95 @@
         <v>20000</v>
       </c>
       <c r="J812">
+        <v>8800</v>
+      </c>
+      <c r="K812">
+        <v>4917.5</v>
+      </c>
+      <c r="L812">
+        <v>3</v>
+      </c>
+      <c r="M812">
+        <v>0</v>
+      </c>
+      <c r="N812">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A813">
+        <v>6974504501018</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C813" t="s">
+        <v>64</v>
+      </c>
+      <c r="D813" t="s">
+        <v>59</v>
+      </c>
+      <c r="F813">
+        <v>6339</v>
+      </c>
+      <c r="G813">
         <v>20000</v>
       </c>
-      <c r="K812">
+      <c r="H813">
+        <v>21</v>
+      </c>
+      <c r="I813">
+        <v>20000</v>
+      </c>
+      <c r="J813">
+        <v>20000</v>
+      </c>
+      <c r="K813">
         <v>6339</v>
       </c>
-      <c r="L812">
+      <c r="L813">
         <v>5</v>
       </c>
-      <c r="M812">
-        <v>0</v>
-      </c>
-      <c r="N812">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A813" t="s">
-        <v>1487</v>
-      </c>
-      <c r="B813" t="s">
+      <c r="M813">
+        <v>0</v>
+      </c>
+      <c r="N813">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
         <v>1488</v>
-      </c>
-      <c r="D813" t="s">
-        <v>31</v>
-      </c>
-      <c r="F813">
-        <v>7742</v>
-      </c>
-      <c r="G813">
-        <v>24000</v>
-      </c>
-      <c r="H813">
-        <v>21</v>
-      </c>
-      <c r="I813">
-        <v>24000</v>
-      </c>
-      <c r="J813">
-        <v>24000</v>
-      </c>
-      <c r="K813">
-        <v>7742</v>
-      </c>
-      <c r="L813">
-        <v>3</v>
-      </c>
-      <c r="M813">
-        <v>0</v>
-      </c>
-      <c r="N813">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A814">
-        <v>843367116218</v>
       </c>
       <c r="B814" t="s">
         <v>1489</v>
       </c>
       <c r="C814" t="s">
-        <v>722</v>
+        <v>64</v>
       </c>
       <c r="D814" t="s">
-        <v>359</v>
-      </c>
-      <c r="E814" t="s">
-        <v>1490</v>
+        <v>31</v>
       </c>
       <c r="F814">
-        <v>18444</v>
+        <v>7742</v>
       </c>
       <c r="G814">
-        <v>34000</v>
+        <v>26000</v>
       </c>
       <c r="H814">
         <v>21</v>
       </c>
       <c r="I814">
-        <v>18444</v>
+        <v>26000</v>
       </c>
       <c r="J814">
-        <v>18444</v>
+        <v>14000</v>
       </c>
       <c r="K814">
-        <v>18444</v>
+        <v>7742</v>
       </c>
       <c r="L814">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M814">
         <v>0</v>
@@ -39690,10 +39702,10 @@
     </row>
     <row r="815" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A815">
-        <v>7448070134219</v>
+        <v>843367116218</v>
       </c>
       <c r="B815" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C815" t="s">
         <v>722</v>
@@ -39702,69 +39714,72 @@
         <v>359</v>
       </c>
       <c r="E815" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F815">
+        <v>18444</v>
+      </c>
+      <c r="G815">
+        <v>34000</v>
+      </c>
+      <c r="H815">
+        <v>21</v>
+      </c>
+      <c r="I815">
+        <v>18444</v>
+      </c>
+      <c r="J815">
+        <v>18444</v>
+      </c>
+      <c r="K815">
+        <v>18444</v>
+      </c>
+      <c r="L815">
+        <v>0</v>
+      </c>
+      <c r="M815">
+        <v>0</v>
+      </c>
+      <c r="N815">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A816">
+        <v>7448070134219</v>
+      </c>
+      <c r="B816" t="s">
         <v>1492</v>
       </c>
-      <c r="F815">
+      <c r="C816" t="s">
+        <v>722</v>
+      </c>
+      <c r="D816" t="s">
+        <v>359</v>
+      </c>
+      <c r="E816" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F816">
         <v>17600</v>
       </c>
-      <c r="G815">
+      <c r="G816">
         <v>32000</v>
       </c>
-      <c r="H815">
-        <v>21</v>
-      </c>
-      <c r="I815">
+      <c r="H816">
+        <v>21</v>
+      </c>
+      <c r="I816">
         <v>17600</v>
       </c>
-      <c r="J815">
+      <c r="J816">
         <v>17600</v>
       </c>
-      <c r="K815">
+      <c r="K816">
         <v>17600</v>
       </c>
-      <c r="L815">
+      <c r="L816">
         <v>1</v>
-      </c>
-      <c r="M815">
-        <v>0</v>
-      </c>
-      <c r="N815">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A816" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C816" t="s">
-        <v>38</v>
-      </c>
-      <c r="D816" t="s">
-        <v>49</v>
-      </c>
-      <c r="F816">
-        <v>900</v>
-      </c>
-      <c r="G816">
-        <v>3500</v>
-      </c>
-      <c r="H816">
-        <v>21</v>
-      </c>
-      <c r="I816">
-        <v>900</v>
-      </c>
-      <c r="J816">
-        <v>900</v>
-      </c>
-      <c r="K816">
-        <v>900</v>
-      </c>
-      <c r="L816">
-        <v>3</v>
       </c>
       <c r="M816">
         <v>0</v>
@@ -39775,37 +39790,37 @@
     </row>
     <row r="817" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B817" t="s">
         <v>1495</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1496</v>
       </c>
       <c r="C817" t="s">
         <v>38</v>
       </c>
       <c r="D817" t="s">
-        <v>528</v>
+        <v>49</v>
       </c>
       <c r="F817">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="G817">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="H817">
         <v>21</v>
       </c>
       <c r="I817">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J817">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K817">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L817">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M817">
         <v>0</v>
@@ -39816,40 +39831,37 @@
     </row>
     <row r="818" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B818" t="s">
         <v>1497</v>
       </c>
-      <c r="B818" t="s">
-        <v>1498</v>
-      </c>
       <c r="C818" t="s">
-        <v>418</v>
+        <v>38</v>
       </c>
       <c r="D818" t="s">
-        <v>28</v>
-      </c>
-      <c r="E818" t="s">
-        <v>419</v>
+        <v>528</v>
       </c>
       <c r="F818">
-        <v>2264</v>
+        <v>650</v>
       </c>
       <c r="G818">
-        <v>8001</v>
+        <v>1500</v>
       </c>
       <c r="H818">
         <v>21</v>
       </c>
       <c r="I818">
-        <v>2264</v>
+        <v>0</v>
       </c>
       <c r="J818">
-        <v>2264</v>
+        <v>0</v>
       </c>
       <c r="K818">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="L818">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M818">
         <v>0</v>
@@ -39860,43 +39872,46 @@
     </row>
     <row r="819" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B819" t="s">
         <v>1499</v>
       </c>
       <c r="C819" t="s">
-        <v>506</v>
+        <v>418</v>
       </c>
       <c r="D819" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="E819" t="s">
+        <v>419</v>
       </c>
       <c r="F819">
-        <v>2200</v>
+        <v>2264</v>
       </c>
       <c r="G819">
-        <v>4900</v>
+        <v>8001</v>
       </c>
       <c r="H819">
         <v>21</v>
       </c>
       <c r="I819">
-        <v>2200</v>
+        <v>2264</v>
       </c>
       <c r="J819">
-        <v>2200</v>
+        <v>2264</v>
       </c>
       <c r="K819">
-        <v>2200</v>
+        <v>8000</v>
       </c>
       <c r="L819">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M819">
         <v>0</v>
       </c>
       <c r="N819">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820" spans="1:14" x14ac:dyDescent="0.25">
@@ -39904,86 +39919,86 @@
         <v>1500</v>
       </c>
       <c r="B820" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C820" t="s">
+        <v>506</v>
+      </c>
+      <c r="D820" t="s">
+        <v>49</v>
+      </c>
+      <c r="F820">
+        <v>2200</v>
+      </c>
+      <c r="G820">
+        <v>4900</v>
+      </c>
+      <c r="H820">
+        <v>21</v>
+      </c>
+      <c r="I820">
+        <v>2200</v>
+      </c>
+      <c r="J820">
+        <v>2200</v>
+      </c>
+      <c r="K820">
+        <v>2200</v>
+      </c>
+      <c r="L820">
+        <v>0</v>
+      </c>
+      <c r="M820">
+        <v>0</v>
+      </c>
+      <c r="N820">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
         <v>1501</v>
-      </c>
-      <c r="C820" t="s">
-        <v>516</v>
-      </c>
-      <c r="E820" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F820">
-        <v>1000</v>
-      </c>
-      <c r="G820">
-        <v>10000</v>
-      </c>
-      <c r="H820">
-        <v>21</v>
-      </c>
-      <c r="I820">
-        <v>1000</v>
-      </c>
-      <c r="J820">
-        <v>1000</v>
-      </c>
-      <c r="K820">
-        <v>1000</v>
-      </c>
-      <c r="L820">
-        <v>-2.2000000476837198</v>
-      </c>
-      <c r="M820">
-        <v>0</v>
-      </c>
-      <c r="N820">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A821">
-        <v>7799135009790</v>
       </c>
       <c r="B821" t="s">
         <v>1502</v>
       </c>
       <c r="C821" t="s">
-        <v>433</v>
-      </c>
-      <c r="D821" t="s">
-        <v>28</v>
+        <v>516</v>
+      </c>
+      <c r="E821" t="s">
+        <v>1501</v>
       </c>
       <c r="F821">
-        <v>6519</v>
+        <v>1000</v>
       </c>
       <c r="G821">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H821">
         <v>21</v>
       </c>
       <c r="I821">
-        <v>6519</v>
+        <v>1000</v>
       </c>
       <c r="J821">
-        <v>6519</v>
+        <v>1000</v>
       </c>
       <c r="K821">
-        <v>6519</v>
+        <v>1000</v>
       </c>
       <c r="L821">
-        <v>2</v>
+        <v>-6.1999998092651403</v>
       </c>
       <c r="M821">
         <v>0</v>
       </c>
       <c r="N821">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A822">
-        <v>700306601221</v>
+        <v>7799135009790</v>
       </c>
       <c r="B822" t="s">
         <v>1503</v>
@@ -39992,28 +40007,28 @@
         <v>433</v>
       </c>
       <c r="D822" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F822">
-        <v>4012</v>
+        <v>6519</v>
       </c>
       <c r="G822">
-        <v>12500</v>
+        <v>16000</v>
       </c>
       <c r="H822">
         <v>21</v>
       </c>
       <c r="I822">
-        <v>4012</v>
+        <v>6519</v>
       </c>
       <c r="J822">
-        <v>4012</v>
+        <v>6519</v>
       </c>
       <c r="K822">
-        <v>4012</v>
+        <v>6519</v>
       </c>
       <c r="L822">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M822">
         <v>0</v>
@@ -40023,79 +40038,79 @@
       </c>
     </row>
     <row r="823" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A823" t="s">
+      <c r="A823">
+        <v>700306601221</v>
+      </c>
+      <c r="B823" t="s">
         <v>1504</v>
       </c>
-      <c r="B823" t="s">
-        <v>1505</v>
-      </c>
       <c r="C823" t="s">
-        <v>1130</v>
+        <v>433</v>
       </c>
       <c r="D823" t="s">
         <v>31</v>
       </c>
       <c r="F823">
-        <v>11138</v>
+        <v>4012</v>
       </c>
       <c r="G823">
-        <v>32000</v>
+        <v>12500</v>
       </c>
       <c r="H823">
         <v>21</v>
       </c>
       <c r="I823">
-        <v>11138</v>
+        <v>4012</v>
       </c>
       <c r="J823">
-        <v>11138</v>
+        <v>4012</v>
       </c>
       <c r="K823">
-        <v>11138</v>
+        <v>4012</v>
       </c>
       <c r="L823">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M823">
         <v>0</v>
       </c>
       <c r="N823">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="824" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B824" t="s">
         <v>1506</v>
       </c>
-      <c r="B824" t="s">
-        <v>1507</v>
-      </c>
       <c r="C824" t="s">
-        <v>58</v>
+        <v>1130</v>
       </c>
       <c r="D824" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F824">
-        <v>17496</v>
+        <v>11138</v>
       </c>
       <c r="G824">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="H824">
         <v>21</v>
       </c>
       <c r="I824">
-        <v>0</v>
+        <v>11138</v>
       </c>
       <c r="J824">
-        <v>0</v>
+        <v>11138</v>
       </c>
       <c r="K824">
-        <v>0</v>
+        <v>11138</v>
       </c>
       <c r="L824">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M824">
         <v>0</v>
@@ -40106,78 +40121,78 @@
     </row>
     <row r="825" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B825" t="s">
         <v>1508</v>
       </c>
-      <c r="B825" t="s">
+      <c r="C825" t="s">
+        <v>58</v>
+      </c>
+      <c r="D825" t="s">
+        <v>3</v>
+      </c>
+      <c r="F825">
+        <v>17496</v>
+      </c>
+      <c r="G825">
+        <v>35000</v>
+      </c>
+      <c r="H825">
+        <v>21</v>
+      </c>
+      <c r="I825">
+        <v>0</v>
+      </c>
+      <c r="J825">
+        <v>0</v>
+      </c>
+      <c r="K825">
+        <v>0</v>
+      </c>
+      <c r="L825">
+        <v>3</v>
+      </c>
+      <c r="M825">
+        <v>0</v>
+      </c>
+      <c r="N825">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
         <v>1509</v>
-      </c>
-      <c r="C825" t="s">
-        <v>421</v>
-      </c>
-      <c r="D825" t="s">
-        <v>31</v>
-      </c>
-      <c r="F825">
-        <v>1150</v>
-      </c>
-      <c r="G825">
-        <v>3000</v>
-      </c>
-      <c r="H825">
-        <v>21</v>
-      </c>
-      <c r="I825">
-        <v>1150</v>
-      </c>
-      <c r="J825">
-        <v>1150</v>
-      </c>
-      <c r="K825">
-        <v>1150</v>
-      </c>
-      <c r="L825">
-        <v>5</v>
-      </c>
-      <c r="M825">
-        <v>0</v>
-      </c>
-      <c r="N825">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A826">
-        <v>7798423541356</v>
       </c>
       <c r="B826" t="s">
         <v>1510</v>
       </c>
       <c r="C826" t="s">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="D826" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="F826">
-        <v>4100</v>
+        <v>1150</v>
       </c>
       <c r="G826">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="H826">
         <v>21</v>
       </c>
       <c r="I826">
-        <v>4100</v>
+        <v>1150</v>
       </c>
       <c r="J826">
-        <v>4100</v>
+        <v>1150</v>
       </c>
       <c r="K826">
-        <v>4100</v>
+        <v>1150</v>
       </c>
       <c r="L826">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M826">
         <v>0</v>
@@ -40188,48 +40203,48 @@
     </row>
     <row r="827" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A827">
-        <v>7798145006027</v>
+        <v>7798423541356</v>
       </c>
       <c r="B827" t="s">
         <v>1511</v>
       </c>
       <c r="C827" t="s">
-        <v>506</v>
+        <v>77</v>
       </c>
       <c r="D827" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F827">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="G827">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="H827">
         <v>21</v>
       </c>
       <c r="I827">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="J827">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="K827">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="L827">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M827">
         <v>0</v>
       </c>
       <c r="N827">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="828" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A828">
-        <v>69855646885262</v>
+        <v>7798145006027</v>
       </c>
       <c r="B828" t="s">
         <v>1512</v>
@@ -40238,31 +40253,28 @@
         <v>506</v>
       </c>
       <c r="D828" t="s">
-        <v>31</v>
-      </c>
-      <c r="E828" t="s">
-        <v>1513</v>
+        <v>3</v>
       </c>
       <c r="F828">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="G828">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H828">
         <v>21</v>
       </c>
       <c r="I828">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="J828">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="K828">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="L828">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M828">
         <v>0</v>
@@ -40273,10 +40285,10 @@
     </row>
     <row r="829" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A829">
-        <v>6985564688526</v>
+        <v>69855646885262</v>
       </c>
       <c r="B829" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C829" t="s">
         <v>506</v>
@@ -40285,7 +40297,7 @@
         <v>31</v>
       </c>
       <c r="E829" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F829">
         <v>2629</v>
@@ -40306,7 +40318,7 @@
         <v>2629</v>
       </c>
       <c r="L829">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M829">
         <v>0</v>
@@ -40317,34 +40329,37 @@
     </row>
     <row r="830" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A830">
-        <v>7790000111020</v>
+        <v>6985564688526</v>
       </c>
       <c r="B830" t="s">
         <v>1515</v>
       </c>
       <c r="C830" t="s">
-        <v>421</v>
+        <v>506</v>
       </c>
       <c r="D830" t="s">
-        <v>3</v>
+        <v>31</v>
+      </c>
+      <c r="E830" t="s">
+        <v>1514</v>
       </c>
       <c r="F830">
-        <v>1200</v>
+        <v>2629</v>
       </c>
       <c r="G830">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H830">
         <v>21</v>
       </c>
       <c r="I830">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="J830">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="K830">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="L830">
         <v>4</v>
@@ -40353,94 +40368,94 @@
         <v>0</v>
       </c>
       <c r="N830">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="831" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A831">
-        <v>6920220096888</v>
+        <v>7790000111020</v>
       </c>
       <c r="B831" t="s">
         <v>1516</v>
       </c>
       <c r="C831" t="s">
+        <v>421</v>
+      </c>
+      <c r="D831" t="s">
+        <v>3</v>
+      </c>
+      <c r="F831">
+        <v>1200</v>
+      </c>
+      <c r="G831">
+        <v>5000</v>
+      </c>
+      <c r="H831">
+        <v>21</v>
+      </c>
+      <c r="I831">
+        <v>0</v>
+      </c>
+      <c r="J831">
+        <v>0</v>
+      </c>
+      <c r="K831">
+        <v>0</v>
+      </c>
+      <c r="L831">
+        <v>4</v>
+      </c>
+      <c r="M831">
+        <v>0</v>
+      </c>
+      <c r="N831">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A832">
+        <v>6920220096888</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C832" t="s">
         <v>53</v>
       </c>
-      <c r="D831" t="s">
+      <c r="D832" t="s">
         <v>49</v>
       </c>
-      <c r="F831">
+      <c r="F832">
         <v>4800</v>
       </c>
-      <c r="G831">
+      <c r="G832">
         <v>9600</v>
       </c>
-      <c r="H831">
-        <v>21</v>
-      </c>
-      <c r="I831">
+      <c r="H832">
+        <v>21</v>
+      </c>
+      <c r="I832">
         <v>4800</v>
       </c>
-      <c r="J831">
+      <c r="J832">
         <v>4800</v>
       </c>
-      <c r="K831">
+      <c r="K832">
         <v>4800</v>
       </c>
-      <c r="L831">
-        <v>0</v>
-      </c>
-      <c r="M831">
-        <v>0</v>
-      </c>
-      <c r="N831">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A832" t="s">
-        <v>1517</v>
-      </c>
-      <c r="B832" t="s">
+      <c r="L832">
+        <v>0</v>
+      </c>
+      <c r="M832">
+        <v>0</v>
+      </c>
+      <c r="N832">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
         <v>1518</v>
-      </c>
-      <c r="C832" t="s">
-        <v>67</v>
-      </c>
-      <c r="D832" t="s">
-        <v>31</v>
-      </c>
-      <c r="F832">
-        <v>3615</v>
-      </c>
-      <c r="G832">
-        <v>9000</v>
-      </c>
-      <c r="H832">
-        <v>21</v>
-      </c>
-      <c r="I832">
-        <v>9000</v>
-      </c>
-      <c r="J832">
-        <v>5800</v>
-      </c>
-      <c r="K832">
-        <v>3615</v>
-      </c>
-      <c r="L832">
-        <v>5</v>
-      </c>
-      <c r="M832">
-        <v>0</v>
-      </c>
-      <c r="N832">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A833">
-        <v>7795234526572</v>
       </c>
       <c r="B833" t="s">
         <v>1519</v>
@@ -40452,25 +40467,25 @@
         <v>31</v>
       </c>
       <c r="F833">
-        <v>4126</v>
+        <v>3615</v>
       </c>
       <c r="G833">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H833">
         <v>21</v>
       </c>
       <c r="I833">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="J833">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="K833">
-        <v>4126</v>
+        <v>3615</v>
       </c>
       <c r="L833">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M833">
         <v>0</v>
@@ -40480,11 +40495,11 @@
       </c>
     </row>
     <row r="834" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A834" t="s">
+      <c r="A834">
+        <v>7795234526572</v>
+      </c>
+      <c r="B834" t="s">
         <v>1520</v>
-      </c>
-      <c r="B834" t="s">
-        <v>1521</v>
       </c>
       <c r="C834" t="s">
         <v>67</v>
@@ -40493,25 +40508,25 @@
         <v>31</v>
       </c>
       <c r="F834">
-        <v>6400</v>
+        <v>4126</v>
       </c>
       <c r="G834">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H834">
         <v>21</v>
       </c>
       <c r="I834">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="J834">
-        <v>9600</v>
+        <v>6200</v>
       </c>
       <c r="K834">
-        <v>6400</v>
+        <v>4126</v>
       </c>
       <c r="L834">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M834">
         <v>0</v>
@@ -40522,10 +40537,10 @@
     </row>
     <row r="835" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B835" t="s">
         <v>1522</v>
-      </c>
-      <c r="B835" t="s">
-        <v>1523</v>
       </c>
       <c r="C835" t="s">
         <v>67</v>
@@ -40534,25 +40549,25 @@
         <v>31</v>
       </c>
       <c r="F835">
-        <v>7245</v>
+        <v>6400</v>
       </c>
       <c r="G835">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H835">
         <v>21</v>
       </c>
       <c r="I835">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="J835">
-        <v>12000</v>
+        <v>9600</v>
       </c>
       <c r="K835">
-        <v>7245</v>
+        <v>6400</v>
       </c>
       <c r="L835">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M835">
         <v>0</v>
@@ -40563,37 +40578,37 @@
     </row>
     <row r="836" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B836" t="s">
         <v>1524</v>
       </c>
-      <c r="B836" t="s">
-        <v>1525</v>
-      </c>
       <c r="C836" t="s">
-        <v>306</v>
+        <v>67</v>
       </c>
       <c r="D836" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F836">
-        <v>15900</v>
+        <v>7245</v>
       </c>
       <c r="G836">
-        <v>45000</v>
+        <v>26000</v>
       </c>
       <c r="H836">
         <v>21</v>
       </c>
       <c r="I836">
-        <v>15900</v>
+        <v>26000</v>
       </c>
       <c r="J836">
-        <v>15900</v>
+        <v>12000</v>
       </c>
       <c r="K836">
-        <v>15900</v>
+        <v>7245</v>
       </c>
       <c r="L836">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M836">
         <v>0</v>
@@ -40604,37 +40619,37 @@
     </row>
     <row r="837" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B837" t="s">
         <v>1526</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1527</v>
       </c>
       <c r="C837" t="s">
         <v>306</v>
       </c>
       <c r="D837" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F837">
-        <v>6815</v>
+        <v>15900</v>
       </c>
       <c r="G837">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="H837">
         <v>21</v>
       </c>
       <c r="I837">
-        <v>20000</v>
+        <v>15900</v>
       </c>
       <c r="J837">
-        <v>20000</v>
+        <v>15900</v>
       </c>
       <c r="K837">
-        <v>6815</v>
+        <v>15900</v>
       </c>
       <c r="L837">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M837">
         <v>0</v>
@@ -40644,8 +40659,8 @@
       </c>
     </row>
     <row r="838" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A838">
-        <v>6902540752361</v>
+      <c r="A838" t="s">
+        <v>1527</v>
       </c>
       <c r="B838" t="s">
         <v>1528</v>
@@ -40654,25 +40669,25 @@
         <v>306</v>
       </c>
       <c r="D838" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="F838">
-        <v>5800</v>
+        <v>6815</v>
       </c>
       <c r="G838">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H838">
         <v>21</v>
       </c>
       <c r="I838">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="J838">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="K838">
-        <v>5800</v>
+        <v>6815</v>
       </c>
       <c r="L838">
         <v>1</v>
@@ -40685,23 +40700,23 @@
       </c>
     </row>
     <row r="839" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A839" t="s">
+      <c r="A839">
+        <v>6902540752361</v>
+      </c>
+      <c r="B839" t="s">
         <v>1529</v>
       </c>
-      <c r="B839" t="s">
-        <v>1530</v>
-      </c>
       <c r="C839" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
       <c r="D839" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F839">
+        <v>5800</v>
+      </c>
+      <c r="G839">
         <v>15000</v>
-      </c>
-      <c r="G839">
-        <v>35000</v>
       </c>
       <c r="H839">
         <v>21</v>
@@ -40713,7 +40728,7 @@
         <v>15000</v>
       </c>
       <c r="K839">
-        <v>15000</v>
+        <v>5800</v>
       </c>
       <c r="L839">
         <v>1</v>
@@ -40726,82 +40741,82 @@
       </c>
     </row>
     <row r="840" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A840">
-        <v>723540564022</v>
+      <c r="A840" t="s">
+        <v>1530</v>
       </c>
       <c r="B840" t="s">
         <v>1531</v>
       </c>
       <c r="C840" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="D840" t="s">
+        <v>3</v>
+      </c>
+      <c r="F840">
+        <v>15000</v>
+      </c>
+      <c r="G840">
+        <v>35000</v>
+      </c>
+      <c r="H840">
+        <v>21</v>
+      </c>
+      <c r="I840">
+        <v>15000</v>
+      </c>
+      <c r="J840">
+        <v>15000</v>
+      </c>
+      <c r="K840">
+        <v>15000</v>
+      </c>
+      <c r="L840">
+        <v>1</v>
+      </c>
+      <c r="M840">
+        <v>0</v>
+      </c>
+      <c r="N840">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A841">
+        <v>723540564022</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C841" t="s">
+        <v>459</v>
+      </c>
+      <c r="D841" t="s">
         <v>31</v>
       </c>
-      <c r="E840" t="s">
+      <c r="E841" t="s">
         <v>142</v>
       </c>
-      <c r="F840">
+      <c r="F841">
         <v>3175</v>
       </c>
-      <c r="G840">
+      <c r="G841">
         <v>9500</v>
       </c>
-      <c r="H840">
-        <v>21</v>
-      </c>
-      <c r="I840">
+      <c r="H841">
+        <v>21</v>
+      </c>
+      <c r="I841">
         <v>3175</v>
       </c>
-      <c r="J840">
+      <c r="J841">
         <v>3175</v>
       </c>
-      <c r="K840">
+      <c r="K841">
         <v>3175</v>
       </c>
-      <c r="L840">
+      <c r="L841">
         <v>2</v>
-      </c>
-      <c r="M840">
-        <v>0</v>
-      </c>
-      <c r="N840">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A841" t="s">
-        <v>1532</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1533</v>
-      </c>
-      <c r="C841" t="s">
-        <v>461</v>
-      </c>
-      <c r="D841" t="s">
-        <v>49</v>
-      </c>
-      <c r="F841">
-        <v>2000</v>
-      </c>
-      <c r="G841">
-        <v>8000</v>
-      </c>
-      <c r="H841">
-        <v>21</v>
-      </c>
-      <c r="I841">
-        <v>8000</v>
-      </c>
-      <c r="J841">
-        <v>8000</v>
-      </c>
-      <c r="K841">
-        <v>2000</v>
-      </c>
-      <c r="L841">
-        <v>8</v>
       </c>
       <c r="M841">
         <v>0</v>
@@ -40812,37 +40827,37 @@
     </row>
     <row r="842" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B842" t="s">
         <v>1534</v>
       </c>
-      <c r="B842" t="s">
-        <v>1535</v>
-      </c>
       <c r="C842" t="s">
-        <v>596</v>
+        <v>459</v>
       </c>
       <c r="D842" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F842">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="G842">
-        <v>8400</v>
+        <v>8000</v>
       </c>
       <c r="H842">
         <v>21</v>
       </c>
       <c r="I842">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J842">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K842">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L842">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M842">
         <v>0</v>
@@ -40853,10 +40868,10 @@
     </row>
     <row r="843" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B843" t="s">
         <v>1536</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1537</v>
       </c>
       <c r="C843" t="s">
         <v>596</v>
@@ -40865,10 +40880,10 @@
         <v>3</v>
       </c>
       <c r="F843">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="G843">
-        <v>9300</v>
+        <v>8400</v>
       </c>
       <c r="H843">
         <v>21</v>
@@ -40883,7 +40898,7 @@
         <v>0</v>
       </c>
       <c r="L843">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M843">
         <v>0</v>
@@ -40893,8 +40908,8 @@
       </c>
     </row>
     <row r="844" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A844">
-        <v>7798347810224</v>
+      <c r="A844" t="s">
+        <v>1537</v>
       </c>
       <c r="B844" t="s">
         <v>1538</v>
@@ -40903,28 +40918,25 @@
         <v>596</v>
       </c>
       <c r="D844" t="s">
-        <v>49</v>
-      </c>
-      <c r="E844" t="s">
-        <v>1539</v>
+        <v>3</v>
       </c>
       <c r="F844">
-        <v>3260</v>
+        <v>4300</v>
       </c>
       <c r="G844">
-        <v>9000</v>
+        <v>9300</v>
       </c>
       <c r="H844">
         <v>21</v>
       </c>
       <c r="I844">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="J844">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="K844">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="L844">
         <v>1</v>
@@ -40938,10 +40950,10 @@
     </row>
     <row r="845" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A845">
-        <v>7798347810569</v>
+        <v>7798347810224</v>
       </c>
       <c r="B845" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C845" t="s">
         <v>596</v>
@@ -40950,25 +40962,25 @@
         <v>49</v>
       </c>
       <c r="E845" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F845">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="G845">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="H845">
         <v>21</v>
       </c>
       <c r="I845">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="J845">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="K845">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="L845">
         <v>1</v>
@@ -40982,75 +40994,78 @@
     </row>
     <row r="846" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A846">
+        <v>7798347810569</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C846" t="s">
+        <v>596</v>
+      </c>
+      <c r="D846" t="s">
+        <v>49</v>
+      </c>
+      <c r="E846" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F846">
+        <v>3261</v>
+      </c>
+      <c r="G846">
+        <v>9500</v>
+      </c>
+      <c r="H846">
+        <v>21</v>
+      </c>
+      <c r="I846">
+        <v>3261</v>
+      </c>
+      <c r="J846">
+        <v>3261</v>
+      </c>
+      <c r="K846">
+        <v>3261</v>
+      </c>
+      <c r="L846">
+        <v>1</v>
+      </c>
+      <c r="M846">
+        <v>0</v>
+      </c>
+      <c r="N846">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A847">
         <v>6905416583656</v>
       </c>
-      <c r="B846" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C846" t="s">
+      <c r="B847" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C847" t="s">
         <v>421</v>
       </c>
-      <c r="F846">
+      <c r="F847">
         <v>1500</v>
       </c>
-      <c r="G846">
+      <c r="G847">
         <v>3000</v>
       </c>
-      <c r="H846">
-        <v>21</v>
-      </c>
-      <c r="I846">
+      <c r="H847">
+        <v>21</v>
+      </c>
+      <c r="I847">
         <v>1500</v>
       </c>
-      <c r="J846">
+      <c r="J847">
         <v>1500</v>
       </c>
-      <c r="K846">
+      <c r="K847">
         <v>1500</v>
       </c>
-      <c r="L846">
+      <c r="L847">
         <v>12</v>
-      </c>
-      <c r="M846">
-        <v>0</v>
-      </c>
-      <c r="N846">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="847" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A847" t="s">
-        <v>1541</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C847" t="s">
-        <v>77</v>
-      </c>
-      <c r="D847" t="s">
-        <v>49</v>
-      </c>
-      <c r="F847">
-        <v>628</v>
-      </c>
-      <c r="G847">
-        <v>2500</v>
-      </c>
-      <c r="H847">
-        <v>21</v>
-      </c>
-      <c r="I847">
-        <v>628</v>
-      </c>
-      <c r="J847">
-        <v>628</v>
-      </c>
-      <c r="K847">
-        <v>628</v>
-      </c>
-      <c r="L847">
-        <v>0</v>
       </c>
       <c r="M847">
         <v>0</v>
@@ -41061,78 +41076,78 @@
     </row>
     <row r="848" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B848" t="s">
         <v>1543</v>
       </c>
-      <c r="B848" t="s">
+      <c r="C848" t="s">
+        <v>77</v>
+      </c>
+      <c r="D848" t="s">
+        <v>49</v>
+      </c>
+      <c r="F848">
+        <v>628</v>
+      </c>
+      <c r="G848">
+        <v>2500</v>
+      </c>
+      <c r="H848">
+        <v>21</v>
+      </c>
+      <c r="I848">
+        <v>628</v>
+      </c>
+      <c r="J848">
+        <v>628</v>
+      </c>
+      <c r="K848">
+        <v>628</v>
+      </c>
+      <c r="L848">
+        <v>0</v>
+      </c>
+      <c r="M848">
+        <v>0</v>
+      </c>
+      <c r="N848">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
         <v>1544</v>
-      </c>
-      <c r="C848" t="s">
-        <v>67</v>
-      </c>
-      <c r="D848" t="s">
-        <v>28</v>
-      </c>
-      <c r="F848">
-        <v>4800</v>
-      </c>
-      <c r="G848">
-        <v>12000</v>
-      </c>
-      <c r="H848">
-        <v>21</v>
-      </c>
-      <c r="I848">
-        <v>4800</v>
-      </c>
-      <c r="J848">
-        <v>4800</v>
-      </c>
-      <c r="K848">
-        <v>4800</v>
-      </c>
-      <c r="L848">
-        <v>8</v>
-      </c>
-      <c r="M848">
-        <v>0</v>
-      </c>
-      <c r="N848">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="849" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A849">
-        <v>6459751458518</v>
       </c>
       <c r="B849" t="s">
         <v>1545</v>
       </c>
       <c r="C849" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D849" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F849">
-        <v>608</v>
+        <v>4800</v>
       </c>
       <c r="G849">
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="H849">
         <v>21</v>
       </c>
       <c r="I849">
-        <v>608</v>
+        <v>4800</v>
       </c>
       <c r="J849">
-        <v>608</v>
+        <v>4800</v>
       </c>
       <c r="K849">
-        <v>608</v>
+        <v>4800</v>
       </c>
       <c r="L849">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M849">
         <v>0</v>
@@ -41142,41 +41157,38 @@
       </c>
     </row>
     <row r="850" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A850" t="s">
+      <c r="A850">
+        <v>6459751458518</v>
+      </c>
+      <c r="B850" t="s">
         <v>1546</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1547</v>
       </c>
       <c r="C850" t="s">
         <v>74</v>
       </c>
       <c r="D850" t="s">
-        <v>31</v>
-      </c>
-      <c r="E850" t="s">
-        <v>1548</v>
+        <v>49</v>
       </c>
       <c r="F850">
-        <v>5887</v>
+        <v>608</v>
       </c>
       <c r="G850">
-        <v>18000</v>
+        <v>2500</v>
       </c>
       <c r="H850">
         <v>21</v>
       </c>
       <c r="I850">
-        <v>18000</v>
+        <v>608</v>
       </c>
       <c r="J850">
-        <v>18000</v>
+        <v>608</v>
       </c>
       <c r="K850">
-        <v>5.3</v>
+        <v>608</v>
       </c>
       <c r="L850">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M850">
         <v>0</v>
@@ -41187,10 +41199,10 @@
     </row>
     <row r="851" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B851" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C851" t="s">
         <v>74</v>
@@ -41199,25 +41211,25 @@
         <v>31</v>
       </c>
       <c r="E851" t="s">
-        <v>96</v>
+        <v>1549</v>
       </c>
       <c r="F851">
-        <v>4700</v>
+        <v>5887</v>
       </c>
       <c r="G851">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H851">
         <v>21</v>
       </c>
       <c r="I851">
-        <v>4700</v>
+        <v>18000</v>
       </c>
       <c r="J851">
-        <v>4700</v>
+        <v>18000</v>
       </c>
       <c r="K851">
-        <v>4700</v>
+        <v>5.3</v>
       </c>
       <c r="L851">
         <v>5</v>
@@ -41231,37 +41243,40 @@
     </row>
     <row r="852" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B852" t="s">
         <v>1551</v>
       </c>
-      <c r="B852" t="s">
-        <v>1552</v>
-      </c>
       <c r="C852" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D852" t="s">
         <v>31</v>
       </c>
+      <c r="E852" t="s">
+        <v>96</v>
+      </c>
       <c r="F852">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="G852">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H852">
         <v>21</v>
       </c>
       <c r="I852">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="J852">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="K852">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="L852">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M852">
         <v>0</v>
@@ -41271,35 +41286,35 @@
       </c>
     </row>
     <row r="853" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A853">
-        <v>6989526542239</v>
+      <c r="A853" t="s">
+        <v>1552</v>
       </c>
       <c r="B853" t="s">
         <v>1553</v>
       </c>
       <c r="C853" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D853" t="s">
         <v>31</v>
       </c>
       <c r="F853">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="G853">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H853">
         <v>21</v>
       </c>
       <c r="I853">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="J853">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="K853">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="L853">
         <v>1</v>
@@ -41312,38 +41327,38 @@
       </c>
     </row>
     <row r="854" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A854" t="s">
+      <c r="A854">
+        <v>6989526542239</v>
+      </c>
+      <c r="B854" t="s">
         <v>1554</v>
       </c>
-      <c r="B854" t="s">
-        <v>1555</v>
-      </c>
       <c r="C854" t="s">
-        <v>299</v>
+        <v>74</v>
       </c>
       <c r="D854" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F854">
-        <v>5200</v>
+        <v>2352</v>
       </c>
       <c r="G854">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H854">
         <v>21</v>
       </c>
       <c r="I854">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="J854">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="K854">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="L854">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="M854">
         <v>0</v>
@@ -41354,10 +41369,10 @@
     </row>
     <row r="855" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B855" t="s">
         <v>1556</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1557</v>
       </c>
       <c r="C855" t="s">
         <v>299</v>
@@ -41366,25 +41381,25 @@
         <v>3</v>
       </c>
       <c r="F855">
-        <v>3724</v>
+        <v>5200</v>
       </c>
       <c r="G855">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H855">
         <v>21</v>
       </c>
       <c r="I855">
-        <v>3724</v>
+        <v>0</v>
       </c>
       <c r="J855">
-        <v>3724</v>
+        <v>0</v>
       </c>
       <c r="K855">
-        <v>3724</v>
+        <v>0</v>
       </c>
       <c r="L855">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M855">
         <v>0</v>
@@ -41395,10 +41410,10 @@
     </row>
     <row r="856" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B856" t="s">
         <v>1558</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1559</v>
       </c>
       <c r="C856" t="s">
         <v>299</v>
@@ -41407,25 +41422,25 @@
         <v>3</v>
       </c>
       <c r="F856">
-        <v>5454</v>
+        <v>3724</v>
       </c>
       <c r="G856">
-        <v>8500</v>
+        <v>6000</v>
       </c>
       <c r="H856">
         <v>21</v>
       </c>
       <c r="I856">
-        <v>5454</v>
+        <v>3724</v>
       </c>
       <c r="J856">
-        <v>5454</v>
+        <v>3724</v>
       </c>
       <c r="K856">
-        <v>5454</v>
+        <v>3724</v>
       </c>
       <c r="L856">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M856">
         <v>0</v>
@@ -41435,35 +41450,35 @@
       </c>
     </row>
     <row r="857" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A857">
-        <v>153500580</v>
+      <c r="A857" t="s">
+        <v>1559</v>
       </c>
       <c r="B857" t="s">
         <v>1560</v>
       </c>
       <c r="C857" t="s">
-        <v>67</v>
+        <v>299</v>
       </c>
       <c r="D857" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F857">
-        <v>3934</v>
+        <v>5454</v>
       </c>
       <c r="G857">
-        <v>10000</v>
+        <v>8500</v>
       </c>
       <c r="H857">
         <v>21</v>
       </c>
       <c r="I857">
-        <v>15000</v>
+        <v>5454</v>
       </c>
       <c r="J857">
-        <v>15000</v>
+        <v>5454</v>
       </c>
       <c r="K857">
-        <v>3934</v>
+        <v>5454</v>
       </c>
       <c r="L857">
         <v>2</v>
@@ -41472,15 +41487,15 @@
         <v>0</v>
       </c>
       <c r="N857">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="858" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A858" t="s">
+      <c r="A858">
+        <v>153500580</v>
+      </c>
+      <c r="B858" t="s">
         <v>1561</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1562</v>
       </c>
       <c r="C858" t="s">
         <v>67</v>
@@ -41489,10 +41504,10 @@
         <v>31</v>
       </c>
       <c r="F858">
-        <v>4350</v>
+        <v>3934</v>
       </c>
       <c r="G858">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="H858">
         <v>21</v>
@@ -41504,10 +41519,10 @@
         <v>15000</v>
       </c>
       <c r="K858">
-        <v>4350</v>
+        <v>3934</v>
       </c>
       <c r="L858">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M858">
         <v>0</v>
@@ -41518,10 +41533,10 @@
     </row>
     <row r="859" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B859" t="s">
         <v>1563</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1564</v>
       </c>
       <c r="C859" t="s">
         <v>67</v>
@@ -41530,22 +41545,22 @@
         <v>31</v>
       </c>
       <c r="F859">
-        <v>3622</v>
+        <v>4350</v>
       </c>
       <c r="G859">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H859">
         <v>21</v>
       </c>
       <c r="I859">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="J859">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="K859">
-        <v>3622</v>
+        <v>4350</v>
       </c>
       <c r="L859">
         <v>1</v>
@@ -41554,15 +41569,15 @@
         <v>0</v>
       </c>
       <c r="N859">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="860" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B860" t="s">
         <v>1565</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1566</v>
       </c>
       <c r="C860" t="s">
         <v>67</v>
@@ -41570,14 +41585,11 @@
       <c r="D860" t="s">
         <v>31</v>
       </c>
-      <c r="E860" t="s">
-        <v>96</v>
-      </c>
       <c r="F860">
-        <v>2264</v>
+        <v>3622</v>
       </c>
       <c r="G860">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="H860">
         <v>21</v>
@@ -41589,21 +41601,21 @@
         <v>18000</v>
       </c>
       <c r="K860">
-        <v>2264</v>
+        <v>3622</v>
       </c>
       <c r="L860">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M860">
         <v>0</v>
       </c>
       <c r="N860">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="861" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A861">
-        <v>723540563780</v>
+      <c r="A861" t="s">
+        <v>1566</v>
       </c>
       <c r="B861" t="s">
         <v>1567</v>
@@ -41618,63 +41630,66 @@
         <v>96</v>
       </c>
       <c r="F861">
-        <v>18400</v>
+        <v>2264</v>
       </c>
       <c r="G861">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="H861">
         <v>21</v>
       </c>
       <c r="I861">
-        <v>18400</v>
+        <v>18000</v>
       </c>
       <c r="J861">
-        <v>18400</v>
+        <v>18000</v>
       </c>
       <c r="K861">
-        <v>18400</v>
+        <v>2264</v>
       </c>
       <c r="L861">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M861">
         <v>0</v>
       </c>
       <c r="N861">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="862" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A862" t="s">
+      <c r="A862">
+        <v>723540563780</v>
+      </c>
+      <c r="B862" t="s">
         <v>1568</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1569</v>
       </c>
       <c r="C862" t="s">
         <v>67</v>
       </c>
       <c r="D862" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="E862" t="s">
+        <v>96</v>
       </c>
       <c r="F862">
-        <v>14171</v>
+        <v>18400</v>
       </c>
       <c r="G862">
-        <v>25500</v>
+        <v>45000</v>
       </c>
       <c r="H862">
         <v>21</v>
       </c>
       <c r="I862">
-        <v>14171</v>
+        <v>18400</v>
       </c>
       <c r="J862">
-        <v>14171</v>
+        <v>18400</v>
       </c>
       <c r="K862">
-        <v>14171</v>
+        <v>18400</v>
       </c>
       <c r="L862">
         <v>1</v>
@@ -41687,8 +41702,8 @@
       </c>
     </row>
     <row r="863" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A863">
-        <v>7769528971157</v>
+      <c r="A863" t="s">
+        <v>1569</v>
       </c>
       <c r="B863" t="s">
         <v>1570</v>
@@ -41697,28 +41712,28 @@
         <v>67</v>
       </c>
       <c r="D863" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F863">
-        <v>12730</v>
+        <v>14171</v>
       </c>
       <c r="G863">
-        <v>28000</v>
+        <v>25500</v>
       </c>
       <c r="H863">
         <v>21</v>
       </c>
       <c r="I863">
-        <v>12730</v>
+        <v>14171</v>
       </c>
       <c r="J863">
-        <v>12730</v>
+        <v>14171</v>
       </c>
       <c r="K863">
-        <v>12730</v>
+        <v>14171</v>
       </c>
       <c r="L863">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M863">
         <v>0</v>
@@ -41728,11 +41743,11 @@
       </c>
     </row>
     <row r="864" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A864" t="s">
+      <c r="A864">
+        <v>7769528971157</v>
+      </c>
+      <c r="B864" t="s">
         <v>1571</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1572</v>
       </c>
       <c r="C864" t="s">
         <v>67</v>
@@ -41740,26 +41755,23 @@
       <c r="D864" t="s">
         <v>31</v>
       </c>
-      <c r="E864" t="s">
-        <v>96</v>
-      </c>
       <c r="F864">
-        <v>4523</v>
+        <v>12730</v>
       </c>
       <c r="G864">
-        <v>18000</v>
+        <v>28000</v>
       </c>
       <c r="H864">
         <v>21</v>
       </c>
       <c r="I864">
-        <v>18000</v>
+        <v>12730</v>
       </c>
       <c r="J864">
-        <v>18000</v>
+        <v>12730</v>
       </c>
       <c r="K864">
-        <v>4523</v>
+        <v>12730</v>
       </c>
       <c r="L864">
         <v>2</v>
@@ -41768,124 +41780,127 @@
         <v>0</v>
       </c>
       <c r="N864">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="865" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B865" t="s">
         <v>1573</v>
       </c>
-      <c r="B865" t="s">
+      <c r="C865" t="s">
+        <v>67</v>
+      </c>
+      <c r="D865" t="s">
+        <v>31</v>
+      </c>
+      <c r="E865" t="s">
+        <v>96</v>
+      </c>
+      <c r="F865">
+        <v>4523</v>
+      </c>
+      <c r="G865">
+        <v>18000</v>
+      </c>
+      <c r="H865">
+        <v>21</v>
+      </c>
+      <c r="I865">
+        <v>18000</v>
+      </c>
+      <c r="J865">
+        <v>18000</v>
+      </c>
+      <c r="K865">
+        <v>4523</v>
+      </c>
+      <c r="L865">
+        <v>2</v>
+      </c>
+      <c r="M865">
+        <v>0</v>
+      </c>
+      <c r="N865">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="866" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
         <v>1574</v>
-      </c>
-      <c r="C865" t="s">
-        <v>38</v>
-      </c>
-      <c r="D865" t="s">
-        <v>3</v>
-      </c>
-      <c r="F865">
-        <v>500</v>
-      </c>
-      <c r="G865">
-        <v>2000</v>
-      </c>
-      <c r="H865">
-        <v>21</v>
-      </c>
-      <c r="I865">
-        <v>500</v>
-      </c>
-      <c r="J865">
-        <v>500</v>
-      </c>
-      <c r="K865">
-        <v>500</v>
-      </c>
-      <c r="L865">
-        <v>503</v>
-      </c>
-      <c r="M865">
-        <v>0</v>
-      </c>
-      <c r="N865">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="866" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A866">
-        <v>701575361335</v>
       </c>
       <c r="B866" t="s">
         <v>1575</v>
       </c>
       <c r="C866" t="s">
+        <v>38</v>
+      </c>
+      <c r="D866" t="s">
+        <v>3</v>
+      </c>
+      <c r="F866">
+        <v>500</v>
+      </c>
+      <c r="G866">
+        <v>2000</v>
+      </c>
+      <c r="H866">
+        <v>21</v>
+      </c>
+      <c r="I866">
+        <v>500</v>
+      </c>
+      <c r="J866">
+        <v>500</v>
+      </c>
+      <c r="K866">
+        <v>500</v>
+      </c>
+      <c r="L866">
+        <v>495</v>
+      </c>
+      <c r="M866">
+        <v>0</v>
+      </c>
+      <c r="N866">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A867">
+        <v>701575361335</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C867" t="s">
         <v>641</v>
       </c>
-      <c r="D866" t="s">
+      <c r="D867" t="s">
         <v>49</v>
       </c>
-      <c r="E866" t="s">
+      <c r="E867" t="s">
         <v>713</v>
       </c>
-      <c r="F866">
+      <c r="F867">
         <v>6467</v>
       </c>
-      <c r="G866">
+      <c r="G867">
         <v>12000</v>
       </c>
-      <c r="H866">
-        <v>21</v>
-      </c>
-      <c r="I866">
+      <c r="H867">
+        <v>21</v>
+      </c>
+      <c r="I867">
         <v>6467</v>
       </c>
-      <c r="J866">
+      <c r="J867">
         <v>6467</v>
       </c>
-      <c r="K866">
+      <c r="K867">
         <v>6467</v>
-      </c>
-      <c r="L866">
-        <v>0</v>
-      </c>
-      <c r="M866">
-        <v>0</v>
-      </c>
-      <c r="N866">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="867" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A867" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B867" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C867" t="s">
-        <v>599</v>
-      </c>
-      <c r="D867" t="s">
-        <v>3</v>
-      </c>
-      <c r="F867">
-        <v>0</v>
-      </c>
-      <c r="G867">
-        <v>49280</v>
-      </c>
-      <c r="H867">
-        <v>21</v>
-      </c>
-      <c r="I867">
-        <v>0</v>
-      </c>
-      <c r="J867">
-        <v>0</v>
-      </c>
-      <c r="K867">
-        <v>0</v>
       </c>
       <c r="L867">
         <v>0</v>
@@ -41899,37 +41914,37 @@
     </row>
     <row r="868" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B868" t="s">
         <v>1578</v>
       </c>
       <c r="C868" t="s">
-        <v>58</v>
+        <v>599</v>
       </c>
       <c r="D868" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="F868">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="G868">
-        <v>35999</v>
+        <v>49280</v>
       </c>
       <c r="H868">
         <v>21</v>
       </c>
       <c r="I868">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="J868">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="K868">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="L868">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M868">
         <v>0</v>
@@ -41943,34 +41958,34 @@
         <v>1579</v>
       </c>
       <c r="B869" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="C869" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D869" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F869">
-        <v>2170.5100000000002</v>
+        <v>17200</v>
       </c>
       <c r="G869">
-        <v>4500</v>
+        <v>35999</v>
       </c>
       <c r="H869">
         <v>21</v>
       </c>
       <c r="I869">
-        <v>2170.5</v>
+        <v>17200</v>
       </c>
       <c r="J869">
-        <v>2170.5</v>
+        <v>17200</v>
       </c>
       <c r="K869">
-        <v>2170.5</v>
+        <v>17200</v>
       </c>
       <c r="L869">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M869">
         <v>0</v>
@@ -41981,10 +41996,10 @@
     </row>
     <row r="870" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B870" t="s">
         <v>1581</v>
-      </c>
-      <c r="B870" t="s">
-        <v>1582</v>
       </c>
       <c r="C870" t="s">
         <v>20</v>
@@ -41993,22 +42008,22 @@
         <v>49</v>
       </c>
       <c r="F870">
-        <v>3613.61</v>
+        <v>2170.5100000000002</v>
       </c>
       <c r="G870">
-        <v>7500</v>
+        <v>4500</v>
       </c>
       <c r="H870">
         <v>21</v>
       </c>
       <c r="I870">
-        <v>3613.6</v>
+        <v>2170.5</v>
       </c>
       <c r="J870">
-        <v>3613.6</v>
+        <v>2170.5</v>
       </c>
       <c r="K870">
-        <v>3613.6</v>
+        <v>2170.5</v>
       </c>
       <c r="L870">
         <v>0</v>
@@ -42022,34 +42037,34 @@
     </row>
     <row r="871" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B871" t="s">
         <v>1583</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1584</v>
       </c>
       <c r="C871" t="s">
         <v>20</v>
       </c>
       <c r="D871" t="s">
-        <v>294</v>
+        <v>49</v>
       </c>
       <c r="F871">
-        <v>4000</v>
+        <v>3613.61</v>
       </c>
       <c r="G871">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="H871">
         <v>21</v>
       </c>
       <c r="I871">
-        <v>4000</v>
+        <v>3613.6</v>
       </c>
       <c r="J871">
-        <v>4000</v>
+        <v>3613.6</v>
       </c>
       <c r="K871">
-        <v>4000</v>
+        <v>3613.6</v>
       </c>
       <c r="L871">
         <v>0</v>
@@ -42063,89 +42078,130 @@
     </row>
     <row r="872" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B872" t="s">
         <v>1585</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1586</v>
       </c>
       <c r="C872" t="s">
         <v>20</v>
       </c>
       <c r="D872" t="s">
+        <v>294</v>
+      </c>
+      <c r="F872">
+        <v>4000</v>
+      </c>
+      <c r="G872">
+        <v>10000</v>
+      </c>
+      <c r="H872">
+        <v>21</v>
+      </c>
+      <c r="I872">
+        <v>4000</v>
+      </c>
+      <c r="J872">
+        <v>4000</v>
+      </c>
+      <c r="K872">
+        <v>4000</v>
+      </c>
+      <c r="L872">
+        <v>0</v>
+      </c>
+      <c r="M872">
+        <v>0</v>
+      </c>
+      <c r="N872">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C873" t="s">
+        <v>20</v>
+      </c>
+      <c r="D873" t="s">
         <v>49</v>
       </c>
-      <c r="E872" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F872">
+      <c r="E873" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F873">
         <v>4588</v>
       </c>
-      <c r="G872">
+      <c r="G873">
         <v>13000</v>
       </c>
-      <c r="H872">
-        <v>21</v>
-      </c>
-      <c r="I872">
+      <c r="H873">
+        <v>21</v>
+      </c>
+      <c r="I873">
         <v>4588</v>
       </c>
-      <c r="J872">
+      <c r="J873">
         <v>4588</v>
       </c>
-      <c r="K872">
+      <c r="K873">
         <v>4588</v>
       </c>
-      <c r="L872">
-        <v>0</v>
-      </c>
-      <c r="M872">
-        <v>0</v>
-      </c>
-      <c r="N872">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="873" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A873">
+      <c r="L873">
+        <v>0</v>
+      </c>
+      <c r="M873">
+        <v>0</v>
+      </c>
+      <c r="N873">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A874">
         <v>7796941141133</v>
       </c>
-      <c r="B873" t="s">
-        <v>1588</v>
-      </c>
-      <c r="C873" t="s">
+      <c r="B874" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C874" t="s">
         <v>508</v>
       </c>
-      <c r="D873" t="s">
+      <c r="D874" t="s">
         <v>517</v>
       </c>
-      <c r="E873" t="s">
+      <c r="E874" t="s">
         <v>96</v>
       </c>
-      <c r="F873">
+      <c r="F874">
         <v>107999</v>
       </c>
-      <c r="G873">
+      <c r="G874">
         <v>280000</v>
       </c>
-      <c r="H873">
-        <v>21</v>
-      </c>
-      <c r="I873">
+      <c r="H874">
+        <v>21</v>
+      </c>
+      <c r="I874">
         <v>190000</v>
       </c>
-      <c r="J873">
+      <c r="J874">
         <v>107999</v>
       </c>
-      <c r="K873">
+      <c r="K874">
         <v>107999</v>
       </c>
-      <c r="L873">
-        <v>0</v>
-      </c>
-      <c r="M873">
-        <v>0</v>
-      </c>
-      <c r="N873">
+      <c r="L874">
+        <v>0</v>
+      </c>
+      <c r="M874">
+        <v>0</v>
+      </c>
+      <c r="N874">
         <v>0</v>
       </c>
     </row>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71636884-B06B-48DD-999F-B46BFCE45374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A26CE0A-4A29-498B-B07F-09156A8FE0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{61C182AC-C284-49DF-BFF8-6DDEB259F2F3}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{2F3154D7-C458-4F9E-8DE4-3CBF0B026EFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5296,7 +5296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57B58E8-B95F-4A8C-941D-28A6DCFA7979}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D83099-706C-457D-B63D-740C418E3342}">
   <dimension ref="A1:N893"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -9707,13 +9707,13 @@
         <v>21</v>
       </c>
       <c r="I105">
-        <v>673</v>
+        <v>15000</v>
       </c>
       <c r="J105">
-        <v>673</v>
+        <v>8000</v>
       </c>
       <c r="K105">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="L105">
         <v>3</v>
@@ -9751,10 +9751,10 @@
         <v>21</v>
       </c>
       <c r="I106">
-        <v>2900</v>
+        <v>25000</v>
       </c>
       <c r="J106">
-        <v>2900</v>
+        <v>12000</v>
       </c>
       <c r="K106">
         <v>12000</v>
@@ -9795,10 +9795,10 @@
         <v>21</v>
       </c>
       <c r="I107">
-        <v>5200</v>
+        <v>24000</v>
       </c>
       <c r="J107">
-        <v>5200</v>
+        <v>15000</v>
       </c>
       <c r="K107">
         <v>15000</v>
@@ -9839,10 +9839,10 @@
         <v>21</v>
       </c>
       <c r="I108">
-        <v>6061</v>
+        <v>28000</v>
       </c>
       <c r="J108">
-        <v>6061</v>
+        <v>15000</v>
       </c>
       <c r="K108">
         <v>15000</v>
@@ -9883,10 +9883,10 @@
         <v>21</v>
       </c>
       <c r="I109">
-        <v>4800</v>
+        <v>24000</v>
       </c>
       <c r="J109">
-        <v>4800</v>
+        <v>15000</v>
       </c>
       <c r="K109">
         <v>15000</v>
@@ -9971,10 +9971,10 @@
         <v>21</v>
       </c>
       <c r="I111">
-        <v>5300</v>
+        <v>24000</v>
       </c>
       <c r="J111">
-        <v>5300</v>
+        <v>15000</v>
       </c>
       <c r="K111">
         <v>15000</v>
@@ -10012,10 +10012,10 @@
         <v>21</v>
       </c>
       <c r="I112">
-        <v>9454</v>
+        <v>30000</v>
       </c>
       <c r="J112">
-        <v>9454</v>
+        <v>18000</v>
       </c>
       <c r="K112">
         <v>18000</v>
@@ -10053,13 +10053,13 @@
         <v>21</v>
       </c>
       <c r="I113">
-        <v>5600</v>
+        <v>20000</v>
       </c>
       <c r="J113">
-        <v>5600</v>
+        <v>10000</v>
       </c>
       <c r="K113">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="L113">
         <v>1</v>
@@ -10091,16 +10091,16 @@
         <v>6625</v>
       </c>
       <c r="G114">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H114">
         <v>21</v>
       </c>
       <c r="I114">
-        <v>6625</v>
+        <v>30000</v>
       </c>
       <c r="J114">
-        <v>6625</v>
+        <v>12000</v>
       </c>
       <c r="K114">
         <v>12000</v>
@@ -10132,19 +10132,19 @@
         <v>7037.5</v>
       </c>
       <c r="G115">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H115">
         <v>21</v>
       </c>
       <c r="I115">
-        <v>7037.5</v>
+        <v>30000</v>
       </c>
       <c r="J115">
-        <v>7037.5</v>
+        <v>16000</v>
       </c>
       <c r="K115">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="L115">
         <v>2</v>
@@ -10176,16 +10176,16 @@
         <v>6600</v>
       </c>
       <c r="G116">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H116">
         <v>21</v>
       </c>
       <c r="I116">
-        <v>6600</v>
+        <v>30000</v>
       </c>
       <c r="J116">
-        <v>6600</v>
+        <v>15000</v>
       </c>
       <c r="K116">
         <v>15000</v>
@@ -10220,16 +10220,16 @@
         <v>8100</v>
       </c>
       <c r="G117">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H117">
         <v>21</v>
       </c>
       <c r="I117">
-        <v>8100</v>
+        <v>30000</v>
       </c>
       <c r="J117">
-        <v>8100</v>
+        <v>18000</v>
       </c>
       <c r="K117">
         <v>18000</v>
@@ -10270,10 +10270,10 @@
         <v>21</v>
       </c>
       <c r="I118">
-        <v>6815</v>
+        <v>30000</v>
       </c>
       <c r="J118">
-        <v>6815</v>
+        <v>18000</v>
       </c>
       <c r="K118">
         <v>18000</v>
@@ -10308,16 +10308,16 @@
         <v>7817</v>
       </c>
       <c r="G119">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H119">
         <v>21</v>
       </c>
       <c r="I119">
-        <v>7817</v>
+        <v>30000</v>
       </c>
       <c r="J119">
-        <v>7817</v>
+        <v>18000</v>
       </c>
       <c r="K119">
         <v>18000</v>
@@ -10349,16 +10349,16 @@
         <v>7995</v>
       </c>
       <c r="G120">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H120">
         <v>21</v>
       </c>
       <c r="I120">
-        <v>7995</v>
+        <v>30000</v>
       </c>
       <c r="J120">
-        <v>7995</v>
+        <v>18000</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -10487,10 +10487,10 @@
         <v>21</v>
       </c>
       <c r="I123">
-        <v>805</v>
+        <v>6000</v>
       </c>
       <c r="J123">
-        <v>805</v>
+        <v>6000</v>
       </c>
       <c r="K123">
         <v>6000</v>
@@ -10528,10 +10528,10 @@
         <v>21</v>
       </c>
       <c r="I124">
-        <v>2099</v>
+        <v>6000</v>
       </c>
       <c r="J124">
-        <v>2099</v>
+        <v>5000</v>
       </c>
       <c r="K124">
         <v>4500</v>
@@ -10563,19 +10563,19 @@
         <v>9030</v>
       </c>
       <c r="G125">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H125">
         <v>21</v>
       </c>
       <c r="I125">
-        <v>9030</v>
+        <v>30000</v>
       </c>
       <c r="J125">
-        <v>9030</v>
+        <v>18000</v>
       </c>
       <c r="K125">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="L125">
         <v>2</v>
@@ -10648,16 +10648,16 @@
         <v>9030</v>
       </c>
       <c r="G127">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H127">
         <v>21</v>
       </c>
       <c r="I127">
-        <v>9030</v>
+        <v>30000</v>
       </c>
       <c r="J127">
-        <v>9030</v>
+        <v>18000</v>
       </c>
       <c r="K127">
         <v>18000</v>
@@ -10698,10 +10698,10 @@
         <v>21</v>
       </c>
       <c r="I128">
-        <v>7511</v>
+        <v>30000</v>
       </c>
       <c r="J128">
-        <v>7511</v>
+        <v>18000</v>
       </c>
       <c r="K128">
         <v>18000</v>
@@ -10742,10 +10742,10 @@
         <v>21</v>
       </c>
       <c r="I129">
-        <v>9135</v>
+        <v>30000</v>
       </c>
       <c r="J129">
-        <v>9135</v>
+        <v>18000</v>
       </c>
       <c r="K129">
         <v>18000</v>
@@ -10786,10 +10786,10 @@
         <v>21</v>
       </c>
       <c r="I130">
-        <v>8482</v>
+        <v>30000</v>
       </c>
       <c r="J130">
-        <v>8482</v>
+        <v>18000</v>
       </c>
       <c r="K130">
         <v>18000</v>
@@ -10830,10 +10830,10 @@
         <v>21</v>
       </c>
       <c r="I131">
-        <v>9323</v>
+        <v>30000</v>
       </c>
       <c r="J131">
-        <v>9323</v>
+        <v>18000</v>
       </c>
       <c r="K131">
         <v>18000</v>
@@ -10868,16 +10868,16 @@
         <v>7192</v>
       </c>
       <c r="G132">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H132">
         <v>21</v>
       </c>
       <c r="I132">
-        <v>7192</v>
+        <v>30000</v>
       </c>
       <c r="J132">
-        <v>7192</v>
+        <v>18000</v>
       </c>
       <c r="K132">
         <v>18000</v>
@@ -10912,16 +10912,16 @@
         <v>7096</v>
       </c>
       <c r="G133">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H133">
         <v>21</v>
       </c>
       <c r="I133">
-        <v>7096</v>
+        <v>30000</v>
       </c>
       <c r="J133">
-        <v>7096</v>
+        <v>18000</v>
       </c>
       <c r="K133">
         <v>18000</v>
@@ -11000,19 +11000,19 @@
         <v>4538</v>
       </c>
       <c r="G135">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H135">
         <v>21</v>
       </c>
       <c r="I135">
-        <v>4538</v>
+        <v>30000</v>
       </c>
       <c r="J135">
-        <v>4538</v>
+        <v>15000</v>
       </c>
       <c r="K135">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="L135">
         <v>3</v>
@@ -11044,16 +11044,16 @@
         <v>8550</v>
       </c>
       <c r="G136">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H136">
         <v>21</v>
       </c>
       <c r="I136">
-        <v>8550</v>
+        <v>30000</v>
       </c>
       <c r="J136">
-        <v>8550</v>
+        <v>18000</v>
       </c>
       <c r="K136">
         <v>18000</v>
@@ -11135,10 +11135,10 @@
         <v>21</v>
       </c>
       <c r="I138">
-        <v>2762</v>
+        <v>15000</v>
       </c>
       <c r="J138">
-        <v>2762</v>
+        <v>8000</v>
       </c>
       <c r="K138">
         <v>8000</v>
@@ -11258,10 +11258,10 @@
         <v>21</v>
       </c>
       <c r="I141">
-        <v>4735.5</v>
+        <v>15000</v>
       </c>
       <c r="J141">
-        <v>4735.5</v>
+        <v>10000</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -11299,10 +11299,10 @@
         <v>21</v>
       </c>
       <c r="I142">
-        <v>6765</v>
+        <v>18000</v>
       </c>
       <c r="J142">
-        <v>6765</v>
+        <v>14000</v>
       </c>
       <c r="K142">
         <v>14000</v>
@@ -11387,10 +11387,10 @@
         <v>21</v>
       </c>
       <c r="I144">
-        <v>7621</v>
+        <v>30000</v>
       </c>
       <c r="J144">
-        <v>7621</v>
+        <v>18000</v>
       </c>
       <c r="K144">
         <v>18000</v>
@@ -11431,10 +11431,10 @@
         <v>21</v>
       </c>
       <c r="I145">
-        <v>8135</v>
+        <v>30000</v>
       </c>
       <c r="J145">
-        <v>8135</v>
+        <v>18000</v>
       </c>
       <c r="K145">
         <v>18000</v>
@@ -18602,16 +18602,16 @@
         <v>1500</v>
       </c>
       <c r="G315">
-        <v>3001</v>
+        <v>3800</v>
       </c>
       <c r="H315">
         <v>21</v>
       </c>
       <c r="I315">
-        <v>1500</v>
+        <v>3800</v>
       </c>
       <c r="J315">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="K315">
         <v>3000</v>
@@ -18763,13 +18763,13 @@
         <v>1435</v>
       </c>
       <c r="G319">
-        <v>6501</v>
+        <v>7500</v>
       </c>
       <c r="H319">
         <v>21</v>
       </c>
       <c r="I319">
-        <v>6501</v>
+        <v>7500</v>
       </c>
       <c r="J319">
         <v>6500</v>
@@ -18804,13 +18804,13 @@
         <v>2009</v>
       </c>
       <c r="G320">
-        <v>7501</v>
+        <v>9000</v>
       </c>
       <c r="H320">
         <v>21</v>
       </c>
       <c r="I320">
-        <v>7501</v>
+        <v>9000</v>
       </c>
       <c r="J320">
         <v>7500</v>
@@ -24218,7 +24218,7 @@
         <v>21000</v>
       </c>
       <c r="L450">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M450">
         <v>0</v>
@@ -27038,7 +27038,7 @@
         <v>18000</v>
       </c>
       <c r="L516">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M516">
         <v>0</v>
@@ -32796,13 +32796,13 @@
         <v>4428</v>
       </c>
       <c r="G650">
-        <v>9001</v>
+        <v>12000</v>
       </c>
       <c r="H650">
         <v>21</v>
       </c>
       <c r="I650">
-        <v>9001</v>
+        <v>12000</v>
       </c>
       <c r="J650">
         <v>9000</v>
@@ -32837,13 +32837,13 @@
         <v>2993</v>
       </c>
       <c r="G651">
-        <v>8001</v>
+        <v>10000</v>
       </c>
       <c r="H651">
         <v>21</v>
       </c>
       <c r="I651">
-        <v>8001</v>
+        <v>10000</v>
       </c>
       <c r="J651">
         <v>8000</v>
@@ -38073,16 +38073,16 @@
         <v>2830</v>
       </c>
       <c r="G773">
-        <v>9001</v>
+        <v>12000</v>
       </c>
       <c r="H773">
         <v>21</v>
       </c>
       <c r="I773">
-        <v>2830</v>
+        <v>12000</v>
       </c>
       <c r="J773">
-        <v>2830</v>
+        <v>9000</v>
       </c>
       <c r="K773">
         <v>9000</v>
@@ -38114,16 +38114,16 @@
         <v>820</v>
       </c>
       <c r="G774">
-        <v>4501</v>
+        <v>5000</v>
       </c>
       <c r="H774">
         <v>21</v>
       </c>
       <c r="I774">
-        <v>820</v>
+        <v>5000</v>
       </c>
       <c r="J774">
-        <v>820</v>
+        <v>4500</v>
       </c>
       <c r="K774">
         <v>4500</v>
@@ -40786,16 +40786,16 @@
         <v>2264</v>
       </c>
       <c r="G838">
-        <v>8001</v>
+        <v>10000</v>
       </c>
       <c r="H838">
         <v>21</v>
       </c>
       <c r="I838">
-        <v>2264</v>
+        <v>10000</v>
       </c>
       <c r="J838">
-        <v>2264</v>
+        <v>8000</v>
       </c>
       <c r="K838">
         <v>8000</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A26CE0A-4A29-498B-B07F-09156A8FE0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03E5479C-6C3D-4F29-923E-82FCAD8D20C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{2F3154D7-C458-4F9E-8DE4-3CBF0B026EFA}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{352FE51E-53C9-49BA-A3EF-541F71FD502F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5296,7 +5296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D83099-706C-457D-B63D-740C418E3342}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB2AF6D-3333-4B96-B535-A1C65EFF3F15}">
   <dimension ref="A1:N893"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E62DCC22-7EC4-4352-9B8D-C612F2B19FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9738B03-6A6D-427D-8914-A88F88A20941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{A4429479-57D4-40BC-8D41-7118A80D051A}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{0819042F-7139-4CA2-996A-48BC38279A09}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4691,6 +4691,12 @@
     <t>TENSIOMETRO DIGITAL MEDIDOR DE PRESION</t>
   </si>
   <si>
+    <t>HOTER8194</t>
+  </si>
+  <si>
+    <t>TERMO CHIMARRITA</t>
+  </si>
+  <si>
     <t>HOTER6908</t>
   </si>
   <si>
@@ -4833,12 +4839,6 @@
   </si>
   <si>
     <t>TRIPODE PARA CELULAR CON FLASH</t>
-  </si>
-  <si>
-    <t>HOTER8194</t>
-  </si>
-  <si>
-    <t>Termo Chimarrita</t>
   </si>
   <si>
     <t>HOTER9828</t>
@@ -5308,7 +5308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B3A81E-AAC0-4F7F-A7FF-46FA76A6AC72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86D5866-FEB1-41B4-AAAD-77F01D2755E3}">
   <dimension ref="A1:N895"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -26924,7 +26924,7 @@
         <v>18000</v>
       </c>
       <c r="L513">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M513">
         <v>0</v>
@@ -29138,7 +29138,7 @@
         <v>55000</v>
       </c>
       <c r="L564">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M564">
         <v>0</v>
@@ -29950,7 +29950,7 @@
         <v>23000</v>
       </c>
       <c r="L583">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M583">
         <v>0</v>
@@ -31630,7 +31630,7 @@
         <v>33000</v>
       </c>
       <c r="L622">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M622">
         <v>0</v>
@@ -41108,31 +41108,31 @@
         <v>1551</v>
       </c>
       <c r="C846" t="s">
-        <v>58</v>
+        <v>294</v>
       </c>
       <c r="D846" t="s">
         <v>3</v>
       </c>
       <c r="F846">
-        <v>17496</v>
+        <v>7000</v>
       </c>
       <c r="G846">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="H846">
         <v>21</v>
       </c>
       <c r="I846">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J846">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K846">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="L846">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="M846">
         <v>0</v>
@@ -41149,72 +41149,72 @@
         <v>1553</v>
       </c>
       <c r="C847" t="s">
+        <v>58</v>
+      </c>
+      <c r="D847" t="s">
+        <v>3</v>
+      </c>
+      <c r="F847">
+        <v>17496</v>
+      </c>
+      <c r="G847">
+        <v>35000</v>
+      </c>
+      <c r="H847">
+        <v>21</v>
+      </c>
+      <c r="I847">
+        <v>0</v>
+      </c>
+      <c r="J847">
+        <v>0</v>
+      </c>
+      <c r="K847">
+        <v>0</v>
+      </c>
+      <c r="L847">
+        <v>3</v>
+      </c>
+      <c r="M847">
+        <v>0</v>
+      </c>
+      <c r="N847">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848" spans="1:14">
+      <c r="A848" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C848" t="s">
         <v>417</v>
       </c>
-      <c r="D847" t="s">
+      <c r="D848" t="s">
         <v>31</v>
       </c>
-      <c r="F847">
+      <c r="F848">
         <v>1150</v>
       </c>
-      <c r="G847">
+      <c r="G848">
         <v>3000</v>
       </c>
-      <c r="H847">
-        <v>21</v>
-      </c>
-      <c r="I847">
+      <c r="H848">
+        <v>21</v>
+      </c>
+      <c r="I848">
         <v>1150</v>
       </c>
-      <c r="J847">
+      <c r="J848">
         <v>1150</v>
       </c>
-      <c r="K847">
+      <c r="K848">
         <v>1150</v>
       </c>
-      <c r="L847">
+      <c r="L848">
         <v>5</v>
-      </c>
-      <c r="M847">
-        <v>0</v>
-      </c>
-      <c r="N847">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="848" spans="1:14">
-      <c r="A848">
-        <v>7798423541356</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C848" t="s">
-        <v>77</v>
-      </c>
-      <c r="D848" t="s">
-        <v>135</v>
-      </c>
-      <c r="F848">
-        <v>4100</v>
-      </c>
-      <c r="G848">
-        <v>9500</v>
-      </c>
-      <c r="H848">
-        <v>21</v>
-      </c>
-      <c r="I848">
-        <v>4100</v>
-      </c>
-      <c r="J848">
-        <v>4100</v>
-      </c>
-      <c r="K848">
-        <v>4100</v>
-      </c>
-      <c r="L848">
-        <v>1</v>
       </c>
       <c r="M848">
         <v>0</v>
@@ -41225,81 +41225,78 @@
     </row>
     <row r="849" spans="1:14">
       <c r="A849">
-        <v>7798145006027</v>
+        <v>7798423541356</v>
       </c>
       <c r="B849" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C849" t="s">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="D849" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F849">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="G849">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="H849">
         <v>21</v>
       </c>
       <c r="I849">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="J849">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="K849">
-        <v>2239</v>
+        <v>4100</v>
       </c>
       <c r="L849">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M849">
         <v>0</v>
       </c>
       <c r="N849">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:14">
       <c r="A850">
-        <v>69855646885262</v>
+        <v>7798145006027</v>
       </c>
       <c r="B850" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C850" t="s">
         <v>502</v>
       </c>
       <c r="D850" t="s">
-        <v>31</v>
-      </c>
-      <c r="E850" t="s">
-        <v>1557</v>
+        <v>3</v>
       </c>
       <c r="F850">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="G850">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H850">
         <v>21</v>
       </c>
       <c r="I850">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="J850">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="K850">
-        <v>2629</v>
+        <v>2239</v>
       </c>
       <c r="L850">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M850">
         <v>0</v>
@@ -41310,7 +41307,7 @@
     </row>
     <row r="851" spans="1:14">
       <c r="A851">
-        <v>6985564688526</v>
+        <v>69855646885262</v>
       </c>
       <c r="B851" t="s">
         <v>1558</v>
@@ -41322,7 +41319,7 @@
         <v>31</v>
       </c>
       <c r="E851" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="F851">
         <v>2629</v>
@@ -41343,7 +41340,7 @@
         <v>2629</v>
       </c>
       <c r="L851">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M851">
         <v>0</v>
@@ -41354,34 +41351,37 @@
     </row>
     <row r="852" spans="1:14">
       <c r="A852">
-        <v>7790000111020</v>
+        <v>6985564688526</v>
       </c>
       <c r="B852" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C852" t="s">
+        <v>502</v>
+      </c>
+      <c r="D852" t="s">
+        <v>31</v>
+      </c>
+      <c r="E852" t="s">
         <v>1559</v>
       </c>
-      <c r="C852" t="s">
-        <v>417</v>
-      </c>
-      <c r="D852" t="s">
-        <v>3</v>
-      </c>
       <c r="F852">
-        <v>1200</v>
+        <v>2629</v>
       </c>
       <c r="G852">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H852">
         <v>21</v>
       </c>
       <c r="I852">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="J852">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="K852">
-        <v>0</v>
+        <v>2629</v>
       </c>
       <c r="L852">
         <v>4</v>
@@ -41390,83 +41390,83 @@
         <v>0</v>
       </c>
       <c r="N852">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="853" spans="1:14">
       <c r="A853">
+        <v>7790000111020</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C853" t="s">
+        <v>417</v>
+      </c>
+      <c r="D853" t="s">
+        <v>3</v>
+      </c>
+      <c r="F853">
+        <v>1200</v>
+      </c>
+      <c r="G853">
+        <v>5000</v>
+      </c>
+      <c r="H853">
+        <v>21</v>
+      </c>
+      <c r="I853">
+        <v>0</v>
+      </c>
+      <c r="J853">
+        <v>0</v>
+      </c>
+      <c r="K853">
+        <v>0</v>
+      </c>
+      <c r="L853">
+        <v>4</v>
+      </c>
+      <c r="M853">
+        <v>0</v>
+      </c>
+      <c r="N853">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854" spans="1:14">
+      <c r="A854">
         <v>6920220096888</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C853" t="s">
-        <v>53</v>
-      </c>
-      <c r="D853" t="s">
-        <v>49</v>
-      </c>
-      <c r="F853">
-        <v>4800</v>
-      </c>
-      <c r="G853">
-        <v>9600</v>
-      </c>
-      <c r="H853">
-        <v>21</v>
-      </c>
-      <c r="I853">
-        <v>4800</v>
-      </c>
-      <c r="J853">
-        <v>4800</v>
-      </c>
-      <c r="K853">
-        <v>4800</v>
-      </c>
-      <c r="L853">
-        <v>0</v>
-      </c>
-      <c r="M853">
-        <v>0</v>
-      </c>
-      <c r="N853">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="854" spans="1:14">
-      <c r="A854" t="s">
-        <v>1561</v>
       </c>
       <c r="B854" t="s">
         <v>1562</v>
       </c>
       <c r="C854" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D854" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F854">
-        <v>3615</v>
+        <v>4800</v>
       </c>
       <c r="G854">
-        <v>9000</v>
+        <v>9600</v>
       </c>
       <c r="H854">
         <v>21</v>
       </c>
       <c r="I854">
-        <v>9000</v>
+        <v>4800</v>
       </c>
       <c r="J854">
-        <v>5800</v>
+        <v>4800</v>
       </c>
       <c r="K854">
-        <v>3615</v>
+        <v>4800</v>
       </c>
       <c r="L854">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M854">
         <v>0</v>
@@ -41476,11 +41476,11 @@
       </c>
     </row>
     <row r="855" spans="1:14">
-      <c r="A855">
-        <v>7795234526572</v>
+      <c r="A855" t="s">
+        <v>1563</v>
       </c>
       <c r="B855" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C855" t="s">
         <v>67</v>
@@ -41489,25 +41489,25 @@
         <v>31</v>
       </c>
       <c r="F855">
-        <v>4126</v>
+        <v>3615</v>
       </c>
       <c r="G855">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H855">
         <v>21</v>
       </c>
       <c r="I855">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="J855">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="K855">
-        <v>4126</v>
+        <v>3615</v>
       </c>
       <c r="L855">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M855">
         <v>0</v>
@@ -41517,8 +41517,8 @@
       </c>
     </row>
     <row r="856" spans="1:14">
-      <c r="A856" t="s">
-        <v>1564</v>
+      <c r="A856">
+        <v>7795234526572</v>
       </c>
       <c r="B856" t="s">
         <v>1565</v>
@@ -41530,25 +41530,25 @@
         <v>31</v>
       </c>
       <c r="F856">
-        <v>6400</v>
+        <v>4126</v>
       </c>
       <c r="G856">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H856">
         <v>21</v>
       </c>
       <c r="I856">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="J856">
-        <v>9600</v>
+        <v>6200</v>
       </c>
       <c r="K856">
-        <v>6400</v>
+        <v>4126</v>
       </c>
       <c r="L856">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M856">
         <v>0</v>
@@ -41571,25 +41571,25 @@
         <v>31</v>
       </c>
       <c r="F857">
-        <v>7245</v>
+        <v>6400</v>
       </c>
       <c r="G857">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H857">
         <v>21</v>
       </c>
       <c r="I857">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="J857">
-        <v>12000</v>
+        <v>9600</v>
       </c>
       <c r="K857">
-        <v>7245</v>
+        <v>6400</v>
       </c>
       <c r="L857">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M857">
         <v>0</v>
@@ -41606,31 +41606,31 @@
         <v>1569</v>
       </c>
       <c r="C858" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="D858" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F858">
-        <v>15900</v>
+        <v>7245</v>
       </c>
       <c r="G858">
-        <v>45000</v>
+        <v>26000</v>
       </c>
       <c r="H858">
         <v>21</v>
       </c>
       <c r="I858">
-        <v>15900</v>
+        <v>26000</v>
       </c>
       <c r="J858">
-        <v>15900</v>
+        <v>12000</v>
       </c>
       <c r="K858">
-        <v>15900</v>
+        <v>7245</v>
       </c>
       <c r="L858">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M858">
         <v>0</v>
@@ -41650,28 +41650,28 @@
         <v>302</v>
       </c>
       <c r="D859" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F859">
-        <v>6815</v>
+        <v>15900</v>
       </c>
       <c r="G859">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="H859">
         <v>21</v>
       </c>
       <c r="I859">
-        <v>20000</v>
+        <v>15900</v>
       </c>
       <c r="J859">
-        <v>20000</v>
+        <v>15900</v>
       </c>
       <c r="K859">
-        <v>6815</v>
+        <v>15900</v>
       </c>
       <c r="L859">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M859">
         <v>0</v>
@@ -41681,35 +41681,35 @@
       </c>
     </row>
     <row r="860" spans="1:14">
-      <c r="A860">
-        <v>6902540752361</v>
+      <c r="A860" t="s">
+        <v>1572</v>
       </c>
       <c r="B860" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="C860" t="s">
         <v>302</v>
       </c>
       <c r="D860" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="F860">
-        <v>5800</v>
+        <v>6815</v>
       </c>
       <c r="G860">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H860">
         <v>21</v>
       </c>
       <c r="I860">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="J860">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="K860">
-        <v>5800</v>
+        <v>6815</v>
       </c>
       <c r="L860">
         <v>1</v>
@@ -41722,23 +41722,23 @@
       </c>
     </row>
     <row r="861" spans="1:14">
-      <c r="A861" t="s">
-        <v>1573</v>
+      <c r="A861">
+        <v>6902540752361</v>
       </c>
       <c r="B861" t="s">
         <v>1574</v>
       </c>
       <c r="C861" t="s">
-        <v>58</v>
+        <v>302</v>
       </c>
       <c r="D861" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F861">
+        <v>5800</v>
+      </c>
+      <c r="G861">
         <v>15000</v>
-      </c>
-      <c r="G861">
-        <v>35000</v>
       </c>
       <c r="H861">
         <v>21</v>
@@ -41750,7 +41750,7 @@
         <v>15000</v>
       </c>
       <c r="K861">
-        <v>15000</v>
+        <v>5800</v>
       </c>
       <c r="L861">
         <v>1</v>
@@ -41763,52 +41763,49 @@
       </c>
     </row>
     <row r="862" spans="1:14">
-      <c r="A862">
+      <c r="A862" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C862" t="s">
+        <v>58</v>
+      </c>
+      <c r="D862" t="s">
+        <v>3</v>
+      </c>
+      <c r="F862">
+        <v>15000</v>
+      </c>
+      <c r="G862">
+        <v>35000</v>
+      </c>
+      <c r="H862">
+        <v>21</v>
+      </c>
+      <c r="I862">
+        <v>15000</v>
+      </c>
+      <c r="J862">
+        <v>15000</v>
+      </c>
+      <c r="K862">
+        <v>15000</v>
+      </c>
+      <c r="L862">
+        <v>1</v>
+      </c>
+      <c r="M862">
+        <v>0</v>
+      </c>
+      <c r="N862">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="1:14">
+      <c r="A863">
         <v>723540564022</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C862" t="s">
-        <v>455</v>
-      </c>
-      <c r="D862" t="s">
-        <v>31</v>
-      </c>
-      <c r="E862" t="s">
-        <v>142</v>
-      </c>
-      <c r="F862">
-        <v>3175</v>
-      </c>
-      <c r="G862">
-        <v>9500</v>
-      </c>
-      <c r="H862">
-        <v>21</v>
-      </c>
-      <c r="I862">
-        <v>3175</v>
-      </c>
-      <c r="J862">
-        <v>3175</v>
-      </c>
-      <c r="K862">
-        <v>3175</v>
-      </c>
-      <c r="L862">
-        <v>2</v>
-      </c>
-      <c r="M862">
-        <v>0</v>
-      </c>
-      <c r="N862">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863" spans="1:14">
-      <c r="A863" t="s">
-        <v>1576</v>
       </c>
       <c r="B863" t="s">
         <v>1577</v>
@@ -41817,28 +41814,31 @@
         <v>455</v>
       </c>
       <c r="D863" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="E863" t="s">
+        <v>142</v>
       </c>
       <c r="F863">
-        <v>2000</v>
+        <v>3175</v>
       </c>
       <c r="G863">
-        <v>8000</v>
+        <v>9500</v>
       </c>
       <c r="H863">
         <v>21</v>
       </c>
       <c r="I863">
-        <v>8000</v>
+        <v>3175</v>
       </c>
       <c r="J863">
-        <v>8000</v>
+        <v>3175</v>
       </c>
       <c r="K863">
-        <v>2000</v>
+        <v>3175</v>
       </c>
       <c r="L863">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M863">
         <v>0</v>
@@ -41855,31 +41855,31 @@
         <v>1579</v>
       </c>
       <c r="C864" t="s">
-        <v>587</v>
+        <v>455</v>
       </c>
       <c r="D864" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F864">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="G864">
-        <v>8400</v>
+        <v>8000</v>
       </c>
       <c r="H864">
         <v>21</v>
       </c>
       <c r="I864">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J864">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K864">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L864">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M864">
         <v>0</v>
@@ -41902,10 +41902,10 @@
         <v>3</v>
       </c>
       <c r="F865">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="G865">
-        <v>9300</v>
+        <v>8400</v>
       </c>
       <c r="H865">
         <v>21</v>
@@ -41920,7 +41920,7 @@
         <v>0</v>
       </c>
       <c r="L865">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M865">
         <v>0</v>
@@ -41930,38 +41930,35 @@
       </c>
     </row>
     <row r="866" spans="1:14">
-      <c r="A866">
-        <v>7798347810224</v>
+      <c r="A866" t="s">
+        <v>1582</v>
       </c>
       <c r="B866" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C866" t="s">
         <v>587</v>
       </c>
       <c r="D866" t="s">
-        <v>49</v>
-      </c>
-      <c r="E866" t="s">
-        <v>1583</v>
+        <v>3</v>
       </c>
       <c r="F866">
-        <v>3260</v>
+        <v>4300</v>
       </c>
       <c r="G866">
-        <v>9000</v>
+        <v>9300</v>
       </c>
       <c r="H866">
         <v>21</v>
       </c>
       <c r="I866">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="J866">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="K866">
-        <v>3260</v>
+        <v>0</v>
       </c>
       <c r="L866">
         <v>1</v>
@@ -41975,10 +41972,10 @@
     </row>
     <row r="867" spans="1:14">
       <c r="A867">
-        <v>7798347810569</v>
+        <v>7798347810224</v>
       </c>
       <c r="B867" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="C867" t="s">
         <v>587</v>
@@ -41987,25 +41984,25 @@
         <v>49</v>
       </c>
       <c r="E867" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="F867">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="G867">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="H867">
         <v>21</v>
       </c>
       <c r="I867">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="J867">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="K867">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="L867">
         <v>1</v>
@@ -42019,34 +42016,40 @@
     </row>
     <row r="868" spans="1:14">
       <c r="A868">
-        <v>6905416583656</v>
+        <v>7798347810569</v>
       </c>
       <c r="B868" t="s">
         <v>1584</v>
       </c>
       <c r="C868" t="s">
-        <v>417</v>
+        <v>587</v>
+      </c>
+      <c r="D868" t="s">
+        <v>49</v>
+      </c>
+      <c r="E868" t="s">
+        <v>1585</v>
       </c>
       <c r="F868">
-        <v>1500</v>
+        <v>3261</v>
       </c>
       <c r="G868">
-        <v>3000</v>
+        <v>9500</v>
       </c>
       <c r="H868">
         <v>21</v>
       </c>
       <c r="I868">
-        <v>1500</v>
+        <v>3261</v>
       </c>
       <c r="J868">
-        <v>1500</v>
+        <v>3261</v>
       </c>
       <c r="K868">
-        <v>1500</v>
+        <v>3261</v>
       </c>
       <c r="L868">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M868">
         <v>0</v>
@@ -42056,38 +42059,35 @@
       </c>
     </row>
     <row r="869" spans="1:14">
-      <c r="A869" t="s">
-        <v>1585</v>
+      <c r="A869">
+        <v>6905416583656</v>
       </c>
       <c r="B869" t="s">
         <v>1586</v>
       </c>
       <c r="C869" t="s">
-        <v>77</v>
-      </c>
-      <c r="D869" t="s">
-        <v>49</v>
+        <v>417</v>
       </c>
       <c r="F869">
-        <v>628</v>
+        <v>1500</v>
       </c>
       <c r="G869">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H869">
         <v>21</v>
       </c>
       <c r="I869">
-        <v>628</v>
+        <v>1500</v>
       </c>
       <c r="J869">
-        <v>628</v>
+        <v>1500</v>
       </c>
       <c r="K869">
-        <v>628</v>
+        <v>1500</v>
       </c>
       <c r="L869">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M869">
         <v>0</v>
@@ -42104,83 +42104,83 @@
         <v>1588</v>
       </c>
       <c r="C870" t="s">
+        <v>77</v>
+      </c>
+      <c r="D870" t="s">
+        <v>49</v>
+      </c>
+      <c r="F870">
+        <v>628</v>
+      </c>
+      <c r="G870">
+        <v>2500</v>
+      </c>
+      <c r="H870">
+        <v>21</v>
+      </c>
+      <c r="I870">
+        <v>628</v>
+      </c>
+      <c r="J870">
+        <v>628</v>
+      </c>
+      <c r="K870">
+        <v>628</v>
+      </c>
+      <c r="L870">
+        <v>0</v>
+      </c>
+      <c r="M870">
+        <v>0</v>
+      </c>
+      <c r="N870">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:14">
+      <c r="A871" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C871" t="s">
         <v>67</v>
       </c>
-      <c r="D870" t="s">
+      <c r="D871" t="s">
         <v>28</v>
       </c>
-      <c r="F870">
+      <c r="F871">
         <v>4800</v>
       </c>
-      <c r="G870">
+      <c r="G871">
         <v>12000</v>
       </c>
-      <c r="H870">
-        <v>21</v>
-      </c>
-      <c r="I870">
+      <c r="H871">
+        <v>21</v>
+      </c>
+      <c r="I871">
         <v>4800</v>
       </c>
-      <c r="J870">
+      <c r="J871">
         <v>4800</v>
       </c>
-      <c r="K870">
+      <c r="K871">
         <v>4800</v>
       </c>
-      <c r="L870">
+      <c r="L871">
         <v>8</v>
       </c>
-      <c r="M870">
-        <v>0</v>
-      </c>
-      <c r="N870">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="871" spans="1:14">
-      <c r="A871">
+      <c r="M871">
+        <v>0</v>
+      </c>
+      <c r="N871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:14">
+      <c r="A872">
         <v>6459751458518</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C871" t="s">
-        <v>74</v>
-      </c>
-      <c r="D871" t="s">
-        <v>49</v>
-      </c>
-      <c r="F871">
-        <v>608</v>
-      </c>
-      <c r="G871">
-        <v>2500</v>
-      </c>
-      <c r="H871">
-        <v>21</v>
-      </c>
-      <c r="I871">
-        <v>608</v>
-      </c>
-      <c r="J871">
-        <v>608</v>
-      </c>
-      <c r="K871">
-        <v>608</v>
-      </c>
-      <c r="L871">
-        <v>0</v>
-      </c>
-      <c r="M871">
-        <v>0</v>
-      </c>
-      <c r="N871">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="872" spans="1:14">
-      <c r="A872" t="s">
-        <v>1590</v>
       </c>
       <c r="B872" t="s">
         <v>1591</v>
@@ -42189,31 +42189,28 @@
         <v>74</v>
       </c>
       <c r="D872" t="s">
-        <v>31</v>
-      </c>
-      <c r="E872" t="s">
-        <v>1592</v>
+        <v>49</v>
       </c>
       <c r="F872">
-        <v>5887</v>
+        <v>608</v>
       </c>
       <c r="G872">
-        <v>18000</v>
+        <v>2500</v>
       </c>
       <c r="H872">
         <v>21</v>
       </c>
       <c r="I872">
-        <v>18000</v>
+        <v>608</v>
       </c>
       <c r="J872">
-        <v>18000</v>
+        <v>608</v>
       </c>
       <c r="K872">
-        <v>5.3</v>
+        <v>608</v>
       </c>
       <c r="L872">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M872">
         <v>0</v>
@@ -42224,10 +42221,10 @@
     </row>
     <row r="873" spans="1:14">
       <c r="A873" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B873" t="s">
         <v>1593</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1594</v>
       </c>
       <c r="C873" t="s">
         <v>74</v>
@@ -42236,28 +42233,28 @@
         <v>31</v>
       </c>
       <c r="E873" t="s">
-        <v>96</v>
+        <v>1594</v>
       </c>
       <c r="F873">
-        <v>4700</v>
+        <v>5887</v>
       </c>
       <c r="G873">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H873">
         <v>21</v>
       </c>
       <c r="I873">
-        <v>4700</v>
+        <v>18000</v>
       </c>
       <c r="J873">
-        <v>4700</v>
+        <v>18000</v>
       </c>
       <c r="K873">
-        <v>4700</v>
+        <v>5.3</v>
       </c>
       <c r="L873">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M873">
         <v>0</v>
@@ -42274,31 +42271,34 @@
         <v>1596</v>
       </c>
       <c r="C874" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D874" t="s">
         <v>31</v>
       </c>
+      <c r="E874" t="s">
+        <v>96</v>
+      </c>
       <c r="F874">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="G874">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H874">
         <v>21</v>
       </c>
       <c r="I874">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="J874">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="K874">
-        <v>773</v>
+        <v>4700</v>
       </c>
       <c r="L874">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M874">
         <v>0</v>
@@ -42308,35 +42308,35 @@
       </c>
     </row>
     <row r="875" spans="1:14">
-      <c r="A875">
-        <v>6989526542239</v>
+      <c r="A875" t="s">
+        <v>1597</v>
       </c>
       <c r="B875" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C875" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D875" t="s">
         <v>31</v>
       </c>
       <c r="F875">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="G875">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H875">
         <v>21</v>
       </c>
       <c r="I875">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="J875">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="K875">
-        <v>2352</v>
+        <v>773</v>
       </c>
       <c r="L875">
         <v>1</v>
@@ -42349,38 +42349,38 @@
       </c>
     </row>
     <row r="876" spans="1:14">
-      <c r="A876" t="s">
-        <v>1598</v>
+      <c r="A876">
+        <v>6989526542239</v>
       </c>
       <c r="B876" t="s">
         <v>1599</v>
       </c>
       <c r="C876" t="s">
-        <v>294</v>
+        <v>74</v>
       </c>
       <c r="D876" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F876">
-        <v>5200</v>
+        <v>2352</v>
       </c>
       <c r="G876">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H876">
         <v>21</v>
       </c>
       <c r="I876">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="J876">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="K876">
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="L876">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="M876">
         <v>0</v>
@@ -42646,7 +42646,7 @@
         <v>1611</v>
       </c>
       <c r="C883" t="s">
-        <v>67</v>
+        <v>414</v>
       </c>
       <c r="D883" t="s">
         <v>31</v>
@@ -42664,13 +42664,13 @@
         <v>21</v>
       </c>
       <c r="I883">
-        <v>18400</v>
+        <v>45000</v>
       </c>
       <c r="J883">
-        <v>18400</v>
+        <v>42000</v>
       </c>
       <c r="K883">
-        <v>18400</v>
+        <v>42000</v>
       </c>
       <c r="L883">
         <v>1</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9738B03-6A6D-427D-8914-A88F88A20941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E684BC72-0483-42D6-93F1-614A843B0A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{0819042F-7139-4CA2-996A-48BC38279A09}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{F35896B5-0D5A-4E2D-9648-B4A082C7C58A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="1635">
   <si>
     <t>CODIGO</t>
   </si>
@@ -2105,7 +2105,13 @@
     <t>Kit de Fusibles Automotor</t>
   </si>
   <si>
+    <t>LAMPARA52</t>
+  </si>
+  <si>
     <t>LAMPARA LED RECARGABLE 52CM</t>
+  </si>
+  <si>
+    <t>LAMPARA20</t>
   </si>
   <si>
     <t>LAMPARA MINI 20 LED MAGNETICO RECARGABLE</t>
@@ -5308,7 +5314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86D5866-FEB1-41B4-AAAD-77F01D2755E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B735C6-F062-45DA-91A3-33CA856C0915}">
   <dimension ref="A1:N895"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -10033,7 +10039,7 @@
         <v>18000</v>
       </c>
       <c r="L112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M112">
         <v>0</v>
@@ -10983,7 +10989,7 @@
         <v>10000</v>
       </c>
       <c r="L134">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -20979,8 +20985,11 @@
       </c>
     </row>
     <row r="373" spans="1:14">
+      <c r="A373" t="s">
+        <v>688</v>
+      </c>
       <c r="B373" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C373" t="s">
         <v>67</v>
@@ -21017,8 +21026,11 @@
       </c>
     </row>
     <row r="374" spans="1:14">
+      <c r="A374" t="s">
+        <v>690</v>
+      </c>
       <c r="B374" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C374" t="s">
         <v>67</v>
@@ -21056,10 +21068,10 @@
     </row>
     <row r="375" spans="1:14">
       <c r="A375" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B375" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C375" t="s">
         <v>38</v>
@@ -21097,10 +21109,10 @@
     </row>
     <row r="376" spans="1:14">
       <c r="A376" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B376" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C376" t="s">
         <v>417</v>
@@ -21138,10 +21150,10 @@
     </row>
     <row r="377" spans="1:14">
       <c r="A377" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B377" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C377" t="s">
         <v>77</v>
@@ -21179,10 +21191,10 @@
     </row>
     <row r="378" spans="1:14">
       <c r="A378" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B378" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C378" t="s">
         <v>429</v>
@@ -21223,7 +21235,7 @@
         <v>7798145006157</v>
       </c>
       <c r="B379" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C379" t="s">
         <v>38</v>
@@ -21261,10 +21273,10 @@
     </row>
     <row r="380" spans="1:14">
       <c r="A380" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B380" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -21302,10 +21314,10 @@
     </row>
     <row r="381" spans="1:14">
       <c r="A381" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B381" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -21346,7 +21358,7 @@
         <v>7798766432656</v>
       </c>
       <c r="B382" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -21387,7 +21399,7 @@
         <v>7264816897268</v>
       </c>
       <c r="B383" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C383" t="s">
         <v>302</v>
@@ -21425,10 +21437,10 @@
     </row>
     <row r="384" spans="1:14">
       <c r="A384" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B384" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C384" t="s">
         <v>302</v>
@@ -21469,7 +21481,7 @@
         <v>7769528971393</v>
       </c>
       <c r="B385" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C385" t="s">
         <v>67</v>
@@ -21510,7 +21522,7 @@
         <v>6956365778198</v>
       </c>
       <c r="B386" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C386" t="s">
         <v>581</v>
@@ -21548,7 +21560,7 @@
         <v>6978078010594</v>
       </c>
       <c r="B387" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C387" t="s">
         <v>581</v>
@@ -21589,7 +21601,7 @@
         <v>7882375154327</v>
       </c>
       <c r="B388" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C388" t="s">
         <v>581</v>
@@ -21627,10 +21639,10 @@
     </row>
     <row r="389" spans="1:14">
       <c r="A389" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B389" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C389" t="s">
         <v>581</v>
@@ -21671,7 +21683,7 @@
         <v>6000051718910</v>
       </c>
       <c r="B390" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C390" t="s">
         <v>581</v>
@@ -21712,7 +21724,7 @@
         <v>6000051718936</v>
       </c>
       <c r="B391" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C391" t="s">
         <v>581</v>
@@ -21753,7 +21765,7 @@
         <v>6957817560071</v>
       </c>
       <c r="B392" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C392" t="s">
         <v>581</v>
@@ -21794,7 +21806,7 @@
         <v>23065509545</v>
       </c>
       <c r="B393" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C393" t="s">
         <v>510</v>
@@ -21835,7 +21847,7 @@
         <v>6942687635905</v>
       </c>
       <c r="B394" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C394" t="s">
         <v>67</v>
@@ -21873,10 +21885,10 @@
     </row>
     <row r="395" spans="1:14">
       <c r="A395" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B395" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C395" t="s">
         <v>67</v>
@@ -21885,7 +21897,7 @@
         <v>3</v>
       </c>
       <c r="E395" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F395">
         <v>1200</v>
@@ -21917,10 +21929,10 @@
     </row>
     <row r="396" spans="1:14">
       <c r="A396" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B396" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C396" t="s">
         <v>67</v>
@@ -21958,10 +21970,10 @@
     </row>
     <row r="397" spans="1:14">
       <c r="A397" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B397" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C397" t="s">
         <v>67</v>
@@ -22002,10 +22014,10 @@
     </row>
     <row r="398" spans="1:14">
       <c r="A398" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B398" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C398" t="s">
         <v>67</v>
@@ -22046,10 +22058,10 @@
     </row>
     <row r="399" spans="1:14">
       <c r="A399" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B399" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C399" t="s">
         <v>67</v>
@@ -22087,10 +22099,10 @@
     </row>
     <row r="400" spans="1:14">
       <c r="A400" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B400" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C400" t="s">
         <v>67</v>
@@ -22128,10 +22140,10 @@
     </row>
     <row r="401" spans="1:14">
       <c r="A401" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B401" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C401" t="s">
         <v>581</v>
@@ -22169,10 +22181,10 @@
     </row>
     <row r="402" spans="1:14">
       <c r="A402" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B402" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C402" t="s">
         <v>581</v>
@@ -22210,10 +22222,10 @@
     </row>
     <row r="403" spans="1:14">
       <c r="A403" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B403" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C403" t="s">
         <v>581</v>
@@ -22251,16 +22263,16 @@
     </row>
     <row r="404" spans="1:14">
       <c r="A404" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B404" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C404" t="s">
         <v>366</v>
       </c>
       <c r="E404" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F404">
         <v>5000</v>
@@ -22292,10 +22304,10 @@
     </row>
     <row r="405" spans="1:14">
       <c r="A405" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B405" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C405" t="s">
         <v>366</v>
@@ -22333,10 +22345,10 @@
     </row>
     <row r="406" spans="1:14">
       <c r="A406" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B406" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
@@ -22377,7 +22389,7 @@
         <v>6973369821507</v>
       </c>
       <c r="B407" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C407" t="s">
         <v>302</v>
@@ -22418,7 +22430,7 @@
         <v>7798347600856</v>
       </c>
       <c r="B408" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C408" t="s">
         <v>302</v>
@@ -22459,7 +22471,7 @@
         <v>7798347600832</v>
       </c>
       <c r="B409" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C409" t="s">
         <v>302</v>
@@ -22500,10 +22512,10 @@
         <v>740617264128</v>
       </c>
       <c r="B410" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C410" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D410" t="s">
         <v>17</v>
@@ -22538,19 +22550,19 @@
     </row>
     <row r="411" spans="1:14">
       <c r="A411" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B411" t="s">
+        <v>752</v>
+      </c>
+      <c r="C411" t="s">
         <v>750</v>
-      </c>
-      <c r="C411" t="s">
-        <v>748</v>
       </c>
       <c r="D411" t="s">
         <v>17</v>
       </c>
       <c r="E411" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F411">
         <v>3700</v>
@@ -22585,16 +22597,16 @@
         <v>740617298857</v>
       </c>
       <c r="B412" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C412" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D412" t="s">
         <v>17</v>
       </c>
       <c r="E412" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F412">
         <v>4200</v>
@@ -22629,16 +22641,16 @@
         <v>740617298697</v>
       </c>
       <c r="B413" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C413" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D413" t="s">
         <v>17</v>
       </c>
       <c r="E413" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F413">
         <v>7500</v>
@@ -22673,16 +22685,16 @@
         <v>7406170128149</v>
       </c>
       <c r="B414" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C414" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D414" t="s">
         <v>3</v>
       </c>
       <c r="E414" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F414">
         <v>3400</v>
@@ -22714,10 +22726,10 @@
     </row>
     <row r="415" spans="1:14">
       <c r="A415" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B415" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C415" t="s">
         <v>685</v>
@@ -22755,10 +22767,10 @@
     </row>
     <row r="416" spans="1:14">
       <c r="A416" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B416" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C416" t="s">
         <v>685</v>
@@ -22796,10 +22808,10 @@
     </row>
     <row r="417" spans="1:14">
       <c r="A417" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B417" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C417" t="s">
         <v>38</v>
@@ -22837,10 +22849,10 @@
     </row>
     <row r="418" spans="1:14">
       <c r="A418" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B418" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C418" t="s">
         <v>685</v>
@@ -22884,7 +22896,7 @@
         <v>1234567890128</v>
       </c>
       <c r="B419" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C419" t="s">
         <v>58</v>
@@ -22922,10 +22934,10 @@
     </row>
     <row r="420" spans="1:14">
       <c r="A420" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B420" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C420" t="s">
         <v>302</v>
@@ -22963,10 +22975,10 @@
     </row>
     <row r="421" spans="1:14">
       <c r="A421" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B421" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C421" t="s">
         <v>423</v>
@@ -23004,10 +23016,10 @@
     </row>
     <row r="422" spans="1:14">
       <c r="A422" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B422" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C422" t="s">
         <v>423</v>
@@ -23016,7 +23028,7 @@
         <v>31</v>
       </c>
       <c r="E422" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F422">
         <v>10007</v>
@@ -23048,10 +23060,10 @@
     </row>
     <row r="423" spans="1:14">
       <c r="A423" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B423" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C423" t="s">
         <v>423</v>
@@ -23060,7 +23072,7 @@
         <v>31</v>
       </c>
       <c r="E423" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F423">
         <v>10007</v>
@@ -23095,7 +23107,7 @@
         <v>6925749735966</v>
       </c>
       <c r="B424" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C424" t="s">
         <v>502</v>
@@ -23133,10 +23145,10 @@
     </row>
     <row r="425" spans="1:14">
       <c r="A425" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B425" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C425" t="s">
         <v>502</v>
@@ -23174,10 +23186,10 @@
     </row>
     <row r="426" spans="1:14">
       <c r="A426" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B426" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C426" t="s">
         <v>67</v>
@@ -23218,7 +23230,7 @@
         <v>7798423540908</v>
       </c>
       <c r="B427" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C427" t="s">
         <v>423</v>
@@ -23256,10 +23268,10 @@
     </row>
     <row r="428" spans="1:14">
       <c r="A428" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B428" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C428" t="s">
         <v>685</v>
@@ -23297,10 +23309,10 @@
     </row>
     <row r="429" spans="1:14">
       <c r="A429" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B429" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C429" t="s">
         <v>429</v>
@@ -23341,10 +23353,10 @@
     </row>
     <row r="430" spans="1:14">
       <c r="A430" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B430" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C430" t="s">
         <v>429</v>
@@ -23382,10 +23394,10 @@
     </row>
     <row r="431" spans="1:14">
       <c r="A431" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B431" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C431" t="s">
         <v>38</v>
@@ -23426,7 +23438,7 @@
         <v>7799135011397</v>
       </c>
       <c r="B432" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C432" t="s">
         <v>58</v>
@@ -23467,10 +23479,10 @@
     </row>
     <row r="433" spans="1:14">
       <c r="A433" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B433" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C433" t="s">
         <v>685</v>
@@ -23508,19 +23520,19 @@
     </row>
     <row r="434" spans="1:14">
       <c r="A434" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B434" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C434" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D434" t="s">
         <v>28</v>
       </c>
       <c r="E434" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F434">
         <v>16120</v>
@@ -23552,19 +23564,19 @@
     </row>
     <row r="435" spans="1:14">
       <c r="A435" t="s">
+        <v>796</v>
+      </c>
+      <c r="B435" t="s">
+        <v>797</v>
+      </c>
+      <c r="C435" t="s">
         <v>794</v>
-      </c>
-      <c r="B435" t="s">
-        <v>795</v>
-      </c>
-      <c r="C435" t="s">
-        <v>792</v>
       </c>
       <c r="D435" t="s">
         <v>28</v>
       </c>
       <c r="E435" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F435">
         <v>3132</v>
@@ -23596,16 +23608,16 @@
     </row>
     <row r="436" spans="1:14">
       <c r="A436" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B436" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C436" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D436" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E436" t="s">
         <v>264</v>
@@ -23640,19 +23652,19 @@
     </row>
     <row r="437" spans="1:14">
       <c r="A437" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B437" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C437" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D437" t="s">
         <v>28</v>
       </c>
       <c r="E437" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F437">
         <v>13702</v>
@@ -23684,19 +23696,19 @@
     </row>
     <row r="438" spans="1:14">
       <c r="A438" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B438" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C438" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D438" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E438" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F438">
         <v>13620</v>
@@ -23728,19 +23740,19 @@
     </row>
     <row r="439" spans="1:14">
       <c r="A439" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B439" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C439" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D439" t="s">
         <v>28</v>
       </c>
       <c r="E439" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F439">
         <v>13411</v>
@@ -23772,19 +23784,19 @@
     </row>
     <row r="440" spans="1:14">
       <c r="A440" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B440" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C440" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D440" t="s">
         <v>28</v>
       </c>
       <c r="E440" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F440">
         <v>15750</v>
@@ -23816,16 +23828,16 @@
     </row>
     <row r="441" spans="1:14">
       <c r="A441" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B441" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C441" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D441" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E441" t="s">
         <v>264</v>
@@ -23860,16 +23872,16 @@
     </row>
     <row r="442" spans="1:14">
       <c r="A442" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B442" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C442" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D442" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E442" t="s">
         <v>264</v>
@@ -23904,16 +23916,16 @@
     </row>
     <row r="443" spans="1:14">
       <c r="A443" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B443" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C443" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D443" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E443" t="s">
         <v>264</v>
@@ -23948,13 +23960,13 @@
     </row>
     <row r="444" spans="1:14">
       <c r="A444" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B444" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C444" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D444" t="s">
         <v>28</v>
@@ -23989,13 +24001,13 @@
     </row>
     <row r="445" spans="1:14">
       <c r="A445" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B445" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C445" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D445" t="s">
         <v>28</v>
@@ -24033,13 +24045,13 @@
     </row>
     <row r="446" spans="1:14">
       <c r="A446" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B446" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C446" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D446" t="s">
         <v>28</v>
@@ -24077,16 +24089,16 @@
     </row>
     <row r="447" spans="1:14">
       <c r="A447" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B447" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C447" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D447" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F447">
         <v>16679</v>
@@ -24118,13 +24130,13 @@
     </row>
     <row r="448" spans="1:14">
       <c r="A448" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B448" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C448" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D448" t="s">
         <v>28</v>
@@ -24162,16 +24174,16 @@
     </row>
     <row r="449" spans="1:14">
       <c r="A449" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B449" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C449" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D449" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E449" t="s">
         <v>264</v>
@@ -24206,13 +24218,13 @@
     </row>
     <row r="450" spans="1:14">
       <c r="A450" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B450" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C450" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D450" t="s">
         <v>28</v>
@@ -24250,13 +24262,13 @@
     </row>
     <row r="451" spans="1:14">
       <c r="A451" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B451" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C451" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D451" t="s">
         <v>28</v>
@@ -24294,13 +24306,13 @@
     </row>
     <row r="452" spans="1:14">
       <c r="A452" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B452" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C452" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D452" t="s">
         <v>28</v>
@@ -24338,16 +24350,16 @@
     </row>
     <row r="453" spans="1:14">
       <c r="A453" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B453" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C453" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D453" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E453" t="s">
         <v>264</v>
@@ -24382,13 +24394,13 @@
     </row>
     <row r="454" spans="1:14">
       <c r="A454" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B454" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C454" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D454" t="s">
         <v>28</v>
@@ -24426,13 +24438,13 @@
     </row>
     <row r="455" spans="1:14">
       <c r="A455" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B455" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C455" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D455" t="s">
         <v>28</v>
@@ -24470,13 +24482,13 @@
     </row>
     <row r="456" spans="1:14">
       <c r="A456" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B456" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C456" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D456" t="s">
         <v>28</v>
@@ -24511,16 +24523,16 @@
     </row>
     <row r="457" spans="1:14">
       <c r="A457" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B457" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C457" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D457" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F457">
         <v>10930</v>
@@ -24552,13 +24564,13 @@
     </row>
     <row r="458" spans="1:14">
       <c r="A458" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B458" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C458" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D458" t="s">
         <v>28</v>
@@ -24593,13 +24605,13 @@
     </row>
     <row r="459" spans="1:14">
       <c r="A459" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B459" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C459" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D459" t="s">
         <v>28</v>
@@ -24634,13 +24646,13 @@
     </row>
     <row r="460" spans="1:14">
       <c r="A460" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B460" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C460" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D460" t="s">
         <v>28</v>
@@ -24675,13 +24687,13 @@
     </row>
     <row r="461" spans="1:14">
       <c r="A461" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B461" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C461" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D461" t="s">
         <v>28</v>
@@ -24716,16 +24728,16 @@
     </row>
     <row r="462" spans="1:14">
       <c r="A462" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B462" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C462" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D462" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="F462">
         <v>15793</v>
@@ -24757,13 +24769,13 @@
     </row>
     <row r="463" spans="1:14">
       <c r="A463" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B463" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C463" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D463" t="s">
         <v>28</v>
@@ -24798,13 +24810,13 @@
     </row>
     <row r="464" spans="1:14">
       <c r="A464" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B464" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C464" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D464" t="s">
         <v>28</v>
@@ -24842,13 +24854,13 @@
     </row>
     <row r="465" spans="1:14">
       <c r="A465" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B465" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C465" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D465" t="s">
         <v>28</v>
@@ -24886,13 +24898,13 @@
     </row>
     <row r="466" spans="1:14">
       <c r="A466" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B466" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C466" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D466" t="s">
         <v>28</v>
@@ -24927,13 +24939,13 @@
     </row>
     <row r="467" spans="1:14">
       <c r="A467" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B467" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C467" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D467" t="s">
         <v>28</v>
@@ -24971,13 +24983,13 @@
     </row>
     <row r="468" spans="1:14">
       <c r="A468" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B468" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C468" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D468" t="s">
         <v>28</v>
@@ -25015,13 +25027,13 @@
     </row>
     <row r="469" spans="1:14">
       <c r="A469" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B469" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C469" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D469" t="s">
         <v>28</v>
@@ -25059,16 +25071,16 @@
     </row>
     <row r="470" spans="1:14">
       <c r="A470" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B470" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C470" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D470" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E470" t="s">
         <v>202</v>
@@ -25103,16 +25115,16 @@
     </row>
     <row r="471" spans="1:14">
       <c r="A471" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B471" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C471" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D471" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E471" t="s">
         <v>264</v>
@@ -25147,19 +25159,19 @@
     </row>
     <row r="472" spans="1:14">
       <c r="A472" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B472" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C472" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D472" t="s">
         <v>28</v>
       </c>
       <c r="E472" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F472">
         <v>14490</v>
@@ -25191,16 +25203,16 @@
     </row>
     <row r="473" spans="1:14">
       <c r="A473" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B473" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C473" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D473" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E473" t="s">
         <v>264</v>
@@ -25235,13 +25247,13 @@
     </row>
     <row r="474" spans="1:14">
       <c r="A474" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B474" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C474" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D474" t="s">
         <v>28</v>
@@ -25279,16 +25291,16 @@
     </row>
     <row r="475" spans="1:14">
       <c r="A475" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B475" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C475" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D475" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E475" t="s">
         <v>264</v>
@@ -25323,13 +25335,13 @@
     </row>
     <row r="476" spans="1:14">
       <c r="A476" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B476" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C476" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D476" t="s">
         <v>28</v>
@@ -25367,13 +25379,13 @@
     </row>
     <row r="477" spans="1:14">
       <c r="A477" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B477" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C477" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D477" t="s">
         <v>28</v>
@@ -25411,16 +25423,16 @@
     </row>
     <row r="478" spans="1:14">
       <c r="A478" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B478" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C478" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D478" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F478">
         <v>6500</v>
@@ -25452,13 +25464,13 @@
     </row>
     <row r="479" spans="1:14">
       <c r="A479" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B479" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C479" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D479" t="s">
         <v>28</v>
@@ -25493,16 +25505,16 @@
     </row>
     <row r="480" spans="1:14">
       <c r="A480" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B480" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C480" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D480" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F480">
         <v>16000</v>
@@ -25534,16 +25546,16 @@
     </row>
     <row r="481" spans="1:14">
       <c r="A481" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B481" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C481" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D481" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E481" t="s">
         <v>264</v>
@@ -25578,16 +25590,16 @@
     </row>
     <row r="482" spans="1:14">
       <c r="A482" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B482" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C482" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D482" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F482">
         <v>14342</v>
@@ -25619,13 +25631,13 @@
     </row>
     <row r="483" spans="1:14">
       <c r="A483" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B483" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C483" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D483" t="s">
         <v>28</v>
@@ -25660,13 +25672,13 @@
     </row>
     <row r="484" spans="1:14">
       <c r="A484" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B484" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C484" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D484" t="s">
         <v>28</v>
@@ -25704,13 +25716,13 @@
     </row>
     <row r="485" spans="1:14">
       <c r="A485" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B485" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C485" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D485" t="s">
         <v>28</v>
@@ -25745,13 +25757,13 @@
     </row>
     <row r="486" spans="1:14">
       <c r="A486" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B486" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C486" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D486" t="s">
         <v>28</v>
@@ -25789,13 +25801,13 @@
     </row>
     <row r="487" spans="1:14">
       <c r="A487" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B487" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C487" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D487" t="s">
         <v>28</v>
@@ -25833,13 +25845,13 @@
     </row>
     <row r="488" spans="1:14">
       <c r="A488" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B488" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C488" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D488" t="s">
         <v>28</v>
@@ -25874,13 +25886,13 @@
     </row>
     <row r="489" spans="1:14">
       <c r="A489" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B489" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C489" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D489" t="s">
         <v>28</v>
@@ -25915,13 +25927,13 @@
     </row>
     <row r="490" spans="1:14">
       <c r="A490" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B490" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C490" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D490" t="s">
         <v>28</v>
@@ -25956,13 +25968,13 @@
     </row>
     <row r="491" spans="1:14">
       <c r="A491" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B491" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C491" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D491" t="s">
         <v>28</v>
@@ -25997,13 +26009,13 @@
     </row>
     <row r="492" spans="1:14">
       <c r="A492" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B492" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C492" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D492" t="s">
         <v>28</v>
@@ -26038,13 +26050,13 @@
     </row>
     <row r="493" spans="1:14">
       <c r="A493" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B493" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C493" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D493" t="s">
         <v>28</v>
@@ -26079,13 +26091,13 @@
     </row>
     <row r="494" spans="1:14">
       <c r="A494" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B494" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C494" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D494" t="s">
         <v>28</v>
@@ -26120,13 +26132,13 @@
     </row>
     <row r="495" spans="1:14">
       <c r="A495" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B495" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C495" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D495" t="s">
         <v>28</v>
@@ -26164,13 +26176,13 @@
     </row>
     <row r="496" spans="1:14">
       <c r="A496" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B496" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C496" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D496" t="s">
         <v>28</v>
@@ -26205,13 +26217,13 @@
     </row>
     <row r="497" spans="1:14">
       <c r="A497" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B497" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C497" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D497" t="s">
         <v>28</v>
@@ -26246,19 +26258,19 @@
     </row>
     <row r="498" spans="1:14">
       <c r="A498" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B498" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C498" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D498" t="s">
         <v>28</v>
       </c>
       <c r="E498" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F498">
         <v>12225</v>
@@ -26290,13 +26302,13 @@
     </row>
     <row r="499" spans="1:14">
       <c r="A499" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B499" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C499" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D499" t="s">
         <v>28</v>
@@ -26331,19 +26343,19 @@
     </row>
     <row r="500" spans="1:14">
       <c r="A500" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B500" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C500" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D500" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E500" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F500">
         <v>12489</v>
@@ -26375,13 +26387,13 @@
     </row>
     <row r="501" spans="1:14">
       <c r="A501" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B501" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C501" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D501" t="s">
         <v>28</v>
@@ -26416,13 +26428,13 @@
     </row>
     <row r="502" spans="1:14">
       <c r="A502" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B502" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C502" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D502" t="s">
         <v>28</v>
@@ -26460,16 +26472,16 @@
     </row>
     <row r="503" spans="1:14">
       <c r="A503" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B503" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C503" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D503" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E503" t="s">
         <v>241</v>
@@ -26504,13 +26516,13 @@
     </row>
     <row r="504" spans="1:14">
       <c r="A504" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B504" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C504" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D504" t="s">
         <v>28</v>
@@ -26545,13 +26557,13 @@
     </row>
     <row r="505" spans="1:14">
       <c r="A505" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B505" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C505" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D505" t="s">
         <v>28</v>
@@ -26589,13 +26601,13 @@
     </row>
     <row r="506" spans="1:14">
       <c r="A506" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B506" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C506" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D506" t="s">
         <v>28</v>
@@ -26633,13 +26645,13 @@
     </row>
     <row r="507" spans="1:14">
       <c r="A507" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B507" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C507" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D507" t="s">
         <v>28</v>
@@ -26677,16 +26689,16 @@
     </row>
     <row r="508" spans="1:14">
       <c r="A508" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B508" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C508" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D508" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E508" t="s">
         <v>264</v>
@@ -26721,13 +26733,13 @@
     </row>
     <row r="509" spans="1:14">
       <c r="A509" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B509" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C509" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D509" t="s">
         <v>28</v>
@@ -26762,13 +26774,13 @@
     </row>
     <row r="510" spans="1:14">
       <c r="A510" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B510" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C510" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D510" t="s">
         <v>28</v>
@@ -26803,13 +26815,13 @@
     </row>
     <row r="511" spans="1:14">
       <c r="A511" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B511" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C511" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D511" t="s">
         <v>28</v>
@@ -26847,13 +26859,13 @@
     </row>
     <row r="512" spans="1:14">
       <c r="A512" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B512" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C512" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D512" t="s">
         <v>28</v>
@@ -26891,16 +26903,16 @@
     </row>
     <row r="513" spans="1:14">
       <c r="A513" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B513" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C513" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D513" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E513" t="s">
         <v>264</v>
@@ -26924,7 +26936,7 @@
         <v>18000</v>
       </c>
       <c r="L513">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M513">
         <v>0</v>
@@ -26935,13 +26947,13 @@
     </row>
     <row r="514" spans="1:14">
       <c r="A514" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B514" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C514" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D514" t="s">
         <v>28</v>
@@ -26979,16 +26991,16 @@
     </row>
     <row r="515" spans="1:14">
       <c r="A515" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B515" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C515" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D515" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E515" t="s">
         <v>264</v>
@@ -27023,16 +27035,16 @@
     </row>
     <row r="516" spans="1:14">
       <c r="A516" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B516" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C516" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D516" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F516">
         <v>13700</v>
@@ -27064,13 +27076,13 @@
     </row>
     <row r="517" spans="1:14">
       <c r="A517" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B517" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C517" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D517" t="s">
         <v>28</v>
@@ -27105,16 +27117,16 @@
     </row>
     <row r="518" spans="1:14">
       <c r="A518" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B518" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C518" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D518" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E518" t="s">
         <v>264</v>
@@ -27149,13 +27161,13 @@
     </row>
     <row r="519" spans="1:14">
       <c r="A519" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B519" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C519" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D519" t="s">
         <v>28</v>
@@ -27193,13 +27205,13 @@
     </row>
     <row r="520" spans="1:14">
       <c r="A520" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B520" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C520" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D520" t="s">
         <v>28</v>
@@ -27234,13 +27246,13 @@
     </row>
     <row r="521" spans="1:14">
       <c r="A521" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B521" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C521" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D521" t="s">
         <v>28</v>
@@ -27278,13 +27290,13 @@
     </row>
     <row r="522" spans="1:14">
       <c r="A522" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B522" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C522" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D522" t="s">
         <v>28</v>
@@ -27322,13 +27334,13 @@
     </row>
     <row r="523" spans="1:14">
       <c r="A523" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B523" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C523" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D523" t="s">
         <v>28</v>
@@ -27366,16 +27378,16 @@
     </row>
     <row r="524" spans="1:14">
       <c r="A524" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B524" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C524" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D524" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E524" t="s">
         <v>178</v>
@@ -27410,16 +27422,16 @@
     </row>
     <row r="525" spans="1:14">
       <c r="A525" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B525" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C525" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D525" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E525" t="s">
         <v>264</v>
@@ -27454,16 +27466,16 @@
     </row>
     <row r="526" spans="1:14">
       <c r="A526" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B526" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C526" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D526" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E526" t="s">
         <v>264</v>
@@ -27498,13 +27510,13 @@
     </row>
     <row r="527" spans="1:14">
       <c r="A527" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B527" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C527" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D527" t="s">
         <v>28</v>
@@ -27542,16 +27554,16 @@
     </row>
     <row r="528" spans="1:14">
       <c r="A528" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B528" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C528" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D528" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E528" t="s">
         <v>264</v>
@@ -27586,13 +27598,13 @@
     </row>
     <row r="529" spans="1:14">
       <c r="A529" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B529" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C529" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D529" t="s">
         <v>28</v>
@@ -27630,13 +27642,13 @@
     </row>
     <row r="530" spans="1:14">
       <c r="A530" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B530" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C530" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D530" t="s">
         <v>28</v>
@@ -27674,16 +27686,16 @@
     </row>
     <row r="531" spans="1:14">
       <c r="A531" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B531" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C531" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D531" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E531" t="s">
         <v>178</v>
@@ -27718,13 +27730,13 @@
     </row>
     <row r="532" spans="1:14">
       <c r="A532" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B532" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C532" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D532" t="s">
         <v>28</v>
@@ -27762,13 +27774,13 @@
     </row>
     <row r="533" spans="1:14">
       <c r="A533" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B533" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C533" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D533" t="s">
         <v>28</v>
@@ -27806,13 +27818,13 @@
     </row>
     <row r="534" spans="1:14">
       <c r="A534" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B534" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C534" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D534" t="s">
         <v>28</v>
@@ -27847,16 +27859,16 @@
     </row>
     <row r="535" spans="1:14">
       <c r="A535" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B535" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C535" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D535" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E535" t="s">
         <v>264</v>
@@ -27891,13 +27903,13 @@
     </row>
     <row r="536" spans="1:14">
       <c r="A536" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B536" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C536" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D536" t="s">
         <v>28</v>
@@ -27932,13 +27944,13 @@
     </row>
     <row r="537" spans="1:14">
       <c r="A537" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B537" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C537" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D537" t="s">
         <v>28</v>
@@ -27973,16 +27985,16 @@
     </row>
     <row r="538" spans="1:14">
       <c r="A538" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B538" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C538" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D538" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E538" t="s">
         <v>264</v>
@@ -28017,16 +28029,16 @@
     </row>
     <row r="539" spans="1:14">
       <c r="A539" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B539" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C539" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D539" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E539" t="s">
         <v>264</v>
@@ -28061,16 +28073,16 @@
     </row>
     <row r="540" spans="1:14">
       <c r="A540" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B540" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C540" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D540" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E540" t="s">
         <v>264</v>
@@ -28105,13 +28117,13 @@
     </row>
     <row r="541" spans="1:14">
       <c r="A541" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B541" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C541" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D541" t="s">
         <v>28</v>
@@ -28149,13 +28161,13 @@
     </row>
     <row r="542" spans="1:14">
       <c r="A542" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B542" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C542" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D542" t="s">
         <v>626</v>
@@ -28193,16 +28205,16 @@
     </row>
     <row r="543" spans="1:14">
       <c r="A543" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B543" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C543" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D543" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E543" t="s">
         <v>264</v>
@@ -28237,16 +28249,16 @@
     </row>
     <row r="544" spans="1:14">
       <c r="A544" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B544" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C544" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D544" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E544" t="s">
         <v>178</v>
@@ -28281,13 +28293,13 @@
     </row>
     <row r="545" spans="1:14">
       <c r="A545" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B545" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C545" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D545" t="s">
         <v>28</v>
@@ -28325,16 +28337,16 @@
     </row>
     <row r="546" spans="1:14">
       <c r="A546" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B546" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C546" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D546" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E546" t="s">
         <v>264</v>
@@ -28369,16 +28381,16 @@
     </row>
     <row r="547" spans="1:14">
       <c r="A547" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B547" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C547" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D547" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E547" t="s">
         <v>178</v>
@@ -28413,13 +28425,13 @@
     </row>
     <row r="548" spans="1:14">
       <c r="A548" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B548" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C548" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D548" t="s">
         <v>28</v>
@@ -28454,13 +28466,13 @@
     </row>
     <row r="549" spans="1:14">
       <c r="A549" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B549" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C549" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D549" t="s">
         <v>28</v>
@@ -28495,13 +28507,13 @@
     </row>
     <row r="550" spans="1:14">
       <c r="A550" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B550" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C550" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D550" t="s">
         <v>28</v>
@@ -28539,13 +28551,13 @@
     </row>
     <row r="551" spans="1:14">
       <c r="A551" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B551" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C551" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D551" t="s">
         <v>28</v>
@@ -28580,16 +28592,16 @@
     </row>
     <row r="552" spans="1:14">
       <c r="A552" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B552" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C552" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D552" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E552" t="s">
         <v>178</v>
@@ -28624,16 +28636,16 @@
     </row>
     <row r="553" spans="1:14">
       <c r="A553" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B553" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C553" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D553" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E553" t="s">
         <v>264</v>
@@ -28668,16 +28680,16 @@
     </row>
     <row r="554" spans="1:14">
       <c r="A554" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B554" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C554" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D554" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E554" t="s">
         <v>264</v>
@@ -28712,16 +28724,16 @@
     </row>
     <row r="555" spans="1:14">
       <c r="A555" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B555" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C555" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D555" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E555" t="s">
         <v>264</v>
@@ -28756,16 +28768,16 @@
     </row>
     <row r="556" spans="1:14">
       <c r="A556" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B556" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C556" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D556" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E556" t="s">
         <v>264</v>
@@ -28800,16 +28812,16 @@
     </row>
     <row r="557" spans="1:14">
       <c r="A557" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B557" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C557" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D557" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F557">
         <v>18092</v>
@@ -28841,13 +28853,13 @@
     </row>
     <row r="558" spans="1:14">
       <c r="A558" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B558" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C558" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D558" t="s">
         <v>28</v>
@@ -28885,13 +28897,13 @@
     </row>
     <row r="559" spans="1:14">
       <c r="A559" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B559" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C559" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D559" t="s">
         <v>28</v>
@@ -28929,13 +28941,13 @@
     </row>
     <row r="560" spans="1:14">
       <c r="A560" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B560" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C560" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D560" t="s">
         <v>626</v>
@@ -28973,13 +28985,13 @@
     </row>
     <row r="561" spans="1:14">
       <c r="A561" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B561" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C561" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D561" t="s">
         <v>28</v>
@@ -29017,16 +29029,16 @@
     </row>
     <row r="562" spans="1:14">
       <c r="A562" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B562" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C562" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D562" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E562" t="s">
         <v>264</v>
@@ -29061,16 +29073,16 @@
     </row>
     <row r="563" spans="1:14">
       <c r="A563" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B563" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C563" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D563" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E563" t="s">
         <v>178</v>
@@ -29105,13 +29117,13 @@
     </row>
     <row r="564" spans="1:14">
       <c r="A564" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B564" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C564" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D564" t="s">
         <v>28</v>
@@ -29149,16 +29161,16 @@
     </row>
     <row r="565" spans="1:14">
       <c r="A565" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B565" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C565" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D565" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E565" t="s">
         <v>178</v>
@@ -29193,16 +29205,16 @@
     </row>
     <row r="566" spans="1:14">
       <c r="A566" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B566" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C566" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D566" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E566" t="s">
         <v>178</v>
@@ -29237,13 +29249,13 @@
     </row>
     <row r="567" spans="1:14">
       <c r="A567" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B567" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C567" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D567" t="s">
         <v>28</v>
@@ -29278,13 +29290,13 @@
     </row>
     <row r="568" spans="1:14">
       <c r="A568" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B568" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C568" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D568" t="s">
         <v>28</v>
@@ -29319,16 +29331,16 @@
     </row>
     <row r="569" spans="1:14">
       <c r="A569" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B569" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C569" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D569" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E569" t="s">
         <v>178</v>
@@ -29363,13 +29375,13 @@
     </row>
     <row r="570" spans="1:14">
       <c r="A570" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B570" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C570" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D570" t="s">
         <v>205</v>
@@ -29404,13 +29416,13 @@
     </row>
     <row r="571" spans="1:14">
       <c r="A571" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B571" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C571" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D571" t="s">
         <v>28</v>
@@ -29445,13 +29457,13 @@
     </row>
     <row r="572" spans="1:14">
       <c r="A572" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B572" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C572" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D572" t="s">
         <v>28</v>
@@ -29489,16 +29501,16 @@
     </row>
     <row r="573" spans="1:14">
       <c r="A573" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B573" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C573" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D573" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E573" t="s">
         <v>178</v>
@@ -29533,13 +29545,13 @@
     </row>
     <row r="574" spans="1:14">
       <c r="A574" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B574" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C574" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D574" t="s">
         <v>28</v>
@@ -29574,16 +29586,16 @@
     </row>
     <row r="575" spans="1:14">
       <c r="A575" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B575" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C575" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D575" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F575">
         <v>15000</v>
@@ -29615,16 +29627,16 @@
     </row>
     <row r="576" spans="1:14">
       <c r="A576" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B576" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C576" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D576" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F576">
         <v>14914.49</v>
@@ -29656,16 +29668,16 @@
     </row>
     <row r="577" spans="1:14">
       <c r="A577" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B577" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C577" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D577" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F577">
         <v>8183</v>
@@ -29697,13 +29709,13 @@
     </row>
     <row r="578" spans="1:14">
       <c r="A578" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B578" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C578" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D578" t="s">
         <v>28</v>
@@ -29741,19 +29753,19 @@
     </row>
     <row r="579" spans="1:14">
       <c r="A579" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B579" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C579" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D579" t="s">
         <v>28</v>
       </c>
       <c r="E579" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F579">
         <v>15050</v>
@@ -29785,19 +29797,19 @@
     </row>
     <row r="580" spans="1:14">
       <c r="A580" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B580" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C580" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D580" t="s">
         <v>28</v>
       </c>
       <c r="E580" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F580">
         <v>13600</v>
@@ -29829,19 +29841,19 @@
     </row>
     <row r="581" spans="1:14">
       <c r="A581" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B581" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C581" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D581" t="s">
         <v>28</v>
       </c>
       <c r="E581" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F581">
         <v>13050</v>
@@ -29873,13 +29885,13 @@
     </row>
     <row r="582" spans="1:14">
       <c r="A582" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B582" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C582" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D582" t="s">
         <v>28</v>
@@ -29917,19 +29929,19 @@
     </row>
     <row r="583" spans="1:14">
       <c r="A583" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B583" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C583" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D583" t="s">
         <v>28</v>
       </c>
       <c r="E583" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F583">
         <v>13600</v>
@@ -29961,19 +29973,19 @@
     </row>
     <row r="584" spans="1:14">
       <c r="A584" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B584" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C584" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D584" t="s">
         <v>28</v>
       </c>
       <c r="E584" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F584">
         <v>16500</v>
@@ -30005,19 +30017,19 @@
     </row>
     <row r="585" spans="1:14">
       <c r="A585" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B585" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C585" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D585" t="s">
         <v>28</v>
       </c>
       <c r="E585" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F585">
         <v>16000</v>
@@ -30049,16 +30061,16 @@
     </row>
     <row r="586" spans="1:14">
       <c r="A586" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B586" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C586" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D586" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F586">
         <v>16416</v>
@@ -30090,16 +30102,16 @@
     </row>
     <row r="587" spans="1:14">
       <c r="A587" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B587" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C587" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D587" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E587" t="s">
         <v>264</v>
@@ -30134,16 +30146,16 @@
     </row>
     <row r="588" spans="1:14">
       <c r="A588" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B588" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C588" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D588" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E588" t="s">
         <v>264</v>
@@ -30178,16 +30190,16 @@
     </row>
     <row r="589" spans="1:14">
       <c r="A589" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B589" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C589" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D589" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F589">
         <v>21907</v>
@@ -30219,19 +30231,19 @@
     </row>
     <row r="590" spans="1:14">
       <c r="A590" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B590" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C590" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D590" t="s">
         <v>28</v>
       </c>
       <c r="E590" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F590">
         <v>15300</v>
@@ -30263,16 +30275,16 @@
     </row>
     <row r="591" spans="1:14">
       <c r="A591" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B591" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C591" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D591" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F591">
         <v>12852</v>
@@ -30304,16 +30316,16 @@
     </row>
     <row r="592" spans="1:14">
       <c r="A592" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B592" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C592" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D592" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F592">
         <v>14429</v>
@@ -30345,19 +30357,19 @@
     </row>
     <row r="593" spans="1:14">
       <c r="A593" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B593" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C593" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D593" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E593" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F593">
         <v>13592</v>
@@ -30389,16 +30401,16 @@
     </row>
     <row r="594" spans="1:14">
       <c r="A594" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B594" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C594" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D594" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E594" t="s">
         <v>264</v>
@@ -30433,19 +30445,19 @@
     </row>
     <row r="595" spans="1:14">
       <c r="A595" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B595" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C595" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D595" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E595" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F595">
         <v>14500</v>
@@ -30477,16 +30489,16 @@
     </row>
     <row r="596" spans="1:14">
       <c r="A596" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B596" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C596" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D596" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E596" t="s">
         <v>264</v>
@@ -30521,19 +30533,19 @@
     </row>
     <row r="597" spans="1:14">
       <c r="A597" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B597" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C597" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D597" t="s">
         <v>28</v>
       </c>
       <c r="E597" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F597">
         <v>42420</v>
@@ -30565,13 +30577,13 @@
     </row>
     <row r="598" spans="1:14">
       <c r="A598" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B598" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C598" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D598" t="s">
         <v>626</v>
@@ -30606,16 +30618,16 @@
     </row>
     <row r="599" spans="1:14">
       <c r="A599" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B599" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C599" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D599" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E599" t="s">
         <v>264</v>
@@ -30650,13 +30662,13 @@
     </row>
     <row r="600" spans="1:14">
       <c r="A600" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B600" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="C600" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D600" t="s">
         <v>28</v>
@@ -30691,19 +30703,19 @@
     </row>
     <row r="601" spans="1:14">
       <c r="A601" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B601" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C601" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D601" t="s">
         <v>28</v>
       </c>
       <c r="E601" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F601">
         <v>13030</v>
@@ -30735,16 +30747,16 @@
     </row>
     <row r="602" spans="1:14">
       <c r="A602" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="B602" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="C602" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D602" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E602" t="s">
         <v>264</v>
@@ -30779,19 +30791,19 @@
     </row>
     <row r="603" spans="1:14">
       <c r="A603" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B603" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C603" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D603" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E603" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F603">
         <v>15704</v>
@@ -30823,16 +30835,16 @@
     </row>
     <row r="604" spans="1:14">
       <c r="A604" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B604" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C604" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D604" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F604">
         <v>12677</v>
@@ -30864,19 +30876,19 @@
     </row>
     <row r="605" spans="1:14">
       <c r="A605" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B605" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C605" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D605" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E605" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F605">
         <v>11722</v>
@@ -30897,7 +30909,7 @@
         <v>20000</v>
       </c>
       <c r="L605">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M605">
         <v>0</v>
@@ -30908,16 +30920,16 @@
     </row>
     <row r="606" spans="1:14">
       <c r="A606" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B606" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C606" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D606" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F606">
         <v>11750</v>
@@ -30949,16 +30961,16 @@
     </row>
     <row r="607" spans="1:14">
       <c r="A607" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B607" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C607" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D607" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E607" t="s">
         <v>264</v>
@@ -30993,16 +31005,16 @@
     </row>
     <row r="608" spans="1:14">
       <c r="A608" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B608" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C608" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D608" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F608">
         <v>11640</v>
@@ -31034,19 +31046,19 @@
     </row>
     <row r="609" spans="1:14">
       <c r="A609" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B609" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C609" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D609" t="s">
         <v>626</v>
       </c>
       <c r="E609" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="F609">
         <v>14946</v>
@@ -31078,19 +31090,19 @@
     </row>
     <row r="610" spans="1:14">
       <c r="A610" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B610" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C610" t="s">
+        <v>794</v>
+      </c>
+      <c r="D610" t="s">
+        <v>801</v>
+      </c>
+      <c r="E610" t="s">
         <v>1160</v>
-      </c>
-      <c r="C610" t="s">
-        <v>792</v>
-      </c>
-      <c r="D610" t="s">
-        <v>799</v>
-      </c>
-      <c r="E610" t="s">
-        <v>1158</v>
       </c>
       <c r="F610">
         <v>16236</v>
@@ -31122,16 +31134,16 @@
     </row>
     <row r="611" spans="1:14">
       <c r="A611" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B611" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C611" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D611" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E611" t="s">
         <v>264</v>
@@ -31166,19 +31178,19 @@
     </row>
     <row r="612" spans="1:14">
       <c r="A612" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B612" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C612" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D612" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E612" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="F612">
         <v>18500</v>
@@ -31210,19 +31222,19 @@
     </row>
     <row r="613" spans="1:14">
       <c r="A613" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B613" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C613" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D613" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E613" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="F613">
         <v>20600</v>
@@ -31254,16 +31266,16 @@
     </row>
     <row r="614" spans="1:14">
       <c r="A614" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B614" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C614" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D614" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E614" t="s">
         <v>264</v>
@@ -31301,7 +31313,7 @@
         <v>77991350098372</v>
       </c>
       <c r="B615" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C615" t="s">
         <v>429</v>
@@ -31345,7 +31357,7 @@
         <v>7799135009837</v>
       </c>
       <c r="B616" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C616" t="s">
         <v>429</v>
@@ -31389,7 +31401,7 @@
         <v>723540565784</v>
       </c>
       <c r="B617" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C617" t="s">
         <v>429</v>
@@ -31433,7 +31445,7 @@
         <v>7799135009868</v>
       </c>
       <c r="B618" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C618" t="s">
         <v>429</v>
@@ -31474,7 +31486,7 @@
         <v>700306605557</v>
       </c>
       <c r="B619" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C619" t="s">
         <v>429</v>
@@ -31512,13 +31524,13 @@
     </row>
     <row r="620" spans="1:14">
       <c r="A620" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B620" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C620" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D620" t="s">
         <v>31</v>
@@ -31556,10 +31568,10 @@
     </row>
     <row r="621" spans="1:14">
       <c r="A621" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B621" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C621" t="s">
         <v>77</v>
@@ -31597,10 +31609,10 @@
     </row>
     <row r="622" spans="1:14">
       <c r="A622" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B622" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C622" t="s">
         <v>58</v>
@@ -31644,7 +31656,7 @@
         <v>6970430176887</v>
       </c>
       <c r="B623" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C623" t="s">
         <v>302</v>
@@ -31682,10 +31694,10 @@
     </row>
     <row r="624" spans="1:14">
       <c r="A624" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B624" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C624" t="s">
         <v>671</v>
@@ -31694,7 +31706,7 @@
         <v>3</v>
       </c>
       <c r="E624" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F624">
         <v>12000</v>
@@ -31726,10 +31738,10 @@
     </row>
     <row r="625" spans="1:14">
       <c r="A625" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B625" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C625" t="s">
         <v>671</v>
@@ -31770,7 +31782,7 @@
         <v>729208240086</v>
       </c>
       <c r="B626" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C626" t="s">
         <v>671</v>
@@ -31779,7 +31791,7 @@
         <v>31</v>
       </c>
       <c r="E626" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F626">
         <v>2400</v>
@@ -31814,7 +31826,7 @@
         <v>6930149999894</v>
       </c>
       <c r="B627" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C627" t="s">
         <v>671</v>
@@ -31855,7 +31867,7 @@
         <v>7798137713162</v>
       </c>
       <c r="B628" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C628" t="s">
         <v>671</v>
@@ -31899,7 +31911,7 @@
         <v>4948872001458</v>
       </c>
       <c r="B629" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C629" t="s">
         <v>671</v>
@@ -31908,7 +31920,7 @@
         <v>17</v>
       </c>
       <c r="E629" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="F629">
         <v>6355</v>
@@ -31943,7 +31955,7 @@
         <v>711719990048</v>
       </c>
       <c r="B630" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="C630" t="s">
         <v>671</v>
@@ -31984,7 +31996,7 @@
         <v>723540565814</v>
       </c>
       <c r="B631" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C631" t="s">
         <v>671</v>
@@ -32025,7 +32037,7 @@
         <v>7799135016361</v>
       </c>
       <c r="B632" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C632" t="s">
         <v>74</v>
@@ -32066,10 +32078,10 @@
     </row>
     <row r="633" spans="1:14">
       <c r="A633" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B633" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C633" t="s">
         <v>74</v>
@@ -32110,7 +32122,7 @@
         <v>7799135016392</v>
       </c>
       <c r="B634" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C634" t="s">
         <v>74</v>
@@ -32151,10 +32163,10 @@
     </row>
     <row r="635" spans="1:14">
       <c r="A635" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B635" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C635" t="s">
         <v>685</v>
@@ -32195,7 +32207,7 @@
         <v>7799135000346</v>
       </c>
       <c r="B636" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C636" t="s">
         <v>685</v>
@@ -32236,10 +32248,10 @@
     </row>
     <row r="637" spans="1:14">
       <c r="A637" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B637" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C637" t="s">
         <v>685</v>
@@ -32248,7 +32260,7 @@
         <v>31</v>
       </c>
       <c r="E637" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F637">
         <v>3804</v>
@@ -32283,7 +32295,7 @@
         <v>5115164112157</v>
       </c>
       <c r="B638" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="C638" t="s">
         <v>685</v>
@@ -32321,10 +32333,10 @@
     </row>
     <row r="639" spans="1:14">
       <c r="A639" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B639" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C639" t="s">
         <v>685</v>
@@ -32368,7 +32380,7 @@
         <v>729208241403</v>
       </c>
       <c r="B640" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C640" t="s">
         <v>685</v>
@@ -32409,7 +32421,7 @@
         <v>731299174584</v>
       </c>
       <c r="B641" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C641" t="s">
         <v>685</v>
@@ -32418,7 +32430,7 @@
         <v>31</v>
       </c>
       <c r="E641" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F641">
         <v>7500</v>
@@ -32450,10 +32462,10 @@
     </row>
     <row r="642" spans="1:14">
       <c r="A642" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B642" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C642" t="s">
         <v>685</v>
@@ -32494,7 +32506,7 @@
         <v>731299174218</v>
       </c>
       <c r="B643" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C643" t="s">
         <v>685</v>
@@ -32503,7 +32515,7 @@
         <v>31</v>
       </c>
       <c r="E643" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F643">
         <v>12037</v>
@@ -32535,10 +32547,10 @@
     </row>
     <row r="644" spans="1:14">
       <c r="A644" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B644" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C644" t="s">
         <v>685</v>
@@ -32579,10 +32591,10 @@
     </row>
     <row r="645" spans="1:14">
       <c r="A645" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="B645" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="C645" t="s">
         <v>685</v>
@@ -32623,10 +32635,10 @@
     </row>
     <row r="646" spans="1:14">
       <c r="A646" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="B646" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="C646" t="s">
         <v>685</v>
@@ -32664,10 +32676,10 @@
     </row>
     <row r="647" spans="1:14">
       <c r="A647" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B647" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C647" t="s">
         <v>685</v>
@@ -32705,10 +32717,10 @@
     </row>
     <row r="648" spans="1:14">
       <c r="A648" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B648" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C648" t="s">
         <v>685</v>
@@ -32749,10 +32761,10 @@
     </row>
     <row r="649" spans="1:14">
       <c r="A649" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B649" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C649" t="s">
         <v>685</v>
@@ -32790,10 +32802,10 @@
     </row>
     <row r="650" spans="1:14">
       <c r="A650" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B650" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C650" t="s">
         <v>685</v>
@@ -32831,10 +32843,10 @@
     </row>
     <row r="651" spans="1:14">
       <c r="A651" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B651" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C651" t="s">
         <v>587</v>
@@ -32872,10 +32884,10 @@
     </row>
     <row r="652" spans="1:14">
       <c r="A652" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B652" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C652" t="s">
         <v>58</v>
@@ -32916,7 +32928,7 @@
         <v>7894561238520</v>
       </c>
       <c r="B653" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="C653" t="s">
         <v>417</v>
@@ -32954,7 +32966,7 @@
         <v>7799135017115</v>
       </c>
       <c r="B654" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C654" t="s">
         <v>414</v>
@@ -32998,7 +33010,7 @@
         <v>6975340320320</v>
       </c>
       <c r="B655" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C655" t="s">
         <v>414</v>
@@ -33036,10 +33048,10 @@
     </row>
     <row r="656" spans="1:14">
       <c r="A656" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B656" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C656" t="s">
         <v>423</v>
@@ -33083,16 +33095,16 @@
         <v>740617309928</v>
       </c>
       <c r="B657" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C657" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D657" t="s">
         <v>17</v>
       </c>
       <c r="E657" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F657">
         <v>6600</v>
@@ -33127,16 +33139,16 @@
         <v>740617300161</v>
       </c>
       <c r="B658" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C658" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D658" t="s">
         <v>17</v>
       </c>
       <c r="E658" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F658">
         <v>3700</v>
@@ -33171,16 +33183,16 @@
         <v>619659069193</v>
       </c>
       <c r="B659" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C659" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D659" t="s">
         <v>59</v>
       </c>
       <c r="E659" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F659">
         <v>6932</v>
@@ -33215,16 +33227,16 @@
         <v>740617309645</v>
       </c>
       <c r="B660" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C660" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D660" t="s">
         <v>17</v>
       </c>
       <c r="E660" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F660">
         <v>8245</v>
@@ -33259,16 +33271,16 @@
         <v>740617300086</v>
       </c>
       <c r="B661" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C661" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D661" t="s">
         <v>17</v>
       </c>
       <c r="E661" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F661">
         <v>3400</v>
@@ -33300,10 +33312,10 @@
     </row>
     <row r="662" spans="1:14">
       <c r="A662" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B662" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C662" t="s">
         <v>423</v>
@@ -33341,10 +33353,10 @@
     </row>
     <row r="663" spans="1:14">
       <c r="A663" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B663" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C663" t="s">
         <v>302</v>
@@ -33385,7 +33397,7 @@
         <v>7798137383488</v>
       </c>
       <c r="B664" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="C664" t="s">
         <v>417</v>
@@ -33429,7 +33441,7 @@
         <v>6970703342117</v>
       </c>
       <c r="B665" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C665" t="s">
         <v>417</v>
@@ -33438,7 +33450,7 @@
         <v>49</v>
       </c>
       <c r="E665" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="F665">
         <v>347.33</v>
@@ -33473,7 +33485,7 @@
         <v>6970703340038</v>
       </c>
       <c r="B666" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="C666" t="s">
         <v>417</v>
@@ -33482,7 +33494,7 @@
         <v>49</v>
       </c>
       <c r="E666" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="F666">
         <v>260.51</v>
@@ -33517,7 +33529,7 @@
         <v>7798137697264</v>
       </c>
       <c r="B667" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C667" t="s">
         <v>417</v>
@@ -33558,16 +33570,16 @@
     </row>
     <row r="668" spans="1:14">
       <c r="A668" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B668" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C668" t="s">
         <v>417</v>
       </c>
       <c r="E668" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F668">
         <v>980</v>
@@ -33602,7 +33614,7 @@
         <v>7899386518000</v>
       </c>
       <c r="B669" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C669" t="s">
         <v>417</v>
@@ -33640,7 +33652,7 @@
         <v>6973417640203</v>
       </c>
       <c r="B670" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="C670" t="s">
         <v>417</v>
@@ -33681,7 +33693,7 @@
         <v>6973417640272</v>
       </c>
       <c r="B671" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C671" t="s">
         <v>417</v>
@@ -33722,7 +33734,7 @@
         <v>6972676900028</v>
       </c>
       <c r="B672" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C672" t="s">
         <v>417</v>
@@ -33763,7 +33775,7 @@
         <v>6936709099868</v>
       </c>
       <c r="B673" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C673" t="s">
         <v>417</v>
@@ -33801,10 +33813,10 @@
     </row>
     <row r="674" spans="1:14">
       <c r="A674" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="B674" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C674" t="s">
         <v>417</v>
@@ -33842,7 +33854,7 @@
         <v>6936709099851</v>
       </c>
       <c r="B675" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C675" t="s">
         <v>417</v>
@@ -33851,7 +33863,7 @@
         <v>17</v>
       </c>
       <c r="E675" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="F675">
         <v>300</v>
@@ -33886,7 +33898,7 @@
         <v>6927799683761</v>
       </c>
       <c r="B676" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C676" t="s">
         <v>417</v>
@@ -33927,7 +33939,7 @@
         <v>6927799681101</v>
       </c>
       <c r="B677" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C677" t="s">
         <v>417</v>
@@ -33968,7 +33980,7 @@
         <v>6927799681132</v>
       </c>
       <c r="B678" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C678" t="s">
         <v>417</v>
@@ -34009,7 +34021,7 @@
         <v>6927799683785</v>
       </c>
       <c r="B679" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C679" t="s">
         <v>417</v>
@@ -34050,7 +34062,7 @@
         <v>6927799681040</v>
       </c>
       <c r="B680" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C680" t="s">
         <v>417</v>
@@ -34091,7 +34103,7 @@
         <v>6927799689619</v>
       </c>
       <c r="B681" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C681" t="s">
         <v>417</v>
@@ -34132,7 +34144,7 @@
         <v>6927799689626</v>
       </c>
       <c r="B682" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="C682" t="s">
         <v>417</v>
@@ -34173,7 +34185,7 @@
         <v>6927799689633</v>
       </c>
       <c r="B683" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C683" t="s">
         <v>417</v>
@@ -34214,10 +34226,10 @@
     </row>
     <row r="684" spans="1:14">
       <c r="A684" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B684" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C684" t="s">
         <v>595</v>
@@ -34255,10 +34267,10 @@
     </row>
     <row r="685" spans="1:14">
       <c r="A685" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B685" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C685" t="s">
         <v>595</v>
@@ -34293,10 +34305,10 @@
     </row>
     <row r="686" spans="1:14">
       <c r="A686" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="B686" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C686" t="s">
         <v>595</v>
@@ -34331,10 +34343,10 @@
     </row>
     <row r="687" spans="1:14">
       <c r="A687" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B687" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C687" t="s">
         <v>595</v>
@@ -34372,10 +34384,10 @@
     </row>
     <row r="688" spans="1:14">
       <c r="A688" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B688" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C688" t="s">
         <v>595</v>
@@ -34410,10 +34422,10 @@
     </row>
     <row r="689" spans="1:14">
       <c r="A689" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B689" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C689" t="s">
         <v>595</v>
@@ -34448,10 +34460,10 @@
     </row>
     <row r="690" spans="1:14">
       <c r="A690" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B690" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C690" t="s">
         <v>595</v>
@@ -34492,7 +34504,7 @@
         <v>6978526354010</v>
       </c>
       <c r="B691" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C691" t="s">
         <v>77</v>
@@ -34536,7 +34548,7 @@
         <v>7899441528562</v>
       </c>
       <c r="B692" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C692" t="s">
         <v>417</v>
@@ -34571,10 +34583,10 @@
     </row>
     <row r="693" spans="1:14">
       <c r="A693" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B693" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C693" t="s">
         <v>423</v>
@@ -34615,10 +34627,10 @@
     </row>
     <row r="694" spans="1:14">
       <c r="A694" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B694" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C694" t="s">
         <v>502</v>
@@ -34656,10 +34668,10 @@
     </row>
     <row r="695" spans="1:14">
       <c r="A695" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B695" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C695" t="s">
         <v>423</v>
@@ -34700,13 +34712,13 @@
     </row>
     <row r="696" spans="1:14">
       <c r="A696" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B696" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C696" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D696" t="s">
         <v>208</v>
@@ -34744,13 +34756,13 @@
     </row>
     <row r="697" spans="1:14">
       <c r="A697" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B697" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C697" t="s">
         <v>1295</v>
-      </c>
-      <c r="C697" t="s">
-        <v>1293</v>
       </c>
       <c r="D697" t="s">
         <v>205</v>
@@ -34788,16 +34800,16 @@
     </row>
     <row r="698" spans="1:14">
       <c r="A698" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B698" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C698" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D698" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E698" t="s">
         <v>264</v>
@@ -34832,13 +34844,13 @@
     </row>
     <row r="699" spans="1:14">
       <c r="A699" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B699" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C699" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D699" t="s">
         <v>208</v>
@@ -34876,13 +34888,13 @@
     </row>
     <row r="700" spans="1:14">
       <c r="A700" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B700" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C700" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D700" t="s">
         <v>208</v>
@@ -34920,13 +34932,13 @@
     </row>
     <row r="701" spans="1:14">
       <c r="A701" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="B701" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="C701" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D701" t="s">
         <v>208</v>
@@ -34964,13 +34976,13 @@
     </row>
     <row r="702" spans="1:14">
       <c r="A702" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B702" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C702" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D702" t="s">
         <v>208</v>
@@ -35008,13 +35020,13 @@
     </row>
     <row r="703" spans="1:14">
       <c r="A703" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B703" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C703" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D703" t="s">
         <v>208</v>
@@ -35052,13 +35064,13 @@
     </row>
     <row r="704" spans="1:14">
       <c r="A704" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B704" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C704" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D704" t="s">
         <v>208</v>
@@ -35096,13 +35108,13 @@
     </row>
     <row r="705" spans="1:14">
       <c r="A705" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B705" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C705" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D705" t="s">
         <v>208</v>
@@ -35140,13 +35152,13 @@
     </row>
     <row r="706" spans="1:14">
       <c r="A706" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B706" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C706" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D706" t="s">
         <v>208</v>
@@ -35184,13 +35196,13 @@
     </row>
     <row r="707" spans="1:14">
       <c r="A707" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="B707" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C707" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D707" t="s">
         <v>208</v>
@@ -35228,13 +35240,13 @@
     </row>
     <row r="708" spans="1:14">
       <c r="A708" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="B708" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C708" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D708" t="s">
         <v>208</v>
@@ -35272,13 +35284,13 @@
     </row>
     <row r="709" spans="1:14">
       <c r="A709" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B709" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C709" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D709" t="s">
         <v>208</v>
@@ -35316,13 +35328,13 @@
     </row>
     <row r="710" spans="1:14">
       <c r="A710" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B710" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C710" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D710" t="s">
         <v>208</v>
@@ -35360,13 +35372,13 @@
     </row>
     <row r="711" spans="1:14">
       <c r="A711" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B711" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C711" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D711" t="s">
         <v>208</v>
@@ -35404,13 +35416,13 @@
     </row>
     <row r="712" spans="1:14">
       <c r="A712" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B712" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C712" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D712" t="s">
         <v>208</v>
@@ -35448,13 +35460,13 @@
     </row>
     <row r="713" spans="1:14">
       <c r="A713" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B713" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C713" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D713" t="s">
         <v>208</v>
@@ -35492,13 +35504,13 @@
     </row>
     <row r="714" spans="1:14">
       <c r="A714" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B714" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C714" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D714" t="s">
         <v>208</v>
@@ -35536,13 +35548,13 @@
     </row>
     <row r="715" spans="1:14">
       <c r="A715" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B715" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C715" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D715" t="s">
         <v>208</v>
@@ -35580,13 +35592,13 @@
     </row>
     <row r="716" spans="1:14">
       <c r="A716" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B716" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C716" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D716" t="s">
         <v>205</v>
@@ -35624,13 +35636,13 @@
     </row>
     <row r="717" spans="1:14">
       <c r="A717" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B717" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C717" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D717" t="s">
         <v>208</v>
@@ -35668,13 +35680,13 @@
     </row>
     <row r="718" spans="1:14">
       <c r="A718" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="B718" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="C718" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D718" t="s">
         <v>205</v>
@@ -35712,13 +35724,13 @@
     </row>
     <row r="719" spans="1:14">
       <c r="A719" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B719" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="C719" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D719" t="s">
         <v>205</v>
@@ -35753,13 +35765,13 @@
     </row>
     <row r="720" spans="1:14">
       <c r="A720" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B720" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C720" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D720" t="s">
         <v>208</v>
@@ -35797,13 +35809,13 @@
     </row>
     <row r="721" spans="1:14">
       <c r="A721" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B721" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C721" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D721" t="s">
         <v>208</v>
@@ -35841,13 +35853,13 @@
     </row>
     <row r="722" spans="1:14">
       <c r="A722" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B722" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C722" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D722" t="s">
         <v>208</v>
@@ -35885,13 +35897,13 @@
     </row>
     <row r="723" spans="1:14">
       <c r="A723" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B723" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C723" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D723" t="s">
         <v>208</v>
@@ -35929,13 +35941,13 @@
     </row>
     <row r="724" spans="1:14">
       <c r="A724" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B724" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C724" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D724" t="s">
         <v>208</v>
@@ -35973,13 +35985,13 @@
     </row>
     <row r="725" spans="1:14">
       <c r="A725" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B725" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C725" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D725" t="s">
         <v>208</v>
@@ -36017,13 +36029,13 @@
     </row>
     <row r="726" spans="1:14">
       <c r="A726" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B726" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C726" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D726" t="s">
         <v>208</v>
@@ -36061,13 +36073,13 @@
     </row>
     <row r="727" spans="1:14">
       <c r="A727" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B727" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C727" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D727" t="s">
         <v>208</v>
@@ -36105,13 +36117,13 @@
     </row>
     <row r="728" spans="1:14">
       <c r="A728" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B728" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C728" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D728" t="s">
         <v>208</v>
@@ -36149,13 +36161,13 @@
     </row>
     <row r="729" spans="1:14">
       <c r="A729" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B729" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="C729" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D729" t="s">
         <v>208</v>
@@ -36193,13 +36205,13 @@
     </row>
     <row r="730" spans="1:14">
       <c r="A730" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B730" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C730" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D730" t="s">
         <v>208</v>
@@ -36237,13 +36249,13 @@
     </row>
     <row r="731" spans="1:14">
       <c r="A731" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B731" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C731" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D731" t="s">
         <v>205</v>
@@ -36281,13 +36293,13 @@
     </row>
     <row r="732" spans="1:14">
       <c r="A732" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B732" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C732" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D732" t="s">
         <v>208</v>
@@ -36325,13 +36337,13 @@
     </row>
     <row r="733" spans="1:14">
       <c r="A733" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B733" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C733" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D733" t="s">
         <v>208</v>
@@ -36369,13 +36381,13 @@
     </row>
     <row r="734" spans="1:14">
       <c r="A734" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B734" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C734" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D734" t="s">
         <v>208</v>
@@ -36413,13 +36425,13 @@
     </row>
     <row r="735" spans="1:14">
       <c r="A735" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B735" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="C735" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D735" t="s">
         <v>208</v>
@@ -36457,13 +36469,13 @@
     </row>
     <row r="736" spans="1:14">
       <c r="A736" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B736" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C736" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D736" t="s">
         <v>208</v>
@@ -36501,13 +36513,13 @@
     </row>
     <row r="737" spans="1:14">
       <c r="A737" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B737" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C737" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D737" t="s">
         <v>208</v>
@@ -36545,13 +36557,13 @@
     </row>
     <row r="738" spans="1:14">
       <c r="A738" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B738" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="C738" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E738" t="s">
         <v>178</v>
@@ -36586,13 +36598,13 @@
     </row>
     <row r="739" spans="1:14">
       <c r="A739" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B739" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C739" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D739" t="s">
         <v>208</v>
@@ -36630,13 +36642,13 @@
     </row>
     <row r="740" spans="1:14">
       <c r="A740" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B740" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C740" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D740" t="s">
         <v>208</v>
@@ -36674,13 +36686,13 @@
     </row>
     <row r="741" spans="1:14">
       <c r="A741" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B741" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C741" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D741" t="s">
         <v>208</v>
@@ -36718,13 +36730,13 @@
     </row>
     <row r="742" spans="1:14">
       <c r="A742" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B742" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="C742" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D742" t="s">
         <v>208</v>
@@ -36762,16 +36774,16 @@
     </row>
     <row r="743" spans="1:14">
       <c r="A743" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B743" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C743" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D743" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E743" t="s">
         <v>264</v>
@@ -36806,13 +36818,13 @@
     </row>
     <row r="744" spans="1:14">
       <c r="A744" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B744" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="C744" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D744" t="s">
         <v>208</v>
@@ -36850,13 +36862,13 @@
     </row>
     <row r="745" spans="1:14">
       <c r="A745" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B745" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="C745" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D745" t="s">
         <v>208</v>
@@ -36894,13 +36906,13 @@
     </row>
     <row r="746" spans="1:14">
       <c r="A746" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B746" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C746" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D746" t="s">
         <v>208</v>
@@ -36938,13 +36950,13 @@
     </row>
     <row r="747" spans="1:14">
       <c r="A747" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B747" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="C747" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D747" t="s">
         <v>208</v>
@@ -36982,13 +36994,13 @@
     </row>
     <row r="748" spans="1:14">
       <c r="A748" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B748" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="C748" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D748" t="s">
         <v>205</v>
@@ -37026,13 +37038,13 @@
     </row>
     <row r="749" spans="1:14">
       <c r="A749" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B749" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="C749" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D749" t="s">
         <v>208</v>
@@ -37070,13 +37082,13 @@
     </row>
     <row r="750" spans="1:14">
       <c r="A750" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B750" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="C750" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D750" t="s">
         <v>208</v>
@@ -37114,13 +37126,13 @@
     </row>
     <row r="751" spans="1:14">
       <c r="A751" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B751" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="C751" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D751" t="s">
         <v>208</v>
@@ -37158,13 +37170,13 @@
     </row>
     <row r="752" spans="1:14">
       <c r="A752" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B752" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C752" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D752" t="s">
         <v>205</v>
@@ -37202,13 +37214,13 @@
     </row>
     <row r="753" spans="1:14">
       <c r="A753" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B753" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="C753" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D753" t="s">
         <v>208</v>
@@ -37246,16 +37258,16 @@
     </row>
     <row r="754" spans="1:14">
       <c r="A754" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="B754" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="C754" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D754" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E754" t="s">
         <v>264</v>
@@ -37290,19 +37302,19 @@
     </row>
     <row r="755" spans="1:14">
       <c r="A755" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B755" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="C755" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D755" t="s">
         <v>208</v>
       </c>
       <c r="E755" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F755">
         <v>2500</v>
@@ -37334,19 +37346,19 @@
     </row>
     <row r="756" spans="1:14">
       <c r="A756" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B756" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="C756" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D756" t="s">
         <v>208</v>
       </c>
       <c r="E756" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F756">
         <v>2200</v>
@@ -37381,7 +37393,7 @@
         <v>723540565531</v>
       </c>
       <c r="B757" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="C757" t="s">
         <v>20</v>
@@ -37422,7 +37434,7 @@
         <v>723540564848</v>
       </c>
       <c r="B758" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C758" t="s">
         <v>298</v>
@@ -37463,7 +37475,7 @@
         <v>7798371200725</v>
       </c>
       <c r="B759" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="C759" t="s">
         <v>58</v>
@@ -37472,7 +37484,7 @@
         <v>59</v>
       </c>
       <c r="E759" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="F759">
         <v>9400</v>
@@ -37507,7 +37519,7 @@
         <v>7798371200749</v>
       </c>
       <c r="B760" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="C760" t="s">
         <v>58</v>
@@ -37516,7 +37528,7 @@
         <v>59</v>
       </c>
       <c r="E760" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="F760">
         <v>18700</v>
@@ -37551,7 +37563,7 @@
         <v>1134338992788</v>
       </c>
       <c r="B761" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C761" t="s">
         <v>298</v>
@@ -37589,10 +37601,10 @@
     </row>
     <row r="762" spans="1:14">
       <c r="A762" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B762" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="C762" t="s">
         <v>298</v>
@@ -37636,7 +37648,7 @@
         <v>6963490162624</v>
       </c>
       <c r="B763" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="C763" t="s">
         <v>298</v>
@@ -37677,7 +37689,7 @@
         <v>6963490162655</v>
       </c>
       <c r="B764" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C764" t="s">
         <v>298</v>
@@ -37715,10 +37727,10 @@
     </row>
     <row r="765" spans="1:14">
       <c r="A765" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B765" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C765" t="s">
         <v>298</v>
@@ -37759,13 +37771,13 @@
         <v>6972910590206</v>
       </c>
       <c r="B766" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C766" t="s">
         <v>417</v>
       </c>
       <c r="E766" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F766">
         <v>8000</v>
@@ -37797,10 +37809,10 @@
     </row>
     <row r="767" spans="1:14">
       <c r="A767" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B767" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C767" t="s">
         <v>502</v>
@@ -37809,7 +37821,7 @@
         <v>28</v>
       </c>
       <c r="E767" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F767">
         <v>3900</v>
@@ -37841,10 +37853,10 @@
     </row>
     <row r="768" spans="1:14">
       <c r="A768" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B768" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C768" t="s">
         <v>502</v>
@@ -37853,7 +37865,7 @@
         <v>31</v>
       </c>
       <c r="E768" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F768">
         <v>2907</v>
@@ -37885,10 +37897,10 @@
     </row>
     <row r="769" spans="1:14">
       <c r="A769" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B769" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C769" t="s">
         <v>502</v>
@@ -37897,7 +37909,7 @@
         <v>31</v>
       </c>
       <c r="E769" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F769">
         <v>2907</v>
@@ -37929,10 +37941,10 @@
     </row>
     <row r="770" spans="1:14">
       <c r="A770" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B770" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="C770" t="s">
         <v>502</v>
@@ -37941,7 +37953,7 @@
         <v>31</v>
       </c>
       <c r="E770" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F770">
         <v>2907</v>
@@ -37973,10 +37985,10 @@
     </row>
     <row r="771" spans="1:14">
       <c r="A771" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B771" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C771" t="s">
         <v>502</v>
@@ -37985,7 +37997,7 @@
         <v>28</v>
       </c>
       <c r="E771" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F771">
         <v>1900</v>
@@ -38017,10 +38029,10 @@
     </row>
     <row r="772" spans="1:14">
       <c r="A772" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B772" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C772" t="s">
         <v>502</v>
@@ -38029,7 +38041,7 @@
         <v>28</v>
       </c>
       <c r="E772" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F772">
         <v>3900</v>
@@ -38061,10 +38073,10 @@
     </row>
     <row r="773" spans="1:14">
       <c r="A773" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B773" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C773" t="s">
         <v>502</v>
@@ -38073,7 +38085,7 @@
         <v>28</v>
       </c>
       <c r="E773" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F773">
         <v>3900</v>
@@ -38105,10 +38117,10 @@
     </row>
     <row r="774" spans="1:14">
       <c r="A774" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="B774" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C774" t="s">
         <v>67</v>
@@ -38146,10 +38158,10 @@
     </row>
     <row r="775" spans="1:14">
       <c r="A775" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="B775" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C775" t="s">
         <v>417</v>
@@ -38187,7 +38199,7 @@
         <v>7799135017122</v>
       </c>
       <c r="B776" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C776" t="s">
         <v>414</v>
@@ -38231,7 +38243,7 @@
         <v>7799135016552</v>
       </c>
       <c r="B777" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C777" t="s">
         <v>414</v>
@@ -38269,10 +38281,10 @@
     </row>
     <row r="778" spans="1:14">
       <c r="A778" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B778" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C778" t="s">
         <v>685</v>
@@ -38313,10 +38325,10 @@
     </row>
     <row r="779" spans="1:14">
       <c r="A779" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B779" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C779" t="s">
         <v>685</v>
@@ -38357,7 +38369,7 @@
         <v>6971131410669</v>
       </c>
       <c r="B780" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C780" t="s">
         <v>685</v>
@@ -38398,7 +38410,7 @@
         <v>7799061002889</v>
       </c>
       <c r="B781" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="C781" t="s">
         <v>685</v>
@@ -38407,7 +38419,7 @@
         <v>31</v>
       </c>
       <c r="E781" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="F781">
         <v>6014</v>
@@ -38439,7 +38451,7 @@
     </row>
     <row r="782" spans="1:14">
       <c r="B782" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="C782" t="s">
         <v>685</v>
@@ -38477,7 +38489,7 @@
     </row>
     <row r="783" spans="1:14">
       <c r="B783" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C783" t="s">
         <v>417</v>
@@ -38515,7 +38527,7 @@
         <v>7891122335568</v>
       </c>
       <c r="B784" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C784" t="s">
         <v>16</v>
@@ -38556,7 +38568,7 @@
         <v>778145003222</v>
       </c>
       <c r="B785" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C785" t="s">
         <v>16</v>
@@ -38597,7 +38609,7 @@
         <v>672852519025</v>
       </c>
       <c r="B786" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C786" t="s">
         <v>587</v>
@@ -38635,10 +38647,10 @@
     </row>
     <row r="787" spans="1:14">
       <c r="A787" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B787" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C787" t="s">
         <v>366</v>
@@ -38676,10 +38688,10 @@
     </row>
     <row r="788" spans="1:14">
       <c r="A788" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B788" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C788" t="s">
         <v>366</v>
@@ -38720,7 +38732,7 @@
         <v>7799135011984</v>
       </c>
       <c r="B789" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C789" t="s">
         <v>366</v>
@@ -38764,7 +38776,7 @@
         <v>7798397481009</v>
       </c>
       <c r="B790" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C790" t="s">
         <v>366</v>
@@ -38808,7 +38820,7 @@
         <v>7799135011861</v>
       </c>
       <c r="B791" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C791" t="s">
         <v>366</v>
@@ -38852,7 +38864,7 @@
         <v>7895168020167</v>
       </c>
       <c r="B792" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C792" t="s">
         <v>366</v>
@@ -38890,10 +38902,10 @@
     </row>
     <row r="793" spans="1:14">
       <c r="A793" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B793" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C793" t="s">
         <v>366</v>
@@ -38934,7 +38946,7 @@
         <v>7798347600771</v>
       </c>
       <c r="B794" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C794" t="s">
         <v>302</v>
@@ -38975,7 +38987,7 @@
         <v>6975842015761</v>
       </c>
       <c r="B795" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C795" t="s">
         <v>302</v>
@@ -39016,7 +39028,7 @@
         <v>7798347600801</v>
       </c>
       <c r="B796" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C796" t="s">
         <v>302</v>
@@ -39054,10 +39066,10 @@
     </row>
     <row r="797" spans="1:14">
       <c r="A797" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B797" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C797" t="s">
         <v>510</v>
@@ -39095,10 +39107,10 @@
     </row>
     <row r="798" spans="1:14">
       <c r="A798" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B798" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C798" t="s">
         <v>417</v>
@@ -39139,7 +39151,7 @@
         <v>7798145004559</v>
       </c>
       <c r="B799" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="C799" t="s">
         <v>298</v>
@@ -39177,10 +39189,10 @@
     </row>
     <row r="800" spans="1:14">
       <c r="A800" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B800" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C800" t="s">
         <v>38</v>
@@ -39218,10 +39230,10 @@
     </row>
     <row r="801" spans="1:14">
       <c r="A801" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B801" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C801" t="s">
         <v>38</v>
@@ -39259,10 +39271,10 @@
     </row>
     <row r="802" spans="1:14">
       <c r="A802" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B802" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C802" t="s">
         <v>417</v>
@@ -39303,7 +39315,7 @@
         <v>6904004020214</v>
       </c>
       <c r="B803" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C803" t="s">
         <v>58</v>
@@ -39341,10 +39353,10 @@
     </row>
     <row r="804" spans="1:14">
       <c r="A804" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B804" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C804" t="s">
         <v>58</v>
@@ -39388,7 +39400,7 @@
         <v>6972831212331</v>
       </c>
       <c r="B805" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C805" t="s">
         <v>298</v>
@@ -39429,10 +39441,10 @@
     </row>
     <row r="806" spans="1:14">
       <c r="A806" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B806" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C806" t="s">
         <v>298</v>
@@ -39476,7 +39488,7 @@
         <v>723540564824</v>
       </c>
       <c r="B807" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C807" t="s">
         <v>302</v>
@@ -39517,7 +39529,7 @@
         <v>6958210712401</v>
       </c>
       <c r="B808" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="C808" t="s">
         <v>298</v>
@@ -39561,7 +39573,7 @@
         <v>6963490162686</v>
       </c>
       <c r="B809" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C809" t="s">
         <v>298</v>
@@ -39602,7 +39614,7 @@
         <v>6955549333260</v>
       </c>
       <c r="B810" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="C810" t="s">
         <v>298</v>
@@ -39611,7 +39623,7 @@
         <v>49</v>
       </c>
       <c r="E810" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="F810">
         <v>10500</v>
@@ -39646,7 +39658,7 @@
         <v>8201756735006</v>
       </c>
       <c r="B811" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C811" t="s">
         <v>429</v>
@@ -39690,7 +39702,7 @@
         <v>763571815083</v>
       </c>
       <c r="B812" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="C812" t="s">
         <v>77</v>
@@ -39731,7 +39743,7 @@
         <v>8214729653849</v>
       </c>
       <c r="B813" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C813" t="s">
         <v>77</v>
@@ -39769,10 +39781,10 @@
     </row>
     <row r="814" spans="1:14">
       <c r="A814" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B814" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C814" t="s">
         <v>77</v>
@@ -39813,7 +39825,7 @@
         <v>5901234123457</v>
       </c>
       <c r="B815" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="C815" t="s">
         <v>64</v>
@@ -39854,7 +39866,7 @@
         <v>723540564831</v>
       </c>
       <c r="B816" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C816" t="s">
         <v>64</v>
@@ -39863,7 +39875,7 @@
         <v>31</v>
       </c>
       <c r="E816" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="F816">
         <v>21500</v>
@@ -39898,7 +39910,7 @@
         <v>7799135013018</v>
       </c>
       <c r="B817" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="C817" t="s">
         <v>64</v>
@@ -39942,7 +39954,7 @@
         <v>6988886869543</v>
       </c>
       <c r="B818" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C818" t="s">
         <v>74</v>
@@ -39980,10 +39992,10 @@
     </row>
     <row r="819" spans="1:14">
       <c r="A819" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B819" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="C819" t="s">
         <v>74</v>
@@ -40021,10 +40033,10 @@
     </row>
     <row r="820" spans="1:14">
       <c r="A820" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B820" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C820" t="s">
         <v>74</v>
@@ -40062,10 +40074,10 @@
     </row>
     <row r="821" spans="1:14">
       <c r="A821" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B821" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C821" t="s">
         <v>74</v>
@@ -40103,10 +40115,10 @@
     </row>
     <row r="822" spans="1:14">
       <c r="A822" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="B822" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C822" t="s">
         <v>74</v>
@@ -40144,10 +40156,10 @@
     </row>
     <row r="823" spans="1:14">
       <c r="A823" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B823" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C823" t="s">
         <v>74</v>
@@ -40188,7 +40200,7 @@
         <v>7821234522365</v>
       </c>
       <c r="B824" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="C824" t="s">
         <v>74</v>
@@ -40226,10 +40238,10 @@
     </row>
     <row r="825" spans="1:14">
       <c r="A825" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B825" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="C825" t="s">
         <v>74</v>
@@ -40267,10 +40279,10 @@
     </row>
     <row r="826" spans="1:14">
       <c r="A826" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B826" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C826" t="s">
         <v>74</v>
@@ -40308,10 +40320,10 @@
     </row>
     <row r="827" spans="1:14">
       <c r="A827" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B827" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C827" t="s">
         <v>74</v>
@@ -40352,10 +40364,10 @@
     </row>
     <row r="828" spans="1:14">
       <c r="A828" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B828" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C828" t="s">
         <v>74</v>
@@ -40396,7 +40408,7 @@
         <v>7798145005969</v>
       </c>
       <c r="B829" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="C829" t="s">
         <v>74</v>
@@ -40437,7 +40449,7 @@
         <v>723540565012</v>
       </c>
       <c r="B830" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C830" t="s">
         <v>64</v>
@@ -40478,7 +40490,7 @@
         <v>7799135001664</v>
       </c>
       <c r="B831" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C831" t="s">
         <v>64</v>
@@ -40522,7 +40534,7 @@
         <v>7798423540649</v>
       </c>
       <c r="B832" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C832" t="s">
         <v>64</v>
@@ -40563,7 +40575,7 @@
         <v>7799135022195</v>
       </c>
       <c r="B833" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="C833" t="s">
         <v>64</v>
@@ -40604,7 +40616,7 @@
         <v>6974504501018</v>
       </c>
       <c r="B834" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C834" t="s">
         <v>64</v>
@@ -40642,10 +40654,10 @@
     </row>
     <row r="835" spans="1:14">
       <c r="A835" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B835" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="C835" t="s">
         <v>64</v>
@@ -40686,16 +40698,16 @@
         <v>843367116218</v>
       </c>
       <c r="B836" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="C836" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D836" t="s">
         <v>355</v>
       </c>
       <c r="E836" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="F836">
         <v>18444</v>
@@ -40730,16 +40742,16 @@
         <v>7448070134219</v>
       </c>
       <c r="B837" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="C837" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D837" t="s">
         <v>355</v>
       </c>
       <c r="E837" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="F837">
         <v>17600</v>
@@ -40771,10 +40783,10 @@
     </row>
     <row r="838" spans="1:14">
       <c r="A838" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B838" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="C838" t="s">
         <v>38</v>
@@ -40812,10 +40824,10 @@
     </row>
     <row r="839" spans="1:14">
       <c r="A839" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B839" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="C839" t="s">
         <v>38</v>
@@ -40853,10 +40865,10 @@
     </row>
     <row r="840" spans="1:14">
       <c r="A840" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B840" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C840" t="s">
         <v>414</v>
@@ -40897,10 +40909,10 @@
     </row>
     <row r="841" spans="1:14">
       <c r="A841" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B841" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="C841" t="s">
         <v>502</v>
@@ -40938,16 +40950,16 @@
     </row>
     <row r="842" spans="1:14">
       <c r="A842" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B842" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="C842" t="s">
         <v>510</v>
       </c>
       <c r="E842" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="F842">
         <v>1000</v>
@@ -40982,7 +40994,7 @@
         <v>7799135009790</v>
       </c>
       <c r="B843" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="C843" t="s">
         <v>429</v>
@@ -41023,7 +41035,7 @@
         <v>700306601221</v>
       </c>
       <c r="B844" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C844" t="s">
         <v>429</v>
@@ -41061,13 +41073,13 @@
     </row>
     <row r="845" spans="1:14">
       <c r="A845" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B845" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="C845" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D845" t="s">
         <v>31</v>
@@ -41102,10 +41114,10 @@
     </row>
     <row r="846" spans="1:14">
       <c r="A846" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B846" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C846" t="s">
         <v>294</v>
@@ -41143,10 +41155,10 @@
     </row>
     <row r="847" spans="1:14">
       <c r="A847" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B847" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C847" t="s">
         <v>58</v>
@@ -41184,10 +41196,10 @@
     </row>
     <row r="848" spans="1:14">
       <c r="A848" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B848" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C848" t="s">
         <v>417</v>
@@ -41228,7 +41240,7 @@
         <v>7798423541356</v>
       </c>
       <c r="B849" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="C849" t="s">
         <v>77</v>
@@ -41269,7 +41281,7 @@
         <v>7798145006027</v>
       </c>
       <c r="B850" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C850" t="s">
         <v>502</v>
@@ -41310,7 +41322,7 @@
         <v>69855646885262</v>
       </c>
       <c r="B851" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C851" t="s">
         <v>502</v>
@@ -41319,7 +41331,7 @@
         <v>31</v>
       </c>
       <c r="E851" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="F851">
         <v>2629</v>
@@ -41354,7 +41366,7 @@
         <v>6985564688526</v>
       </c>
       <c r="B852" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="C852" t="s">
         <v>502</v>
@@ -41363,7 +41375,7 @@
         <v>31</v>
       </c>
       <c r="E852" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="F852">
         <v>2629</v>
@@ -41398,7 +41410,7 @@
         <v>7790000111020</v>
       </c>
       <c r="B853" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C853" t="s">
         <v>417</v>
@@ -41439,7 +41451,7 @@
         <v>6920220096888</v>
       </c>
       <c r="B854" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="C854" t="s">
         <v>53</v>
@@ -41477,10 +41489,10 @@
     </row>
     <row r="855" spans="1:14">
       <c r="A855" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B855" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="C855" t="s">
         <v>67</v>
@@ -41521,7 +41533,7 @@
         <v>7795234526572</v>
       </c>
       <c r="B856" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C856" t="s">
         <v>67</v>
@@ -41559,10 +41571,10 @@
     </row>
     <row r="857" spans="1:14">
       <c r="A857" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B857" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="C857" t="s">
         <v>67</v>
@@ -41600,10 +41612,10 @@
     </row>
     <row r="858" spans="1:14">
       <c r="A858" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B858" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C858" t="s">
         <v>67</v>
@@ -41641,10 +41653,10 @@
     </row>
     <row r="859" spans="1:14">
       <c r="A859" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B859" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="C859" t="s">
         <v>302</v>
@@ -41682,10 +41694,10 @@
     </row>
     <row r="860" spans="1:14">
       <c r="A860" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B860" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C860" t="s">
         <v>302</v>
@@ -41726,7 +41738,7 @@
         <v>6902540752361</v>
       </c>
       <c r="B861" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C861" t="s">
         <v>302</v>
@@ -41764,10 +41776,10 @@
     </row>
     <row r="862" spans="1:14">
       <c r="A862" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B862" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C862" t="s">
         <v>58</v>
@@ -41808,7 +41820,7 @@
         <v>723540564022</v>
       </c>
       <c r="B863" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C863" t="s">
         <v>455</v>
@@ -41849,10 +41861,10 @@
     </row>
     <row r="864" spans="1:14">
       <c r="A864" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B864" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C864" t="s">
         <v>455</v>
@@ -41890,10 +41902,10 @@
     </row>
     <row r="865" spans="1:14">
       <c r="A865" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B865" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C865" t="s">
         <v>587</v>
@@ -41931,10 +41943,10 @@
     </row>
     <row r="866" spans="1:14">
       <c r="A866" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B866" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C866" t="s">
         <v>587</v>
@@ -41975,7 +41987,7 @@
         <v>7798347810224</v>
       </c>
       <c r="B867" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C867" t="s">
         <v>587</v>
@@ -41984,7 +41996,7 @@
         <v>49</v>
       </c>
       <c r="E867" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="F867">
         <v>3260</v>
@@ -42019,7 +42031,7 @@
         <v>7798347810569</v>
       </c>
       <c r="B868" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C868" t="s">
         <v>587</v>
@@ -42028,7 +42040,7 @@
         <v>49</v>
       </c>
       <c r="E868" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="F868">
         <v>3261</v>
@@ -42063,7 +42075,7 @@
         <v>6905416583656</v>
       </c>
       <c r="B869" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C869" t="s">
         <v>417</v>
@@ -42098,10 +42110,10 @@
     </row>
     <row r="870" spans="1:14">
       <c r="A870" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B870" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="C870" t="s">
         <v>77</v>
@@ -42139,10 +42151,10 @@
     </row>
     <row r="871" spans="1:14">
       <c r="A871" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B871" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C871" t="s">
         <v>67</v>
@@ -42183,7 +42195,7 @@
         <v>6459751458518</v>
       </c>
       <c r="B872" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C872" t="s">
         <v>74</v>
@@ -42221,10 +42233,10 @@
     </row>
     <row r="873" spans="1:14">
       <c r="A873" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B873" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="C873" t="s">
         <v>74</v>
@@ -42233,7 +42245,7 @@
         <v>31</v>
       </c>
       <c r="E873" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="F873">
         <v>5887</v>
@@ -42265,10 +42277,10 @@
     </row>
     <row r="874" spans="1:14">
       <c r="A874" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B874" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C874" t="s">
         <v>74</v>
@@ -42309,10 +42321,10 @@
     </row>
     <row r="875" spans="1:14">
       <c r="A875" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B875" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C875" t="s">
         <v>38</v>
@@ -42353,7 +42365,7 @@
         <v>6989526542239</v>
       </c>
       <c r="B876" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="C876" t="s">
         <v>74</v>
@@ -42391,10 +42403,10 @@
     </row>
     <row r="877" spans="1:14">
       <c r="A877" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B877" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="C877" t="s">
         <v>294</v>
@@ -42432,10 +42444,10 @@
     </row>
     <row r="878" spans="1:14">
       <c r="A878" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B878" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="C878" t="s">
         <v>294</v>
@@ -42476,7 +42488,7 @@
         <v>153500580</v>
       </c>
       <c r="B879" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C879" t="s">
         <v>67</v>
@@ -42514,10 +42526,10 @@
     </row>
     <row r="880" spans="1:14">
       <c r="A880" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B880" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="C880" t="s">
         <v>67</v>
@@ -42555,10 +42567,10 @@
     </row>
     <row r="881" spans="1:14">
       <c r="A881" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B881" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="C881" t="s">
         <v>67</v>
@@ -42596,10 +42608,10 @@
     </row>
     <row r="882" spans="1:14">
       <c r="A882" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="B882" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="C882" t="s">
         <v>67</v>
@@ -42643,7 +42655,7 @@
         <v>723540563780</v>
       </c>
       <c r="B883" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C883" t="s">
         <v>414</v>
@@ -42684,10 +42696,10 @@
     </row>
     <row r="884" spans="1:14">
       <c r="A884" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B884" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C884" t="s">
         <v>67</v>
@@ -42728,7 +42740,7 @@
         <v>7769528971157</v>
       </c>
       <c r="B885" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="C885" t="s">
         <v>67</v>
@@ -42766,10 +42778,10 @@
     </row>
     <row r="886" spans="1:14">
       <c r="A886" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B886" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="C886" t="s">
         <v>67</v>
@@ -42810,10 +42822,10 @@
     </row>
     <row r="887" spans="1:14">
       <c r="A887" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B887" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="C887" t="s">
         <v>38</v>
@@ -42854,7 +42866,7 @@
         <v>701575361335</v>
       </c>
       <c r="B888" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C888" t="s">
         <v>671</v>
@@ -42863,7 +42875,7 @@
         <v>49</v>
       </c>
       <c r="E888" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F888">
         <v>6467</v>
@@ -42895,10 +42907,10 @@
     </row>
     <row r="889" spans="1:14">
       <c r="A889" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B889" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C889" t="s">
         <v>590</v>
@@ -42936,10 +42948,10 @@
     </row>
     <row r="890" spans="1:14">
       <c r="A890" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B890" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="C890" t="s">
         <v>58</v>
@@ -42977,10 +42989,10 @@
     </row>
     <row r="891" spans="1:14">
       <c r="A891" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B891" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="C891" t="s">
         <v>20</v>
@@ -43018,10 +43030,10 @@
     </row>
     <row r="892" spans="1:14">
       <c r="A892" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B892" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="C892" t="s">
         <v>20</v>
@@ -43059,10 +43071,10 @@
     </row>
     <row r="893" spans="1:14">
       <c r="A893" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B893" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C893" t="s">
         <v>20</v>
@@ -43100,10 +43112,10 @@
     </row>
     <row r="894" spans="1:14">
       <c r="A894" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B894" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="C894" t="s">
         <v>20</v>
@@ -43112,7 +43124,7 @@
         <v>49</v>
       </c>
       <c r="E894" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="F894">
         <v>4588</v>
@@ -43147,7 +43159,7 @@
         <v>7796941141133</v>
       </c>
       <c r="B895" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="C895" t="s">
         <v>504</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C35B15D0-FAFC-437D-9FE8-D08CF2F19CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAB490CF-8FDE-43AC-89D3-2E0B37E28F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{01F4AF28-4509-40BD-BE22-A35F9BEC4B53}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{46ED21DB-057C-45C7-858F-B6F4D8D157F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5320,7 +5320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7DAD8C-EA4C-475D-BF93-8DCF48161EB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3D781B-E9D7-4335-9B51-37E232A28583}">
   <dimension ref="A1:N897"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAB490CF-8FDE-43AC-89D3-2E0B37E28F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8250DE5A-48CF-40D5-BBF4-61E133B85F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{46ED21DB-057C-45C7-858F-B6F4D8D157F8}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{71A93199-90D9-4150-9A4E-A83A4B60D710}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5320,7 +5320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3D781B-E9D7-4335-9B51-37E232A28583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E0A513E-0316-470B-BAF1-1C797E2544EB}">
   <dimension ref="A1:N897"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -25057,7 +25057,7 @@
         <v>24000</v>
       </c>
       <c r="L469">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M469">
         <v>0</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{202E8881-3A2A-445E-BE48-FCB579353D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA6F020-60B4-42FF-8C33-9440833F0EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{78DD5431-4C6B-4C33-A7E8-A7F5873F8C10}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{F8D95E5D-FD57-432B-9E37-46E764F533F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2192,7 +2192,7 @@
     <t>EC100457</t>
   </si>
   <si>
-    <t xml:space="preserve">LINTERNA MINERA MINI CON PILAS </t>
+    <t>LINTERNA MINERA MINI CON PILAS</t>
   </si>
   <si>
     <t>LINTERNA MINI RECARGABLE CAMUFLADO 512</t>
@@ -5362,7 +5362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2799CED5-8492-49B8-AA54-BCDBDABFDC02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4D7BA9-55A4-4260-9115-4C2DC702DB0D}">
   <dimension ref="A1:N904"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -8487,7 +8487,7 @@
         <v>711</v>
       </c>
       <c r="L74">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -10213,7 +10213,7 @@
         <v>16000</v>
       </c>
       <c r="L115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M115">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>21</v>
       </c>
       <c r="I158">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="J158">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K158">
         <v>500</v>
@@ -13363,13 +13363,13 @@
         <v>21</v>
       </c>
       <c r="I190">
+        <v>2000</v>
+      </c>
+      <c r="J190">
+        <v>800</v>
+      </c>
+      <c r="K190">
         <v>92</v>
-      </c>
-      <c r="J190">
-        <v>92</v>
-      </c>
-      <c r="K190">
-        <v>1000</v>
       </c>
       <c r="L190">
         <v>530</v>
@@ -13794,13 +13794,13 @@
         <v>4000</v>
       </c>
       <c r="J200">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="K200">
         <v>689</v>
       </c>
       <c r="L200">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M200">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>3079</v>
       </c>
       <c r="L209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M209">
         <v>0</v>
@@ -14943,7 +14943,7 @@
         <v>1365</v>
       </c>
       <c r="L227">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M227">
         <v>0</v>
@@ -15119,7 +15119,7 @@
         <v>1929</v>
       </c>
       <c r="L231">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M231">
         <v>0</v>
@@ -15295,7 +15295,7 @@
         <v>9000</v>
       </c>
       <c r="L235">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M235">
         <v>0</v>
@@ -17165,10 +17165,10 @@
         <v>21</v>
       </c>
       <c r="I279">
-        <v>1215.2</v>
+        <v>3400</v>
       </c>
       <c r="J279">
-        <v>1215.2</v>
+        <v>2200</v>
       </c>
       <c r="K279">
         <v>1215.2</v>
@@ -17839,7 +17839,7 @@
         <v>2262</v>
       </c>
       <c r="L295">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M295">
         <v>0</v>
@@ -18384,7 +18384,7 @@
         <v>0</v>
       </c>
       <c r="L308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M308">
         <v>0</v>
@@ -18674,7 +18674,7 @@
         <v>563</v>
       </c>
       <c r="L315">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M315">
         <v>0</v>
@@ -19084,7 +19084,7 @@
         <v>15000</v>
       </c>
       <c r="L325">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M325">
         <v>0</v>
@@ -20273,7 +20273,7 @@
         <v>2453</v>
       </c>
       <c r="L354">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M354">
         <v>0</v>
@@ -20642,7 +20642,7 @@
         <v>0</v>
       </c>
       <c r="L363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M363">
         <v>0</v>
@@ -20926,7 +20926,7 @@
         <v>15000</v>
       </c>
       <c r="J370">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="K370">
         <v>2400</v>
@@ -21143,7 +21143,7 @@
         <v>3169</v>
       </c>
       <c r="L375">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M375">
         <v>0</v>
@@ -21348,7 +21348,7 @@
         <v>0</v>
       </c>
       <c r="L380">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M380">
         <v>0</v>
@@ -21790,7 +21790,7 @@
         <v>885</v>
       </c>
       <c r="J391">
-        <v>885</v>
+        <v>1500</v>
       </c>
       <c r="K391">
         <v>885</v>
@@ -21828,16 +21828,16 @@
         <v>21</v>
       </c>
       <c r="I392">
-        <v>2516</v>
+        <v>6900</v>
       </c>
       <c r="J392">
-        <v>2516</v>
+        <v>4000</v>
       </c>
       <c r="K392">
         <v>2516</v>
       </c>
       <c r="L392">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M392">
         <v>0</v>
@@ -22086,7 +22086,7 @@
         <v>0</v>
       </c>
       <c r="L398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M398">
         <v>0</v>
@@ -23419,7 +23419,7 @@
         <v>3678</v>
       </c>
       <c r="J430">
-        <v>3678</v>
+        <v>6500</v>
       </c>
       <c r="K430">
         <v>3678</v>
@@ -24592,7 +24592,7 @@
         <v>22000</v>
       </c>
       <c r="L457">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M457">
         <v>0</v>
@@ -25008,7 +25008,7 @@
         <v>20000</v>
       </c>
       <c r="L467">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M467">
         <v>0</v>
@@ -25225,7 +25225,7 @@
         <v>20000</v>
       </c>
       <c r="L472">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M472">
         <v>0</v>
@@ -25445,7 +25445,7 @@
         <v>20000</v>
       </c>
       <c r="L477">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M477">
         <v>0</v>
@@ -25489,7 +25489,7 @@
         <v>27000</v>
       </c>
       <c r="L478">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M478">
         <v>0</v>
@@ -25788,7 +25788,7 @@
         <v>23000</v>
       </c>
       <c r="L485">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -25829,7 +25829,7 @@
         <v>25000</v>
       </c>
       <c r="L486">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M486">
         <v>0</v>
@@ -25999,7 +25999,7 @@
         <v>23000</v>
       </c>
       <c r="L490">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M490">
         <v>0</v>
@@ -26972,7 +26972,7 @@
         <v>10740</v>
       </c>
       <c r="L513">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M513">
         <v>0</v>
@@ -27013,7 +27013,7 @@
         <v>20000</v>
       </c>
       <c r="L514">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M514">
         <v>0</v>
@@ -27145,7 +27145,7 @@
         <v>18000</v>
       </c>
       <c r="L517">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M517">
         <v>0</v>
@@ -27233,7 +27233,7 @@
         <v>11276</v>
       </c>
       <c r="L519">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M519">
         <v>0</v>
@@ -27274,7 +27274,7 @@
         <v>24000</v>
       </c>
       <c r="L520">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M520">
         <v>0</v>
@@ -27359,7 +27359,7 @@
         <v>20000</v>
       </c>
       <c r="L522">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M522">
         <v>0</v>
@@ -27620,7 +27620,7 @@
         <v>23000</v>
       </c>
       <c r="L528">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M528">
         <v>0</v>
@@ -27708,7 +27708,7 @@
         <v>22000</v>
       </c>
       <c r="L530">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M530">
         <v>0</v>
@@ -27840,7 +27840,7 @@
         <v>20000</v>
       </c>
       <c r="L533">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M533">
         <v>0</v>
@@ -28142,7 +28142,7 @@
         <v>11333</v>
       </c>
       <c r="L540">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -28664,7 +28664,7 @@
         <v>45000</v>
       </c>
       <c r="L552">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M552">
         <v>0</v>
@@ -28919,7 +28919,7 @@
         <v>22000</v>
       </c>
       <c r="L558">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M558">
         <v>0</v>
@@ -29180,7 +29180,7 @@
         <v>57000</v>
       </c>
       <c r="L564">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M564">
         <v>0</v>
@@ -30212,7 +30212,7 @@
         <v>23000</v>
       </c>
       <c r="L588">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M588">
         <v>0</v>
@@ -30426,7 +30426,7 @@
         <v>24000</v>
       </c>
       <c r="L593">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M593">
         <v>0</v>
@@ -30511,7 +30511,7 @@
         <v>35000</v>
       </c>
       <c r="L595">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M595">
         <v>0</v>
@@ -30813,7 +30813,7 @@
         <v>21000</v>
       </c>
       <c r="L602">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M602">
         <v>0</v>
@@ -31109,7 +31109,7 @@
         <v>23000</v>
       </c>
       <c r="L609">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M609">
         <v>0</v>
@@ -33627,7 +33627,7 @@
         <v>6932</v>
       </c>
       <c r="L668">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M668">
         <v>0</v>
@@ -33791,7 +33791,7 @@
         <v>10000</v>
       </c>
       <c r="J672">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="K672">
         <v>1460</v>
@@ -34248,7 +34248,7 @@
         <v>112</v>
       </c>
       <c r="J683">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="K683">
         <v>112</v>
@@ -36083,7 +36083,7 @@
         <v>10000</v>
       </c>
       <c r="L726">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M726">
         <v>0</v>
@@ -36828,7 +36828,7 @@
         <v>10000</v>
       </c>
       <c r="L743">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M743">
         <v>0</v>
@@ -39091,7 +39091,7 @@
         <v>1971</v>
       </c>
       <c r="L796">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M796">
         <v>0</v>
@@ -39132,7 +39132,7 @@
         <v>1800</v>
       </c>
       <c r="L797">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M797">
         <v>0</v>
@@ -40175,16 +40175,16 @@
         <v>21</v>
       </c>
       <c r="I822">
-        <v>2328</v>
+        <v>9000</v>
       </c>
       <c r="J822">
-        <v>2328</v>
+        <v>4000</v>
       </c>
       <c r="K822">
         <v>2328</v>
       </c>
       <c r="L822">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M822">
         <v>0</v>
@@ -40354,7 +40354,7 @@
         <v>29820</v>
       </c>
       <c r="L826">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M826">
         <v>0</v>
@@ -41227,7 +41227,7 @@
         <v>900</v>
       </c>
       <c r="L847">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M847">
         <v>0</v>
@@ -42595,7 +42595,7 @@
         <v>4800</v>
       </c>
       <c r="L880">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M880">
         <v>0</v>
@@ -42888,7 +42888,7 @@
         <v>5454</v>
       </c>
       <c r="L887">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M887">
         <v>0</v>
@@ -43266,7 +43266,7 @@
         <v>500</v>
       </c>
       <c r="L896">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M896">
         <v>0</v>

--- a/tienda/productos.xlsx
+++ b/tienda/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA6F020-60B4-42FF-8C33-9440833F0EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E356FDA-54C5-4A9F-92CE-59E8660CD858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{F8D95E5D-FD57-432B-9E37-46E764F533F1}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{6C86DD04-0CA8-4B57-B439-1F0C7E06A732}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5362,7 +5362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4D7BA9-55A4-4260-9115-4C2DC702DB0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7027A99A-9683-44C2-AECD-15298B5ABD1D}">
   <dimension ref="A1:N904"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -18302,7 +18302,7 @@
         <v>3225.8</v>
       </c>
       <c r="L306">
-        <v>0</v>
+        <v>-11.699999809265099</v>
       </c>
       <c r="M306">
         <v>0</v>
@@ -20932,7 +20932,7 @@
         <v>2400</v>
       </c>
       <c r="L370">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M370">
         <v>0</v>
@@ -24331,7 +24331,7 @@
         <v>23000</v>
       </c>
       <c r="L451">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M451">
         <v>0</v>
@@ -24504,7 +24504,7 @@
         <v>20000</v>
       </c>
       <c r="L455">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M455">
         <v>0</v>
@@ -25137,7 +25137,7 @@
         <v>26000</v>
       </c>
       <c r="L470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M470">
         <v>0</v>
@@ -25313,7 +25313,7 @@
         <v>23000</v>
       </c>
       <c r="L474">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M474">
         <v>0</v>
@@ -27057,7 +27057,7 @@
         <v>20000</v>
       </c>
       <c r="L515">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M515">
         <v>0</v>
@@ -27145,7 +27145,7 @@
         <v>18000</v>
       </c>
       <c r="L517">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M517">
         <v>0</v>
@@ -27359,7 +27359,7 @@
         <v>20000</v>
       </c>
       <c r="L522">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M522">
         <v>0</v>
@@ -27708,7 +27708,7 @@
         <v>22000</v>
       </c>
       <c r="L530">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M530">
         <v>0</v>
@@ -28790,7 +28790,7 @@
         <v>23000</v>
       </c>
       <c r="L555">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M555">
         <v>0</v>
@@ -28831,7 +28831,7 @@
         <v>25000</v>
       </c>
       <c r="L556">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M556">
         <v>0</v>
